--- a/reports/housing_hanoi_clean.xlsx
+++ b/reports/housing_hanoi_clean.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R259"/>
+  <dimension ref="A1:N259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,26 +496,6 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>moTa</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
           <t>list_id</t>
         </is>
       </c>
@@ -571,31 +551,6 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O2" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ 7 TẦNG CẠNH HỒ THẠCH BÀN, MẶT ĐƯỜNG Ô TÔ TRÁNH FULL NỘI THẤT</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>🔥 SIÊU PHẨM CẠNH HỒ THẠCH BÀN – 7 TẦNG THANG MÁY 50M² – Ô TÔ TRÁNH – GARA – VIEW CÔNG VIÊN – G.IÁ HẤP DẪN 🔥
-🏡 Nhà đẹp 7 tầng – thang máy xịn – full nội thất cao cấp
-📐 Thiết kế hiện đại – ở sướng, kinh doanh cực tốt
-🚗 Đường rộng, vỉa hè – ô tô tránh nhau thoải mái
-🌳 View công viên cây xanh – không khí trong lành
-📍 Cách Hồ Thạch Bàn 100m tận hưởng cuộc sống 
-🛍️ Cách Aeon Mall Long Biên ~500m – tiện ích bạt ngàn
-💰 Gi.á hấp dẫn – chủ thiện chí bán nhanh, có thương lượng
-📕 Sổ đỏ chính chủ, sẵn sàng giao dịch
-📞 Alo Em Thiêm xem nhà ngay hôm nay 🚀</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
         <v>131475977</v>
       </c>
     </row>
@@ -650,29 +605,6 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>21.02167</v>
-      </c>
-      <c r="O3" t="n">
-        <v>105.91418</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Cần bán nhà dân xây 4 tầng 68m² full nội thất ô tô đỗ cửa Long Biên</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>🏡 ✨ Nhà dân xây chắc chắn, thiết kế hiện đại
-🚗 Ô tô đỗ cửa, 2 mặt ngõ thoáng sáng
-🛏️ 4 phòng ngủ rộng, công năng đầy đủ
-🛋️ Full nội thất – xách vali vào ở ngay
-📍 Vị trí đẹp: Gần Aeon Mall Long Biên, gần trường THPT – tiện ích đầy đủ, khu dân trí cao, an ninh tốt
-📕 Sổ đỏ chính chủ, sẵn sàng giao dịch
-🔥 Phù hợp ở gia đình hoặc đầu tư giữ tiền cực tốt
-📞 Alo em Thiêm xem nhà ngay</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
         <v>131756849</v>
       </c>
     </row>
@@ -727,44 +659,6 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>21.05286</v>
-      </c>
-      <c r="O4" t="n">
-        <v>105.92033</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bán Nhà Trung Tâm Phường Phúc Lợi, Cạnh Chợ Phúc Lợi</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: SIÊU PHẨM PHÚC LỢI] NHÀ MỚI KÍNH KOONG 
-42M2x5T - MẶT TIỀN RỘNG - CHỈ 7,2 TỶ
-Chính chủ cần bán gấp căn "Hoa hậu" tại trung tâm phường Phúc Lợi, quận Long Biên. Nhà tự xây cực kỳ tâm huyết, hiện đại, xem là mê!
-1. Thông số vàng:
-• Diện tích: 42m2.
-• Mặt tiền: 4,7m (Rất rộng, nhà cực thoáng, dễ bố trí nội thất).
-• Xây dựng: 5 tầng kiên cố, thiết kế hiện đại, có gu thẩm mỹ riêng, tối ưu hóa công năng sử dụng.
-• Tình trạng: Nhà mới hoàn thiện, vẫn còn thơm mùi sơn mới, khách mua chỉ việc xách vali về ở ngay.
-2. Thiết kế tinh tế:
-• Nhà vuông vức, không lỗi phong thủy.
-• Nội thất và trang thiết bị được chọn lọc kỹ lưỡng, đảm bảo sự sang trọng và bền bỉ.
-• Không gian các phòng đều có ánh sáng tự nhiên, thoáng đãng.
-3. Vị trí đắc địa:
-• Tọa lạc tại trung tâm phường Phúc Lợi, khu vực dân trí cao, an ninh tuyệt đối.
-• Gần trường học các cấp, chợ dân sinh và các tiện ích công cộng chỉ trong bán kính vài trăm mét.
-• Giao thông thuận tiện, đường xá sạch đẹp.
-4. Giá bán:
-• Giá cực sốc: 7,2 tỷ (Có thương lượng cho khách thiện chí).
-• Đây là mức giá không thể tìm được căn thứ hai đẹp và chất lượng hơn trong cùng phân khúc tại khu vực.
-5. Pháp lý:
-• Sổ đỏ chính chủ, pháp lý sạch, sẵn sàng giao dịch ngay.
-☎️ *** liên hệ em cường để xem nhà 🏚️</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
         <v>132019978</v>
       </c>
     </row>
@@ -819,28 +713,6 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O5" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>📢📢📢Nhà Mặt Sau Aeon Long Biên 40m2 x 7 Tầng Kinh Doanh - 2 Ô Tô Tránh</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>✨️Diện tích 40m2/ 7 tầng
-- Mặt tiền 3.1m, hướng Tây
-- Trước nhà 2 ô tô tránh nhau, trục kinh doanh sầm uất, 300m tới cổng sau Aeon Long Biên
-- Thiết kế 6 tầng 1 tum, thang máy nhập khẩu, 4 ngủ
-- Pháp lý chuẩn, ss giao dịch
-Giá hơn 12 tỷ còn thương lượng
-📱Phở bò/ zep lào: Huy Định *** xem nhà và tư vấn 24/7</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
         <v>132040260</v>
       </c>
     </row>
@@ -895,28 +767,6 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>21.040733</v>
-      </c>
-      <c r="O6" t="n">
-        <v>105.89656</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>📢📢📢Nhà 6 Tầng Ngay Mặt Phố Mai Phúc - Ngõ Rộng Ít Nhà</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>✨️Diện tích 35m2 / 6 tầng
-- Mặt tiền 5.01m = hậu, hướng Đông Nam
-- Trước nhà ngõ gần 3m, cách 15m ra mặt phố Mai Phúc, Phúc Đồng, qua Aeon Long Biên chỉ 5p
-- Thiết kế 5 tầng 1 tum, thang máy nhập khẩu 450 kg
-- Pháp lý chuẩn, ss giao dịch
-Giá Nhỉnh 9 tỷ
-📱Phở bò/ zep lào: Huy Định *** xem nhà và tư vấn 24/7</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
         <v>132040123</v>
       </c>
     </row>
@@ -971,27 +821,6 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>21.034845</v>
-      </c>
-      <c r="O7" t="n">
-        <v>105.91271</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>📢📢📢 GẦN NGAY MẶT PHỐ SÀI ĐỒNG - LONG BIÊN | 53M2 X 6 TẦNG KINH DOANH</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>✨️Diện tích 53m2 / 6 tầng
-- Mặt tiền 4.5m, hướng Đông Bắc
-- Trước nhà gần 5m, ngõ thông ô tô tránh, cách 50m ra mặt phố Sài Đồng, kinh doanh đỉnh
-- Thiết kế 6 tầng, thang máy, full nội thất, lô góc cực thoáng
-Giá 16.x tỷ còn thương lượng
-📱Phở bò/ zep lào: Huy Định *** xem nhà và tư vấn 24/7</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
         <v>132039613</v>
       </c>
     </row>
@@ -1046,43 +875,6 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>21.048788</v>
-      </c>
-      <c r="O8" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bán Gấp phân lô quân đội 92m2 8 tầng thang máy,gara ô tô, full đồ</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>BÁN GẤP NHÀ KHU VIP PHÂN LÔ QUÂN ĐỘI 918 – PHÚC ĐỒNG – LONG BIÊN 🔥
-💎 Biệt thự phố 8 tầng thang máy – 92m² – Gara ô tô – Hàng cực hiếm
-📍 Vị trí vàng Long Biên:
-Khu phân lô quân đội 918 Phúc Đồng, sát sân Golf Long Biên – Aeon Mall – Cầu Vĩnh Tuy, khu dân trí cao, an ninh tuyệt đối, không khí xanh – sạch – yên tĩnh.
-🏠 Thông số đỉnh cao:
-Diện tích 92m² thực tế, thoáng trước – thoáng sau, có khe thoáng 5m²
-Nhà 8 tầng thang máy, thiết kế tân cổ điển hiện đại – ở sướng như khách sạn 5⭐
-Đường trước nhà 6m, ô tô tránh, 7 chỗ quay đầu – đỗ cửa ngày đêm
-🧱 Công năng hoàn hảo:
-T1: Gara ô tô + kho
-T2: Phòng khách riêng biệt
-T3: Master đẳng cấp – bể sục, xông hơi, điều hòa âm trần
-T4–5: Mỗi tầng 2 ngủ khép kín, hút gió tự nhiên
-T6: Bếp + phòng ăn sang trọng
-T7: Phòng thờ + sân BBQ
-T8: Sân thượng, trồng cây xanh
-✅ Xây dựng cực kỳ chắc chắn: ép cọc BTCT, khung cột đúng bản vẽ, hoàn thiện tỉ mỉ từng chi tiết phào chỉ
-✅ Pháp lý chuẩn: Sổ đỏ riêng, GPXD, bản vẽ đầy đủ – hỗ trợ vay bank 3 bên
-🚗 Kết nối nhanh: Đàm Quang Trung – Cổ Linh – Nguyễn Văn Linh (QL5) – QL1A – Cao tốc Hà Nội Hải Phòng – Nguyễn Văn Cừ – BV Tâm Anh…
-💰 Giá bán: THƯƠNG LƯỢNG TRỰC TIẾP CHỦ – BÁN NHANH TRONG THÁNG
-📹 Xem video thực tế trên TikTok để cảm nhận rõ đẳng cấp căn nhà
-📞 Liên hệ ngay (có nhà là có tiền): ***/***</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
         <v>131995974</v>
       </c>
     </row>
@@ -1137,31 +929,6 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>21.05643</v>
-      </c>
-      <c r="O9" t="n">
-        <v>105.903</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Chính chủ cần bán phố  Kim Quan 32m2- 5T- 3 phòng ngủ- 6.6 tỷ</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Chính chủ cần bán phố  Kim Quan 32m2- 5T- 3 phòng ngủ- 6.6 tỷ
-Vị trí: gần làng Lệ Mật, phố Đoàn Khuê, phố Ô Cách. 5 phút gần BigC Long Biên, bệnh viện đa khoa Đức Giang,  công viên Long Biên. Hàng xóm  khu đô thị Việt Hưng, Vinhomes 	Riverside. Trước nhà ô tô đỗ cửa, ngõ nông và thông, chỉ 10m ra ô tô tránh
-Thiết kế:  Nhà xây chắc chắn,  nhà ở được vài năm còn như mới chủ rất giữ gìn, nội thất cơ bản, 3 phòng ngủ. Chủ có việc gấp cần tiền nên để giá tốt.  Phù hợp mua định cư lâu dài, đầu tư sinh lời.
-Sổ vuông đẹp,  pháp lý đầy đủ, chính chủ.
-LH: Hồng Thúy để biết thêm chi tiết về căn nhà và qua xem thực tế để biết thêm các tiện ích xung quanh
-Ngoài ra em Thúy còn có 1 số căn nhà đẹp khác thuộc khu vực này
-Anh/ chị quan tâm, kết bạn Zalo với Hồng Thúy- chuyên BĐS Thổ cư để cập nhật những lô đất đẹp, ngôi nhà xinh mới nhất khu vực này nhé!
-Chuyên BĐS khu vực Phường Bồ Đề, Phường Việt Hưng, Phường Phúc Lợi, Phường Long Biên ( quận Long Biên cũ)- TP. Hà Nội
-Ngọc Thụy- Thượng Thanh- Đức Giang- Thanh Am- Nguyễn Văn Cừ-Ngọc Lâm- Phú Viên- Ngô Gia Tự- Nguyễn Văn Linh- Tân Thụy- Mai Phúc- Chu Huy Mân- Kim Quan- Kim Quan Thượng- Việt Hưng- Ái Mộ-  Bồ Đề- Hồng Tiến- Hoàng Như Tiếp- Bắc Cầu- Bắc Biên
-#batdongsan#nhadep#nhapho #dautu</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
         <v>129972265</v>
       </c>
     </row>
@@ -1216,31 +983,6 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O10" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bán nhà Khu A38 Tư Đình Long Biên 60m 5 tầng Giá 13,9 tỷ </t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚡ BÁN NHÀ _ KHU PHÂN LÔ A38 -TƯ ĐÌNH –LONG BIÊN _ 60M² XÂY 5 TẦNG – NGÕ  Ô TÔ TRÁNH – NHANH CHÂN SỞ HỮU EM NÓ ---ĐỪNG ĐỂ TUỘT MẤT CƠ HỘI 
-💥 GIÁ  – CHỈ HƠN   13 TỶ
-🎈Thực sự khu vực này .với phân khúc này cực kỳ ít nhà bán ..quý khách hàng nhanh chân để sở hữu em nó thôi 
-📍 Vị trí vàng – tăng giá từng ngày:
-• Cách cầu Trần Hưng Đạo (đang thi công) ~500m
-• Kết nối nhanh cầu Vĩnh Tuy – sang phố cổ ít phút
-•🎈 Gần ngay trung tâm thương mại AEON Mall Long Biên, tiện ích bạt ngàn  ...chỉ sang cuối  năm 2027 cầu #TRẦN #HƯNG #ĐẠO # đi vào hoạt động thông tuyến thì khu vực này #VIP bậc nhất long biên luôn 
-👉 Đầu tư đón sóng hạ tầng – tiềm năng tăng giá rõ rệt
-📜 Sổ đỏ chính chủ – pháp lý sạch – giao dịch ngay
-</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
         <v>132038442</v>
       </c>
     </row>
@@ -1295,30 +1037,6 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O11" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Nhà đẹp tái định cư giang biên</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: HÓT HÒN HỌT
-NHỈNH 12tỷ có ngay căn nhà tái định cư Giang biên. ĐẸP!
-- DT 40m. Mặt tiền = hậu 4,04m. Thông số tuyệt vời
-- Sẵn nhà 4 tầng kiên cố
-- Vỉa hè rộng, công viên ngay cạnh
-- Trường học các cấp, tiện ích ngập tràn
-Gần vinhome, bigc, aeon
-Em T Râu *** luôn ss!</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
         <v>132023684</v>
       </c>
     </row>
@@ -1373,26 +1091,6 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>21.036516</v>
-      </c>
-      <c r="O12" t="n">
-        <v>105.91136</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bán nhà Sài Đồng 50m² ngõ ô tô thông 6 tầng thang máy giá đầu tư</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Ban nha Sài Đồng 50m² x 7 tầng thang máy mặt ngõ ô tô tránh. Gi.á 12,x tỷ
-Vị trí đẹp cách Aeon, cầu Vĩnh Tuy 1km, Khu vực dân cư văn minh, dân trí cao. Gần trường cấp 1, cấp 2 Sài Đồng, hàng xóm FLC Sài Đồng, Vinhome Riverside.
-Nhà mặt ngõ ô tô tránh, mở cửa hàng kinh doanh ngày đêm, giá trị bất động sản tăng mạnh.
-Sổ đỏ chính chủ, sẵn giao dịch
-Alo em Thiêm xem nhà ngay hôm nay</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
         <v>132035068</v>
       </c>
     </row>
@@ -1447,26 +1145,6 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>21.057487</v>
-      </c>
-      <c r="O13" t="n">
-        <v>105.88704</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bán nhà Thượng Thanh</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Bán nhà riêng phố Thượng Thanh, Long Biên  - ba bước chân ra mặt phố rộng 15m ô tô…
-- Nhà 3 tầng, 2 thoáng + ban công trước sau, 3 ngủ rộng rãi, thiết kế đầy đủ công năng.
-- Vị trí thoáng, 1 ngoặt ra mặt phố Thượng Thanh, đường ô tô lý thuyết thông bàn cờ, 30m ra đường to ô tô tránh nhau.
-- Sổ đỏ chính chủ, vuông vắn, chủ nhà thiện chí.</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
         <v>131993579</v>
       </c>
     </row>
@@ -1521,32 +1199,6 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>21.036098</v>
-      </c>
-      <c r="O14" t="n">
-        <v>105.87419</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>HIẾM – NHÀ BỒ ĐỀ DÂN XÂY – NỞ HẬU – Ô TÔ 7 CHỖ QUA NHÀ – NGÕ THÔNG TỨ</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: HIẾM – NHÀ BỒ ĐỀ DÂN XÂY – NỞ HẬU – Ô TÔ 7 CHỖ QUA NHÀ – NGÕ THÔNG TỨ TUNG 🔥
-🏡 Nhà nằm – vị trí cực đẹp, ngõ thông khắp ngả, kết nối nhanh ra Hồng Tiến
-.🏗️ Nhà dân xây tâm huyết, khung cột chắc chắn, nở hậu nhẹ – phong thủy tốt, ở cực vượng.
-💥 Thiết kế tối ưu – full công năng: 
-• Tầng 1: Phòng khách + để xe 
-• Tầng 2,3,4: Mỗi tầng 1 phòng ngủ khép kín
- • Tầng 5: Bếp + phòng ăn + phòng thờ + sân phơi
-🚗 Đường trước nhà rộng, ô tô 7 chỗ qua nhà, có thể vào nhà nếu cần.
-🌳 Tiện ích bạt ngàn trong bán kính 100m: chợ, trường học, công viên, hồ điều hòa – sống cực tiện nghi.
-📕 Sổ đỏ chính chủ, cất két – sẵn sàng giao dịch ngay.</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
         <v>132032070</v>
       </c>
     </row>
@@ -1601,31 +1253,6 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>21.060038</v>
-      </c>
-      <c r="O15" t="n">
-        <v>105.89593</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>NHÀ Ô CÁCH, DÂN XÂY GẦN Ô TÔ DT RỘNG GIÁ TỐT, TIỆN ÍCH Ở SƯỚNG</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: NHÀ Ô CÁCH – NGÕ NÔNG – GẦN Ô TÔ TRÁNH – 45M² ĐẸP Ở NGAY
- 🔥🏡 Vị trí trung tâm – đi lại cực tiện:* Cách mặt phố Ô Cách ~30m, ngõ thông thoáng* Gần ô tô tránh, chỉ ~100m ra Ngô Gia Tự* Khu dân cư đông đúc, an sinh tốt
-📍 Tiện ích đầy đủ quanh nhà:* Gần chợ Ô Cách, Kim Quan* Sát Bệnh viện Đức Giang* Gần trường THCS Đức Giang &amp; THPT Đức Giang
-🏠 Nhà dân xây – công năng hợp lý:
-* T1: Khách + bếp + để xe
-* T2: 2 phòng ngủ
-* T3: 1 ngủ + phòng thờ + sân phơi    
-→ Cầu thang giữa, thoáng trước sau
-* Sổ đỏ chính chủ, sẵn sàng giao dịch</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
         <v>132031892</v>
       </c>
     </row>
@@ -1680,28 +1307,6 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>21.051487</v>
-      </c>
-      <c r="O16" t="n">
-        <v>105.89713</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ VIỆT HƯNG: 69M2 - MT 5M - ĐƯỜNG 6M - DÒNG TIỀN 300TR/NĂM - GIÁ</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>🌟 SIÊU PHẨM CHÀO CHỦ MỚI 🌟
-• Diện tích: 69m2, mặt tiền 5m vuông vắn.
-• Đường trước nhà 6m, ô tô đi lại kinh doanh tấp nập.
-• Nhà dân xây kiên cố, đầy đủ công năng, thiết kế siêu hợp lý.
-• Tiện ích bủa vây, ở hay kinh doanh đều đỉnh.
-• ĐẶC BIỆT: Nhà đang mang lại dòng tiền chảy xiết 300 triệu/năm. Mua là có lãi!
-Giá cực tốt: 17.5 Tỷ. Sổ đỏ hoa hậu, sẵn sàng giao dịch.</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
         <v>131279895</v>
       </c>
     </row>
@@ -1756,26 +1361,6 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O17" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Siêu hiếm ngõ to Thanh Am 35m2 6T thang máy gara, giá nhỉnh 10tỷ</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Chủ nhà chuyển đổi nhu cầu cần bán gấp siêu phẩm tâm huyết tại Thanh Am, Long Biên. Nhà đẹp không tì vết, khách đến xem là mê!
-Đường ngõ: Đường rộng, ngõ to, ô tô phi ầm ầm vào tận Gara trong nhà.
-Chất lượng: Hàng hiếm nhà dân xây 6 tầng kiên cố, không phải nhà xây thương mại. Đầu tư hệ thống thang máy nhập khẩu cao cấp.
-Thiết kế: Diện tích 35m2, kiến trúc hiện đại, sang trọng. Bố trí đầy đủ công năng với các phòng ngủ rộng rãi, ngập tràn sinh khí.
-Sổ đỏ: Pháp lý chuẩn chỉnh, sẵn sàng sang tên trong nốt nhạc.</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
         <v>131261137</v>
       </c>
     </row>
@@ -1830,28 +1415,6 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O18" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>TRƯỜNG LÂM 40M2- 5TẦNG-MẶT TIỀN 4.2M- NGÕ THÔNG GẦN Ô TÔ - GIÁ 8.6 TỶ</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Cần bán gấp căn nhà cực đẹp phố Trường Lâm. Thông số chuẩn, thiết kế xứng tầm, xách vali về ở ngay không cần sắm sửa thêm bất cứ thứ gì!
-Diện tích &amp; Mặt tiền: 40m2 x 5 tầng, Mặt tiền 4.2m cực hiếm, đất vuông như tờ A4.
-Thiết kế &amp; Nội thất: Phong cách thiết kế hiện đại, trẻ trung. Trang bị full nội thất nhập khẩu từ sofa, bàn ăn đến giường tủ... sang xịn mịn.
-Công năng: Bố trí thông minh với 3 phòng ngủ Master khép kín siêu rộng rãi.
-Vị trí: Ngõ thông tứ tung. Vài bước chân là ra mặt ngõ ô tô tránh. Tiện ích bạt ngàn bao quanh, khu vực dân trí cao.
-Sổ đỏ: Chính chủ, nét căng, sẵn sàng sang tên.
-💵 Giá bán: 8.6 Tỷ (Khách ưng là chốt, giá cả thương lượng linh động).</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
         <v>131260528</v>
       </c>
     </row>
@@ -1906,35 +1469,6 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>21.067125</v>
-      </c>
-      <c r="O19" t="n">
-        <v>105.88424</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>🔥 HÀNG HIẾM ĐỨC GIANG - 5 TẦNG THANG MÁY - Ô TÔ ĐỖ CỬA - DÒNG TIỀN CHẢ</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💎 Thông số vàng: 47m2 x 5 tầng thang máy xịn sò.
-💰 Giá: Nhỉnh 10 tỷ (Thương lượng mạnh cho khách thiện chí).
-📍 Vị trí Độc tôn:
-• Ngõ nông, thoáng sáng, ô tô đỗ ngay cửa.
-• Chỉ 15m ra mặt ngõ to ô tô tránh nhau, giao thông kết nối tứ tung.
-• Khu vực tiện ích thượng lưu bủa vây, không thiếu thứ gì.
-🏠 Thiết kế Đẳng cấp:
-• Nhà xây mới 5 tầng, thang máy nhập khẩu chạy êm ru.
-• Thiết kế hiện đại, tối ưu công năng, nội thất sang trọng.
-📈 Giá trị kép:
-• Ở Đỉnh: Không gian sống đẳng cấp, dân trí cao.
-• Đầu Tư: Vị trí đắc địa, dễ dàng cho thuê văn phòng hoặc căn hộ dịch vụ, dòng tiền chẩy xiết quanh năm.
-📕 Pháp lý: Sổ đỏ chính chủ, vuông đẹp, sẵn sàng giao dịch.</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
         <v>131191440</v>
       </c>
     </row>
@@ -1989,31 +1523,6 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>21.051487</v>
-      </c>
-      <c r="O20" t="n">
-        <v>105.89713</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Mới! Việt Hưng 33m2x5T-MT4m, ngõ rộng ô tô 15m. Chỉ nhỉnh 6 tỷ</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 📍 Vị trí cực đỉnh: * Nằm tại khu vực Việt Hưng sầm uất, tiện ích bạt ngàn bao quanh không thiếu thứ gì (chợ, trường học các cấp, siêu thị,...).
-• Giao thông vô cùng thuận tiện: Ngõ trước nhà rộng rãi, thông thoáng các ngả. Đặc biệt, chỉ cách đúng 15m là ra đường lớn ô tô tránh nhau thoải mái.
-🏠 Thiết kế &amp; Công năng:
-• Diện tích: 33m2.
-• Mặt tiền: 4m cân đối, bề thế.
-• Kết cấu: Nhà 5 tầng do chủ tự tay xây dựng cực kỳ tâm huyết và kiên cố. Thiết kế theo phong cách hiện đại, tối ưu không gian ánh sáng, đầy đủ công năng sử dụng cho gia đình.
-• Tình trạng: Nhà mới tinh, thiết kế bắt mắt, khách mua chỉ việc xách vali về ở ngay.
-💰 Giá bán: Chỉ nhỉnh 6 tỷ (Có thương lượng cho khách hàng thiện chí).
-Pháp lý chuẩn mực, sẵn sàng giao dịch ngay.</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
         <v>131419540</v>
       </c>
     </row>
@@ -2068,27 +1577,6 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O21" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Tổ ấm hoàn hảo cho đại gia đình! Nhà Đức Giang 55m2, 5 tầng, 4PN, full</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Bạn đang tìm một không gian sống rộng rãi, tiện nghi cho gia đình nhiều thế hệ tại khu vực Đức Giang? Đây chính là lựa chọn không thể bỏ qua!
-• Căn nhà 5 tầng, diện tích 55m2 được thiết kế thông minh với 4 phòng ngủ siêu rộng.
-• Tình trạng: Mới đẹp, chủ để lại toàn bộ nội thất xịn, dọn về ở ngay.
-• Đường đi lối lại: Cực thoáng! Ngõ phân lô bàn cờ, ô tô đỗ cửa, cách 3 bước chân là ra đường ô tô tránh nhau. Tiện ích nội khu bao la.
-• Giá đầu tư hoặc mua ở cực tốt: Nhỉnh 9 tỷ.</t>
-        </is>
-      </c>
-      <c r="R21" t="n">
         <v>132030447</v>
       </c>
     </row>
@@ -2143,23 +1631,6 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>21.043814</v>
-      </c>
-      <c r="O22" t="n">
-        <v>105.872314</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP BỒ ĐỀ- 5 tỷ-Ở Ngay</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Nhà đẹp trung tâm bồ đề thiết kế 5 tầng ở ngay full nội thất.</t>
-        </is>
-      </c>
-      <c r="R22" t="n">
         <v>132011432</v>
       </c>
     </row>
@@ -2214,33 +1685,6 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>21.049221</v>
-      </c>
-      <c r="O23" t="n">
-        <v>105.86504</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>🌟 BÁN NHÀ NGỌC THỤY - 7 TẦNG THANG MÁY - GARA Ô TÔ - NỘI THẤT TIỀN TỶ</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Thông tin chi tiết: 
-Thông tin chi tiết: 📍 Vị trí đắc địa: Trung tâm Ngọc Thụy, hưởng trọn không gian sống thoáng mát, an sinh đỉnh cao.
-📐 Thông số vàng:
-• Diện tích: 48m2.
-• Mặt tiền: 4m (cực kỳ cân đối và hút tài lộc).
-• Kết cấu: Nhà 7 tầng do chính chủ dân xây cực kỳ tâm huyết, móng cột bê tông cốt thép chắc chắn.
-💎 Điểm nhấn không thể bỏ lỡ:
-• Tiện ích vượt trội: Tòa nhà thiết kế thông minh với thang máy nhập khẩu chạy êm ru, gara ô tô rộng rãi ra vào thoải mái ngày đêm.
-• Nội thất xa hoa: Chủ nhà hào phóng tặng lại toàn bộ nội thất cao cấp trị giá hàng tỷ đồng. Không gian sống đẳng cấp, khách mua chỉ việc xách vali về ở ngay mà không cần sắm sửa gì thêm.
-• Giao thông &amp; Tiện ích: Nằm tại vị trí trung tâm, tiện ích bạt ngàn không thiếu thứ gì từ trường học các cấp, chợ truyền thống đến siêu thị. Giao thông kết nối hoàn hảo, di chuyển đi các ngả vô cùng thuận tiện.
-💰 Giá chào: Nhỉnh 12 tỷ (Có thương lượng cho khách thiện chí).
-📕 Pháp lý: Sổ đỏ chính chủ, vuông vắn, sẵn sàng giao dịch ngay.</t>
-        </is>
-      </c>
-      <c r="R23" t="n">
         <v>131180079</v>
       </c>
     </row>
@@ -2295,22 +1739,6 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>21.045307</v>
-      </c>
-      <c r="O24" t="n">
-        <v>105.86899</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>tôi chính chủ bán nhà 5 tầng mới phố cổ quận Long biên</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Tôi chính chủ bán nhà 5tầng xây mới. Nhà lằm vị trí phố cổ quận Long biên.  Diện tích 35m mặt tiền 3m30      Hướng Tây nam  đường trước nhà 4m  nhà cách phố ngọc lâm 100m ngõ vào nhà ô tô đi thoải mái khu dân trí cao tiện ích thuận tiện nhà xây cho con gái ở nên thiết kế đẹp và lắp nội thất xịn</t>
-        </is>
-      </c>
-      <c r="R24" t="n">
         <v>129628407</v>
       </c>
     </row>
@@ -2365,24 +1793,6 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O25" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>NHÀ TÌM CHỦ MỚI</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: HIẾM CÓ KHÓ TÌM – Nhà đẹp trung tâm Việt Hưng, vị trí quá đỉnh!
-    65m², mặt tiền rộng 5m, chỉ cách 1 nhà ra ô tô tránh. Nhà xây 5 tầng đẹp lung linh, công năng đầy đủ, ở sướng miễn bàn. Giá 9 tỷ 2 cực hợp lý khu vực.</t>
-        </is>
-      </c>
-      <c r="R25" t="n">
         <v>132029185</v>
       </c>
     </row>
@@ -2437,28 +1847,6 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O26" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng - thang máy 
-+ Diện tích ; 50m2- MT 5m
-+ Nội thất cơ bản
-+ Đường trước nhà 2,5m- cách 10m ra đường ô tô chạy 
-+ Tiện ích ;nhà gần ngay trường các cấp - chợ - rùi hồ công viên thạch bàn - và khu vực đông dân cư- chỉ mất tầm 10 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
         <v>130458416</v>
       </c>
     </row>
@@ -2513,29 +1901,6 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O27" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng chủ xây kiên cố - thang máy 
-+ Diện tích ; 82m2- MT 4,5m
-+ Hướng đông bắc
-+ Đường trước nhà 12m - vỉa hè đường thông tứ ngả 
-+ Hiện nhà đang cho thuê dòng tiền 30tr/tháng 
-+ Tiện ích ngập tràn ; nhà nằm trên mặt phố lớn của long biên - kinh doanh sầm uất ngày và đêm - nhà lại đối diện TTTM -AEON -Long biên - rùi trường các cấp - và khu vực dân trí cao - mất 5 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên thổ cư long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
         <v>124526487</v>
       </c>
     </row>
@@ -2590,29 +1955,6 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O28" t="n">
-        <v>105.910774</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ VIỆT HƯNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ VIỆT HƯNG LONG BIÊN HÀ NỘI.
-+Biệt thự 4 tầng xây kiên cố
-+ Diện tích ; 230m2- MT 14m 
-+ Nội thất cơ bản 
-+ Hướng đông nam - quanh năm thoáng mát
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả 
-+ Tiện ích ngập tràn ; nhà cạnh vườn hoa công viên - trường quốc tê - hàng xóm Vinhom long biên - và khu vực dân trí cao sinh sống- chỉ mất 10 phút lái xe - là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
         <v>131350225</v>
       </c>
     </row>
@@ -2667,29 +2009,6 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>21.058014</v>
-      </c>
-      <c r="O29" t="n">
-        <v>105.90377</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ VIỆT HƯNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ VIỆT HƯNG LONG BIÊN HÀ NỘI.
-+ Biệt thự 5 tầng ( căn góc )
-+ Diện tích 250m2- MT 20m 
-+ Nhà lắp đặt phun nội thất đẹp 
-+ Hướng đông bắc 
-+ Đường trước nhà 7m vỉa hè đường thông tứ ngả 
-+ Tiện ích ngập tràn ; nhà gần trước quốc tế - rùi TTTM -cạnh hàng xóm Vinhom - và khu vực dân trí cao sinh sống- chỉ mất 10 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
         <v>131336584</v>
       </c>
     </row>
@@ -2744,27 +2063,6 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>21.073374</v>
-      </c>
-      <c r="O30" t="n">
-        <v>105.905464</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>🇻🇳PHẢI NHANH- NGÔ GIA TỰ - 5TẦNG THANG MÁY- 2THOÁNG-92M2-MT4,5M-13TY</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>🏠Nhà Ngô Gia Tự đang trong quá trình hoàn thiện , khoảng 1 tháng nữa là hoàn thành. Chủ nhà KIẾN TRỨC SƯ tự tay thiết kế và thi công rất cẩn thận, ép cọc bê tông chắc chắn 👉 chất lượng miễn bàn.
-🔥Nhà có Ban Công, hai mặt thoáng vĩnh viễn, đằng trước và đằng sau đón không khí và ánh sáng tự nhiên, Vượng khí ngập tràn. Với DT92m2 X5 tầng thang máy +6 phòng ngủ -wc khép kín . Trước nhà sân rất rộng để được gần chục xe máy rất thích hợp cho nhà đông người muốn một không gian sống Rộng Rãi, Riêng Tư,Thoải Mái. Hoặc vừa ở vừa làm Văn phòng hay làm kho hàng khinh doanh online cũng hết Nước Chấm.
-❤️ Nhà cách mặt Phố vài bước chân ,nơi mua sắm thoả thúch , giao thông đi lại vô cùng thuận tiện . Với vị trí ,công năng sử dụng ,diện tích và giá thành, 13tỷ, nhờ Quý Anh, Chị cầm cái máy tính Nhân, Chia thử xem căn nhà này Có Đáng Ra Quyết Đình Ngay Chưa.
-📕 Sổ đỏ vuông đẹp, pháp lý chuẩn rõ ràng 👉 chờ sang tên chủ mới.
-💥 Hỗ trợ ngân hàng lên đến 75% giá trị căn nhà
-☎️ Hãy nhanh tay bấm máy, kết bạn Zalo để được gửi video xem toàn cảnh căn nhà. Mr Tùng dẫn đi xem nhà nhiệt tình , gúp Quý Anh, Chị tìm được những căn nhà ưng ý nhất, đẹp nhất ở quận Long Biên</t>
-        </is>
-      </c>
-      <c r="R30" t="n">
         <v>131932402</v>
       </c>
     </row>
@@ -2819,33 +2117,6 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>21.027077</v>
-      </c>
-      <c r="O31" t="n">
-        <v>105.923355</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ 5 TẦNG THANG MÁY 44M² Ô TÔ ĐỖ CỬA THẠCH BÀN, LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>💥💥 NHÀ THẠCH BÀN - 5 TẦNG THANG MÁY - Ô TÔ NHỎ ĐỖ CỬA 💥💥
-🏡 Diện tích: 44m²
-🏗️ Kết cấu: 5 tầng thang máy xịn, xây chắc chắn
-🚗 Ô tô nhỏ đỗ cửa, ngõ thông thoáng
-📍 Vị trí trung tâm Thạch Bàn:
-Cạnh chợ Đồng Dinh, gần Hồ Ben, hồ điều hòa 
-Gần trường học các cấp, tiện ích ngập tràn
-Khu dân trí cao, an ninh tốt
-🛋️ Thiết kế hiện đại, công năng tối ưu, ở cực thích
-💰 Giá 9,x tỷ (có thương lượng)
-📕 Sổ đỏ chính chủ, sẵn sàng giao dịch
-📞 Alo Em Thiêm xem nhà ngay hôm nay</t>
-        </is>
-      </c>
-      <c r="R31" t="n">
         <v>131442361</v>
       </c>
     </row>
@@ -2900,25 +2171,6 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>21.043814</v>
-      </c>
-      <c r="O32" t="n">
-        <v>105.872314</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP TRUNG TÂM VIỆT HƯNG</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: NHÀ ĐẸP TRUNG TÂM VIỆT HƯNG.
-Thiết kế 5 tầng, mặt tiền 5m
-Gần tiểu học việt hưng, cầu Trần Hưng Đạo,Big C, bv Hồng Ngọc ….</t>
-        </is>
-      </c>
-      <c r="R32" t="n">
         <v>132000792</v>
       </c>
     </row>
@@ -2973,30 +2225,6 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O33" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>🔥 CỰC HIẾM  BÁN ĐẤT TẶNG NHÀ 4 TẦNG - TRUNG TÂM NGỌC LÂM - Ở NGAY</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 CỰC HIẾM  BÁN ĐẤT TẶNG NHÀ 4 TẦNG - TRUNG TÂM NGỌC LÂM - Ở NGAY - 5.6 TỶ 🔥
-• Vị trí vàng: Ngõ nông, thông tứ tung (Ngọc Lâm - Nguyễn Văn Cừ). Vài bước chân ra phố, gần trường Ái Mộ.
-• Tặng kèm: Toàn bộ nội thất, khách chỉ việc xách vali về ở.
-• Thiết kế: 3 tầng + 1 tum kiên cố, công năng tối ưu, sân phơi cực thoáng.
-• Điểm cộng: Ngõ rộng, ô tô đỗ gần (trường Ái Mộ), khu dân trí cao, tiện ích không thiếu thứ gì.
-• Pháp lý: Sổ đỏ chính chủ, sẵn sàng sang tên.
-💰 Giá chào: 5.6 Tỷ (Có thương lượng)
-☎️ Liên hệ xem nhà ngay: ***</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
         <v>132022443</v>
       </c>
     </row>
@@ -3051,28 +2279,6 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>21.051487</v>
-      </c>
-      <c r="O34" t="n">
-        <v>105.89713</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>🔥 NGỘP THỞ – GIÁ SỐC - TẶNG NHÀ 4 TẦNG- NGÕ THÔNG Ô TÔ</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>🔥 NGỘP THỞ – GIÁ SỐC - TẶNG NHÀ 4 TẦNG- NGÕ THÔNG Ô TÔ
-Chủ cần bán gấp nhà 45m² – nhỉnh 8 tỷ
-✔ Ngõ thông Ô TÔ , Trung tâm Long Biên
-✔ Nhà 4 tầng xây chắc chắn, ở luôn
-✔ Ngay sát Big C, thông Ngô Gia Tự, Vinhome Reversite, đi cầu Trần Hưng Đạo
-📞 Liên hệ ngay: em Hằng xem vị trí ạ
-#nhadatlongbien #banhadep #ngothong #nhaxinh #batdongsan #giasoc #nhapho #dautu #nhadatgiare</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
         <v>132022294</v>
       </c>
     </row>
@@ -3127,30 +2333,6 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O35" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>💥MẶT PHỐ NGỌC LÂM – KINH DOANH ĐỈNH – TẶNG NHÀ 5 TẦNG- GIÁ CHỈ 9 TỶ</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>💥MẶT PHỐ NGỌC LÂM – KINH DOANH ĐỈNH – TẶNG NHÀ 5 TẦNG- GIÁ CHỈ  9 T.Ỷ
-* Vị trí: Phố Ngọc Lâm – tuyến phố kinh doanh sầm uất bậc nhất
-* Ô tô tránh thoải mái
-* Thông phố : Hồng Tiến – Nguyễn Sơn – Nguyễn Văn Cừ - Hoàng Như Tiếp - Bồ Đề
-* Phù hợp: Kinh doanh, spa, văn phòng, cho thuê dòng tiền
-Giá chỉ nhỉnh 9 tỷ (cực hiếm trong phân khúc mặt phố)
-Liên hệ ngay em Hằng để xem nhà và chốt sớm
-⸻
-#MatPhoNgocLam #NhaDepLongBien #BatDongSanHaNoi #KinhDoanhDinh #LongBiên #NgọcLâm #Bồđề #NguyễnSơn #Hồngtiến #Hoàngnhưtiếp</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
         <v>132021992</v>
       </c>
     </row>
@@ -3205,22 +2387,6 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>21.032537</v>
-      </c>
-      <c r="O36" t="n">
-        <v>105.90829</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>nhà chính chủ</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>chính chủ bán nhà 30,6m2 nhà mới xây khách chỉ việc sách vali vào ở . nhà ở khu dân chí cao tiện ích ngập tràn rất gần trường cấp 1-2-3 thạch bàn gần chợ đồng dinh ngỗ thông các ngả , cách 500m ra đường cao tốc 5B và 5A cách eon long biên 1,5km nn lên rất tiện cho việc đi lại sang phố</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
         <v>130571107</v>
       </c>
     </row>
@@ -3275,35 +2441,6 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O37" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>🚨 HÀNG HIẾM: BIỆT THỰ LIỀN KỀ BÌNH MINH GARDEN 79M2 x 4 TẦNG - 23 TỶ</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>📍 Vị trí: Khu đô thị Bình Minh Garden – Đức Giang, Long Biên.
-💰 Giá bán: 23 Tỷ (Có thương lượng cho khách thiện chí).
-📏 Diện tích: 79m2 | Kết cấu: 4 Tầng + Thang máy xịn.
-🌟 ĐIỂM NHẤN TRIỆU ĐÔ - HIẾM NHÀ BÁN:
-Vị trí đắc địa nhất khu: Tọa lạc tại tọa độ vàng của dự án Bình Minh Garden, cực hiếm nhà bán lại.
-Hạ tầng hoàn hảo: Đường trước nhà rộng rãi, hai ô tô tránh nhau thoải mái. Vỉa hè thênh thang, để xe máy, ô tô cho khách cực kỳ thuận tiện.
-Tiềm năng kinh doanh đỉnh cao: Lợi thế tuyệt đối với View trực diện khu chung cư đông đúc, lượng cư dân và khách vãng lai qua lại tấp nập. Vị trí "hái ra tiền", cực kỳ phù hợp để mở Showroom, Spa làm đẹp, Phòng khám, Trụ sở văn phòng, Nhà hàng...
-🏠 THIẾT KẾ HIỆN ĐẠI – TỐI ƯU CÔNG NĂNG:
-Nhà xây 4 tầng kiên cố, trang bị Thang máy xịn sò, không gian cực kỳ thoáng đãng với hai mặt thoáng trước sau:
-Tầng 1 &amp; 2: Thiết kế thông sàn hoàn toàn – Tối ưu hóa không gian, dễ dàng setup và bài trí cho mọi mô hình kinh doanh.
-Tầng 3 &amp; 4: Mỗi tầng gồm 2 phòng ngủ + WC riêng biệt – Rất thích hợp cho gia chủ vừa ở vừa kết hợp kinh doanh hoặc cho thuê nguyên căn.
-📜 PHÁP LÝ AN TOÀN:
-Sổ đỏ phân lô vuông đét, chính chủ, pháp lý chuẩn mực.
-Sẵn sàng giao dịch sang tên ngay. Chủ nhà vô cùng thiện chí bán.</t>
-        </is>
-      </c>
-      <c r="R37" t="n">
         <v>131403129</v>
       </c>
     </row>
@@ -3358,32 +2495,6 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O38" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ LONG BIÊN 31M 5T FULL FULL ĐỒ CHỈ 5.65 TỶ . ẢNH THẬT KO LỖI GÌ</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>🏠🏠 BÁN NHÀ LONG BIÊN 30M 5 TẦNG FULL ĐỒ Ở LUÔN, NGÕ NÔNG GIÁ BÁN NHANH 5.65 TỶ CTL . ẢNH THẬT 100% 
-🍀🍀 DT : 30M vuông vắn , ngõ 2,3m rộng , nông 50m ra oto tránh đỗ dừng ngày đêm .
-​
-​🏤🏤 Nhà xây dựng 5 tầng hiện đại chắc chắn Thiết kế gồm :
-​+Tầng 1: khách bếp, vs 
-​+Tầng 2,3,4: 1 ngủ rộng + vs 
-​+Tầng 5: phòng thờ, sân phơi 
-Nhà đầy đủ công năng,  full nội thất sẵn ở luôn . 
-📕 Cam kết sổ đỏ chính chủ,  Pháp lý chuẩn , không tranh chấp, không quy hoach , k lỗi phong thủy - sẵn sàng giao dịch. 
-- 🍁🌹 Giá bán nhanh 5.65 tỷ bao thuế phí sang tên , có tl . Hỗ trợ vay vốn ngân hàng 70%-30 năm . 
-☎️☎️ LH: Em Thơm  xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
         <v>132017213</v>
       </c>
     </row>
@@ -3438,31 +2549,6 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>21.022837</v>
-      </c>
-      <c r="O39" t="n">
-        <v>105.88859</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ LONG BIÊN BÁT KHỐI 32M 5T CHỈ 10M RA OTO TẢI CHỈ 5,95 TỶ</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ LONG BIÊN BÁT KHỐI 31M 5 TẦNG MỚI ĐẸP CHỈ 5,95 TỶ CTL . SỔ ĐẤT ĐẸP K LỖI- K QUY HOẠCH , OTO VÀO CÁCH 1 NHÀ . 
-Dt: 31m mặt tiền = hậu vuông vắn, đường 2,3m cách đúng 1 nhà ra oto tải vào . 
-Nhà xây dựng 5 tầng hiện đại đầy đủ công năng : 
-Tầng 1 : khách , bếp , vs 
-Tầng 2, 3, 4 : Ngủ + vs 
-Tầng 5: Phòng Thở , sân phơi 
-Nhà mới tinh đầy đủ công năng cho gia đình vợ chồng con cái  ở luôn . Vị Trí khu dân cư đông, đường xá rộng rãi thuận tiện đi lại các ngả , bán kính 300m đầy đủ chợ- trương học các cấp , 5 phút qua TTTM AEN MALL . 
-CAM KẾT SỔ ĐỎ CHÍNH CHỦ , PHÁP LÝ CHUẨN, KHÔNG TRANH CHẤP, K QUY HOẠCH , MUA BÁN NGAY . 
-Gía mong muốn : 5.95 tỷ ctl, bao thuế phí sang tên , Hỗ trợ vay vốn ngân hàng 70%-20 năm . 
-LH : Em Thơm  xem nhà miễn phí .</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
         <v>132017121</v>
       </c>
     </row>
@@ -3517,33 +2603,6 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O40" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ LONG BIÊN 50M 6T NGÕ 6M XE TẢI RA VÀO, THANG MÁY- NỘI THẤT XỊN</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>🟠✅MỞ BÁN NHÀ LONG BIÊN 50M 6 TẦNG THANG MÁY- NGÕ 5M- ÔTÔ 7 CHỖ VÀO- ĐANG HOÀN THIỆN- GIÁ ƯU ĐÃI HƠN 11 TỶ
-DT : 50m mt 5,2m vuông vắn , ngõ 5m thoáng rộng xe tải ra vào thoải mái 
-🏠🚘Diện tích: 50m xây 6 tầng thang máy, nội thất cơ bản, điều hòa âm Trần, thông sàn. 
-+Tầng 1: gara ô tô 
-+Tầng 2: Khách bếp, wc
-+Tầng 3: Có 2 ngủ vệ sinh 
-+Tầng 4,5: phòng Ngủ master + wc khép kín
-+Tầng 6: phòng Thờ, sân phơi.
-🌟Nhà chính chủ hàng f0, giá ưu đãi cho người mua sớm. phù hợp mua đầu tư, giữ tiền...
-CAM KẾT KHÔNG QUY HOẠCH . K TRANH CHẤP. SỔ ĐỎ PHÁP LÝ CHUẨN MUA BAN NGAY . 
-Hỗ trợ vay vốn ngân hàng 70%-20 năm thủ tục nhanh gọn 
-☎️LH : Em Thơm để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R40" t="n">
         <v>132017063</v>
       </c>
     </row>
@@ -3598,31 +2657,6 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>21.012106</v>
-      </c>
-      <c r="O41" t="n">
-        <v>105.91772</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ CỔ LINH THẠCH BÀN TRONG ẢNH OTO ĐỖ CỬA 32M 5T ~ 6 TỶ CTL MẠNH</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Bán nhà Thạch Bàn, long biên 32m2-5 tầng ngõ Ô TÔ  giá hơn 6 tỷ (có thương lượng)
-Diện tích:  32m2 mặt tiền 4m vuông vắn, đường rộng 4m cực thoáng. 
-- Nhà xây mới 5 tầng 3 phòng ngủ 4 vệ sinh. 
-- Tầng 1 phòng khách và bếp
-- Tầng 2,3,4 mỗi tầng 1 ngủ và vệ sinh 
-- Tầng 5 sân phơi, phòng thờ 
-Nhà ở rất lộc, chủ nhà đã chuyển sang ở căn to hơn.
-Sổ đỏ chính chủ, không quy hoạch , không tranh chấp, mua bán ngay.
-Giá mong muốn : 6.98 tỷ ctl thiện chí , khách ưng là bán . Hỗ trợ vay vốn ngân hàng 70%-20 năm 
-LH : Em Thơm để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R41" t="n">
         <v>132016917</v>
       </c>
     </row>
@@ -3677,26 +2711,6 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>21.048956</v>
-      </c>
-      <c r="O42" t="n">
-        <v>105.886284</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Nhà Đẹp Nguyễn Văn Cừ- Ở Ngay</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>11 tỷ ..  SIÊU PHẨM  -6 NGỦ - Ô TÔ ĐỖ CỬA - TRUNG TÂM QUẬN LONG BIÊN - NỘI THẤT
-Xây 5 tầng .DT 58 
-Nguyễn Văn Cừ Nhà vị trí tuyệt đẹp  ngay phố. -🏠Khu trung tâm tiện ích đầy đủ,  trường học các cấp, gần bệnh viên Tâm Anh, trường wellspring nổi tiếng, các ngân hàng, dịch vụ sát nách 
-🏠 Nhà đẹp không tỳ vết, Dân xây chắc chắn rất tâm huyết, tỉ mỉ từng chi tiết, thoáng trước, cạnh nhà, sau nhà, nhà tạo nên sự thoáng mát, không gian mở ánh sáng ngập tràn các phòng. Thiết kế hợp lý, đầy đủ công năng.
- + Rất thích hợp cho thuê căn hộ mini hoặc gia đình nhiều thế hệ ở khu vực tên tĩnh thoáng mát. + Tầng 1: Sân, Phòng khách + bếp, WC, cầu thang Góc.+ Tầng 2+3+4: Mỗi tầng 2 Phòng ngủ rộng + WC khép kín.+ Tầng 5 : phòng thờ + bếp BBQ, sân. 📕📕📕Sổ đỏ chính chủ đẹp, pháp lý rõ ràng, sổ ngay tại nhà sẵn sàng giao dịch</t>
-        </is>
-      </c>
-      <c r="R42" t="n">
         <v>131974716</v>
       </c>
     </row>
@@ -3751,26 +2765,6 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>21.022837</v>
-      </c>
-      <c r="O43" t="n">
-        <v>105.88859</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ THẠCH BÀN 35M 5 TẦNG GẦN KĐT GARDEN CITY 6,X TỶ</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>🟠✅BÁN NHÀ THẠCH BÀN 35M 5 TẦNG GẦN KĐT GARDEN CITY- 20M RA ĐƯỜNG THÔNG Ô TÔ- FULL NỘI THẤT- GIÁ 6,X TỶ
-🏠Nhà 35m xây 5 tầng hiện đại: Thiết kế đầy đủ 3 ngủ, 4 vệ sinh, phòng thờ sân phơi.
-🔶Gần khu đô thị Garden City, chỉ cách 20m ra đường thông Ô tô, Khu vực đang quy hoạch đường giao thông rất đẹp.
-📕Sổ đỏ chính chủ, ko quy hoạch, ngân hàng hỗ trợ vay vốn 70%
-☎️LH Em Hiệp để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R43" t="n">
         <v>128574981</v>
       </c>
     </row>
@@ -3825,29 +2819,6 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>21.026669</v>
-      </c>
-      <c r="O44" t="n">
-        <v>105.89605</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ PHỐ ĐÀM QUANG TRUNG 38M 5 TẦNG- CÓ SÂN RIÊNG ĐỂ XE- GIÁ 6,6 TỶ</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ PHỐ ĐÀM QUANG TRUNG NGAY CẦU VĨNH TUY 38M 5 TẦNG- CÓ SÂN RIÊNG ĐỂ XE- GIÁ 6,6 TỶ (CÓ THƯƠNG LƯỢNG)
-+ LH ***
-Diện tích 38m, nhà xây 33m 5 tầng còn lại làm sân. có cổng riêng.
-Nhà thiết kế full nội thất đẹp, gồm 3 ngủ, 4 vệ sinh, phòng thờ sân phơi đầy đủ.
-Vị trí trung tâm cách Aeon Mall chỉ 300m, ngay chân cầu Vĩnh Tuy sang phố cực gần.
-+ Sổ đỏ chính chủ, cam kết không quy hoạch.
-+ Giá cần bán nhanh 6,6 tỷ (có thương lượng)
-LH *** Em Hiệp để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R44" t="n">
         <v>131512322</v>
       </c>
     </row>
@@ -3902,28 +2873,6 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>21.025381</v>
-      </c>
-      <c r="O45" t="n">
-        <v>105.895256</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>NHÀ PHỐ TRẠM NGAY CẠNH AEON MALL 40M 5 TẦNG GIÁ HƠN 7 TỶ</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>🟠✅CẦN BÁN NHÀ PHỐ TRẠM THÔNG ĐÀM QUANG TRUNG NGAY CẠNH AEON MALL 40M 5 TẦNG GIÁ HƠN 7 TỶ
-☎️LH ***
-🕌Tổng Diện Tích Sử Dụng Riêng 40m 5 Tầng 3 phòng ngủ 4 vệ sinh và có sân để xe riêng biệt.
-🔶Vị trí ngập tràn tiện ích trường học các cấp, công viên, chợ, TTTM Aeon Mall... Gần cầu Vĩnh Tuy, sang phố chỉ mất 5 phút
-💰Giá hơn 7 tỷ (có thương lượng), sổ đỏ đầy đủ cam kết ko quy hoạch
-☎️LH *** Em Hiệp để đi xem nhà miễn phí
-#photram #muanhalongbien #AeonMall</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
         <v>131448567</v>
       </c>
     </row>
@@ -3978,31 +2927,6 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O46" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ THẠCH BÀN 40M 5 TẦNG CÓ SÂN CỔNG RIÊNG -NHỈNH 7 TỶ</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>✅BÁN CĂN NHÀ THẠCH BÀN 40M 5 TẦNG- SÂN CỔNG RIÊNG BIỆT- CÁCH VÀI BƯỚC RA ĐƯỜNG Ô TÔ TRÁNH- GIÁ NHỈNH 7 TỶ
-🔶Diện tích:40m xây 5 tầng, có sân cổng riêng biệt để xe máy bên ngoài.
-- Ngõ rộng 2,5m chỉ cách vài bước ra đường thông Ô tô dừng đỗ ngày đêm.
-- Thiết kế đầy đủ công năng sử dụng:
-+ Tầng 1: Sân để xe, phòng khách, bếp wc
-+ Tầng 2,3,4: Mỗi tầng 1 ngủ + wc khép kín
-+ Tâng 5: Phòng thờ, sân phơi
-Vị trí trung tâm Thạch Bàn, hàng xóm của KĐT Garden City, xung quanh gần nhà văn hoá, trường học, chợ...khu dân cư sầm uất
-+ Sổ đỏ chính chủ, cam kết không bị quy hoạch.
-☎️LH Em Hiệp để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R46" t="n">
         <v>129293878</v>
       </c>
     </row>
@@ -4057,29 +2981,6 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>21.05286</v>
-      </c>
-      <c r="O47" t="n">
-        <v>105.92033</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>nhà Đẹp Phúc Lợi . Long Biên. Giá Bán Nhanh</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Giá Tốt. Nhà Đẹp Phúc Lợi. Long Biên.3 ngủ . 5.x tỷ
-Dt 30m2* 5 tầng. 3 ngủ . Tậng nội thất 
-Công năng sử dụng đầy đủ 
-Khu vực tiện ích. Giao thông thuận 
-Sang Phố Cổ Hà Nội 15 phút 
-Zá 5.x tỷ ( CTL )
-Lh  TT xem nhà . Tư vấn không mất phí</t>
-        </is>
-      </c>
-      <c r="R47" t="n">
         <v>132012859</v>
       </c>
     </row>
@@ -4134,30 +3035,6 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O48" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>NHÀ Q.LONG BIÊN–DÂN XÂY- OTO ĐỖ-KINH DOANH-DIỆN TÍCH LỚN- GIÁ BÌNH DÂN</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chỉ cần làm thủ tục nhập trạch và đèo đồ dùng cá nhân đến ở ngôi nhà được kiến trúc sư thiết kế và dân tự xây chất lượng cao, ở phường Việt Hưng- Trung tâm quận Long Biên.
-Oto đỗ cửa và đường oto thông ra các phố lớn như phố Việt Hưng, phố Kim Quan Thượng, phố Đào Đình Luyện. Giáp với WINHOMES RIVER SIDES. Thích hợp vừa ở vừa Kinh doanh. 
-Trên địa bàn đầy đủ hệ thống tiện ích dân sinh gồm chợ truyền thống và hệ thống siêu thị . Có 07 trường học phổ thông liên cấp công lập đạt chuẩn Quốc gia từ mầm non, tiểu học đến THCS. Gần bệnh viện đa khoa Đức Giang và bệnh viện phụ sản Hà Nội cùng đội ngũ Bác sỹ chuyên gia đầu ngành và trang thiết bị y tế hiện đại – là những bệnh viện được xếp hạng I của thành phố Hà Nội. Được hưởng các tiện ích chung của Khu đô thị Việt Hưng hiện đại bậc nhất miền Bắc và đô thị WINHOMES RIVER SIDES. Tiện ra công viên Long Biên, đáp ứng yêu cầu thể thao, vui chơi. 
-Hàng xóm dân trí cao, an ninh cực tốt. 
-Sổ đỏ đất ở lâu dài. 
-GIÓ HÃY NÓI RẰNG GIÁ BÌNH DÂN / GIÓ HÃY NÓI RẰNG NHÀ DÂN XÂY / GIÓ HÃY NÓI RẰNG TÔI TẶNG NHÀ CHO EM / GIÓ HÃY NÓI RẰNG TÔI YÊU EM, MÃI KHÔNG THÔI: Chỉ loanh quanh 8 tỷ (Chủ nhà tuổi trẻ được hưởng thừa kế, nay lấy chồng, muốn bán nhà để theo chồng vào Sài Gòn lập nghiệp, thùy mị, nết na, trọng tình cảm, CƠ CHẾ THOÁNG, thiện chí thương lượng đến cùng để bên BÁN- MUA cùng WIN-WIN)
-Đừng do dự, chần chừ, hãy liên hệ Mr. THU số Điện thoại hoặc Zalo ***
-Kính chúc Bạn sức khỏe, thành đạt  và sớm sở hữu nhà !
-</t>
-        </is>
-      </c>
-      <c r="R48" t="n">
         <v>132010359</v>
       </c>
     </row>
@@ -4212,27 +3089,6 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>21.0472</v>
-      </c>
-      <c r="O49" t="n">
-        <v>105.91091</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>🏘️BÁN NHÀ PHÚC ĐỒNG - 54M2 - 6 TẦNG THANG MÁY💥💥</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: ✅ Vị trí: Trung tâm Phúc Đồng, sát Hồ Sài Đồng, 500m ra Aeon Mall.
-✅ Thiết kế: 54m2 x 6 tầng Thang máy, Full nội thất xịn.
-✅ Trạng thái: Nhà mới koong, xách vali về ở ngay.
-✅ Pháp lý: Sổ đỏ phân lô, sẵn sàng giao dịch.
-📞 Lh em Đạt: ***</t>
-        </is>
-      </c>
-      <c r="R49" t="n">
         <v>131871372</v>
       </c>
     </row>
@@ -4287,30 +3143,6 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>21.043814</v>
-      </c>
-      <c r="O50" t="n">
-        <v>105.872314</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>🏠 7 TẦNG THANG MÁY - NGUYỄN VĂN CỪ - MẶT TIỀN 6M</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: ✅ 7 TẦNG THANG MÁY - NGUYỄN VĂN CỪ
-✅ Mặt tiền 6m: Cực hiếm, căn góc thoáng sáng.
-✅ Vị trí: 5 phút sang Phố Cổ, gần Big C, BV Tâm Anh.
-✅ Tiện ích: Ô tô đỗ cửa, đi bộ ra trường điểm Gia Thụy.
-✅ Thiết kế: 55m² x 7 tầng, 4 PN Master, full nội thất.
-✅ Pháp lý: Sổ nở hậu, sẵn sàng giao dịch.
-💰 Giá: Nhỉnh 14 tỷ (Thương lượng).
-📞 Liên hệ Em Đạt: ***.</t>
-        </is>
-      </c>
-      <c r="R50" t="n">
         <v>131882015</v>
       </c>
     </row>
@@ -4365,33 +3197,6 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O51" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>🔥 SIÊU HIẾM MẶT TIỀN 8.5M - LÔ GÓC - THANG MÁY - NHÀ DÂN XÂY 🔥</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 SIÊU HIẾM MẶT TIỀN 8.5M - LÔ GÓC - THANG MÁY - NHÀ DÂN XÂY 🔥 
-💎 Mặt tiền: 8.5m cực hiếm (diện tích 65m²), nhà bề thế như biệt thự mini.
-📐 Thông số: Lô góc 2 mặt thoáng vĩnh viễn, phòng nào cũng ngập tràn ánh sáng tự nhiên. 
-💰 Giá trị: Chỉ hơn 200tr/m² cho một căn nhà hội tụ đủ: Thang máy - Lô góc - Mặt tiền khủng. Mức giá cực kỳ cạnh tranh tại khu vực!
-🏗️ Thiết kế: Nhà dân tự xây tâm huyết, kết cấu chắc chắn, thang máy nhập khẩu chạy êm ru.
-🛋️ Nội thất: Tặng lại toàn bộ đồ đạc cao cấp (Điều hòa, tủ lạnh, máy giặt, giường tủ...). Khách chỉ việc xách vali về ở.
-🏠 Công năng: 4 tầng với 5 phòng ngủ khép kín, phòng thờ và sân phơi rộng rãi.
-📍 Vị trí: Ngõ nông, gần đường ô tô, khu dân trí cao, an ninh tuyệt đối.
-📜 Pháp lý: Sổ đỏ vuông đẹp, sẵn sàng sang tên ngay.
-⚠️ Lưu ý: Thông số mặt tiền 8.5m và mức giá này là "hàng hiếm" có 1-0-2. Anh chị chậm chân là mất cơ hội!
-📞 Liên hệ em Đạt xem nhà ngay: ***</t>
-        </is>
-      </c>
-      <c r="R51" t="n">
         <v>131423027</v>
       </c>
     </row>
@@ -4446,36 +3251,6 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>21.046835</v>
-      </c>
-      <c r="O52" t="n">
-        <v>105.8782</v>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>💎 NGỌC THỤY - Ô TÔ THÔNG - 5 PHÚT SANG PHỐ - DÂN XÂY CHẮC CHẮN 💎</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💎 NGỌC THỤY - Ô TÔ THÔNG - 5 PHÚT SANG PHỐ - DÂN XÂY CHẮC CHẮN 💎
-📍 VỊ TRÍ VÀNG - TRUNG TÂM NGỌC THỤY:
-• Sát vách Mipec Riverside &amp; Cầu Long Biên. 5 phút sang Phố Cổ.
-• Đường trước nhà Ô TÔ THÔNG 2 ĐẦU, vài bước ra chợ, trường quốc tế Việt Pháp.
-🏠 THIẾT KẾ &amp; TIỀM NĂNG:
-• Nhà 5 tầng dân xây khung cột cực chắc (Có gác lửng hiện đại).
-• Đủ công năng: Bếp, khách, 2-3 phòng ngủ khép kín, phòng thờ, sân phơi.
-• Tiềm năng: Dễ dàng cải tạo thêm phòng hoặc đập đi xây mới tòa Building thang máy cực đỉnh.
-⚖️ PHÁP LÝ &amp; GIÁ CHỐT:
-• Sổ đỏ vuông đét, chính chủ, sẵn sàng giao dịch ngay.
-• Chủ nhà cực thiện chí — Sẵn sàng gia lộc sâu cho khách chốt nhanh trong tháng.
-💰 GIÁ ĐẦU TƯ CỰC TỐT - ALO LÀ MUA ĐƯỢC
-📞 Liên hệ em Đạt xem nhà 24/7:
-*** / ***</t>
-        </is>
-      </c>
-      <c r="R52" t="n">
         <v>131545147</v>
       </c>
     </row>
@@ -4530,32 +3305,6 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O53" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>💎 NGUYỄN VĂN CỪ - 1 NHÀ RA Ô TÔ - 65M2 RỘNG RÃI 💎</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💎 NGUYỄN VĂN CỪ - 1 NHÀ RA Ô TÔ - 65M2 RỘNG RÃI 💎
-📍 Vị trí: Trung tâm Nguyễn Văn Cừ, 3 phút sang Phố Cổ. Ngõ thông, cách đúng 1 nhà ra đường ô tô, giao thông cực đỉnh.
-✅ Thông số:
-• Diện tích: 65m² x 4 tầng (Chủ tự xây tâm huyết, cực chắc chắn).
-• Mặt tiền: 4m (Thông số vàng, thoáng sáng tự nhiên).
-• Công năng: Đầy đủ phòng ngủ, phòng khách, bếp, sân phơi rộng.
-🌟 Tiện ích: Gần Big C, BV Tâm Anh, trường Quốc tế. Khu dân trí cao, an ninh tuyệt đối.
-⚖️ Pháp lý: Sổ đỏ chính chủ, vuông đẹp, sẵn sàng giao dịch.
-💰 Giá: (Anh điền giá tại đây)
-📞 Liên hệ xem nhà: *** (Hỗ trợ 24/7)</t>
-        </is>
-      </c>
-      <c r="R53" t="n">
         <v>131723078</v>
       </c>
     </row>
@@ -4610,27 +3359,6 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>21.054022</v>
-      </c>
-      <c r="O54" t="n">
-        <v>105.88715</v>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Nhà diện tích rộng,ở ngay, gi.á rẻ 90m2x3T, 5.9tỷ, phố Nguyễn Văn Cừ</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Nhà diện tích rộng gi.á rẻ , ở ngay, 90m2x3T chỉ 5.9 tỷ, phố Nguyễn Văn Cừ
-Nếu bạn đã chán cảnh sống chật trội, lúc nào cũng tắc đường, không khí ô nhiễm bên nội đô thì chỉ cần qua 1 chiếc cầu thôi, bạn sẽ tìm được ngôi nhà diện tích rộng, ô tô vào nhà
-Căn nhà dân xây 90m2 x tầng chắc chắn, thuộc đường Nguyễn Văn Cừ , gần bigC, phố Ngô Gia Tự, thẳng đường đi cầu Chương Dương, 10 phút sang Hồ Gươm. Giao thông vô cùng thuận lợi, ngõ ô tô nông.  
-Chuyên BĐS khu vực Phường Bồ Đề, Phường Việt Hưng, Phường Phúc Lợi, Phường Long Biên ( quận Long Biên cũ)- TP. Hà Nội
-Ngọc Thụy- Thượng Thanh- Đức Giang- Thanh Am- Nguyễn Văn Cừ-Ngọc Lâm- Phú Viên- Ngô Gia Tự- Nguyễn Văn Linh- Tân Thụy- Mai Phúc- Chu Huy Mân- Kim Quan- Kim Quan Thượng- Việt Hưng- Ái Mộ-  Bồ Đề- Hồng Tiến- Hoàng Như Tiếp- Bắc Cầu- Bắc Biên
-#batdongsan#nhadep#nhapho #dautu#datthocu#dautubatdongsan#ngooto</t>
-        </is>
-      </c>
-      <c r="R54" t="n">
         <v>131889253</v>
       </c>
     </row>
@@ -4685,28 +3413,6 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>21.06651</v>
-      </c>
-      <c r="O55" t="n">
-        <v>105.89193</v>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>đẹp</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>A chị muốn thay đổi công việc . muốn nhượng lại căn nhà 
-Xây 5 tầng . 3 ngủ 
-Lô góc . DT 56m2 ạ 
-Xe ô tô để cạnh nhà ngày đêm luôn 
-Nhà việt Hưng . Long Biên Hà Nội .
-2 bước ra ô tô tránh . Ngay BigC long biên . 
-***</t>
-        </is>
-      </c>
-      <c r="R55" t="n">
         <v>131958854</v>
       </c>
     </row>
@@ -4761,29 +3467,6 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O56" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>🔥 CHỈ HƠN 12 TỶ - CÓ NGAY NHÀ 7 TẦNG THANG MÁY TẠI AEON LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 CHỈ HƠN 12 TỶ - CÓ NGAY NHÀ 7 TẦNG THANG MÁY TẠI AEON LONG BIÊN
-✅ Thông số vàng: 55m² x 7 tầng, MT 4m, Nở hậu đẹp.
-✅ Vị trí: Trung tâm Long Biên, gần cầu Vĩnh Tuy, trường học, TTTM.
-✅ Thiết kế: Hiện đại, nội thất cao cấp. Gara ô tô, 3 Master khép kín, khách + bếp tầng 6 cực thoáng.
-✅ Hướng: Đông Nam (2 mặt ngõ lấy sáng tự nhiên).
-🧧 Nhà mới tinh, sẵn sàng bàn giao đón Tết 2026!
-☎️ LH em Đạt xem nhà ngay: ***</t>
-        </is>
-      </c>
-      <c r="R56" t="n">
         <v>131471429</v>
       </c>
     </row>
@@ -4838,33 +3521,6 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>21.046711</v>
-      </c>
-      <c r="O57" t="n">
-        <v>105.87843</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>💎 SIÊU PHẨM LÔ GÓC NGỌC LÂM - 78M2 - 6 TẦNG THANG MÁY - KINH DOANH ĐỈN</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: ✅ THÔNG SỐ VÀNG: Diện tích 78m2, mặt tiền rộng, LÔ GÓC cực thoáng. Nhà xây mới 6 tầng, thiết kế hiện đại, thang máy chạy êm ru.
-✅ VỊ TRÍ ĐẮC ĐỊA:
-• Ngõ thông, ô tô tránh, vài bước chân ra Hồ công viên Ngọc Lâm.
-• Thuộc khu vực sầm uất nhất phố Ngọc Lâm - Nguyễn Sơn, dân trí cao, an ninh tuyệt đối.
-• Gần Bến xe Gia Lâm, di chuyển sang Phố Cổ Hoàn Kiếm chỉ mất "phút mốt".
-✅ CÔNG NĂNG ĐA DẠNG:
-• Thiết kế 6 phòng ngủ rộng, gara 2 ô tô.
-• Phù hợp: Ở đẳng cấp, làm Văn phòng Công ty, Spa, hoặc khai thác DÒNG TIỀN Homestay cực tốt (Khu vực này cực hiếm nhà bán).
-✅ PHÁP LÝ: Sổ đỏ vuông đẹp, sẵn sàng giao dịch.
-💰 Giá: [Anh điền giá] (Có thương lượng cho khách thiện chí).
-☎️ LH chính chủ em Đạt: *** / *** (Xem nhà 24/7).</t>
-        </is>
-      </c>
-      <c r="R57" t="n">
         <v>131455857</v>
       </c>
     </row>
@@ -4919,23 +3575,6 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>21.030355</v>
-      </c>
-      <c r="O58" t="n">
-        <v>105.88742</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Nhà mới 65m 5 tầng Mtien 8m thang máy</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Bán nhà ngõ Tư Đình 55m, 5 tầng, MT 8m , ngõ ô tô, thang máy, 17,9 tỷ, nhà mới. LH ngay Bích Thuỷ</t>
-        </is>
-      </c>
-      <c r="R58" t="n">
         <v>132004626</v>
       </c>
     </row>
@@ -4990,38 +3629,6 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>21.044104</v>
-      </c>
-      <c r="O59" t="n">
-        <v>105.87255</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>SIÊU PHẨM HỒNG TIẾN 127m x 7 TẦNG–MẶT TIỀN 12M–GIÁ CHỈ NHỈNH 220TR/1M</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Cơ hội hiếm có để sở hữu "viên kim cương" tại trung tâm Quận Long Biên. Căn nhà do bà cô ruột của em trực tiếp gửi gắm, xây dựng cực kỳ tâm huyết nhưng nay có việc cần chuyển nhượng gấp với mức giá siêu đầu tư.
-​✨ Thông Số Vàng – Giá "Hạt Dẻ"
-​Diện tích: 127 m^2 (Sổ đỏ chính chủ, pháp lý sạch).
-​Giá chào: Nhỉnh 220 triệu/m^2 (Tổng 29 tỷ - Mức giá cực tốt cho một căn nhà 7 tầng thang máy, mặt tiền 12m tại khu vực này).
-​Hạ tầng: Ngõ thông, ô tô chạy vòng quanh, cách mặt phố Hồng Tiến chỉ 40m.
-​✨ Kiến Trúc Đẳng Cấp – Công Năng Toàn Diện
-​Ngôi nhà sở hữu thiết kế hiện đại, phù hợp làm văn phòng công ty, spa, phòng khám hoặc để ở thượng lưu:
-​Tầng 1: Thông sàn kinh doanh/văn phòng VIP, kết hợp tiểu cảnh sân vườn, hồ cá Koi và giếng trời thoáng đãng.
-​Tầng 2: Không gian bếp "Master Chef" với đầy đủ thiết bị cao cấp (lò nướng, tủ lạnh side-by-side).
-​Tầng 3, 4, 5: Mỗi tầng 02 phòng ngủ lớn có ban công riêng, vệ sinh khép kín, ánh sáng tự nhiên ngập tràn.
-​Tầng 6: Phòng thờ, khu giặt đồ, sân phơi và kho chứa đồ rộng rãi.
-​Tầng 7: Rooftop BBQ kịch nóc – Tận hưởng không gian tiệc ngoài trời view toàn cảnh quận Long Biên.
-​💰 Tại sao đây là cơ hội đầu tư ***?
-​Mặt tiền cực hiếm: Gần 12m mặt tiền là thông số không có căn thứ hai trong tầm giá.
-​Giá trị thực: Chủ tự xây cực kỳ chắc chắn (bê tông cốt thép kiên cố), nội thất toàn đồ xịn.
-​Vị trí: Ngõ ô tô tránh, thông vòng quanh – Yếu tố then chốt giúp tăng giá trị bất động sản bền vững.
-​Liên hệ xem nhà trực tiếp (Làm việc chính chủ)</t>
-        </is>
-      </c>
-      <c r="R59" t="n">
         <v>131235556</v>
       </c>
     </row>
@@ -5076,28 +3683,6 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O60" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>NGỌC THỤY - 6.85 TỶ - HÀNG XÓM KHAI SƠN CITY - TIỆN ÍCH NGẬP TRÀN</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: NGỌC THỤY - 6.85 TỶ - HÀNG XÓM KHAI SƠN CITY - TIỆN ÍCH NGẬP TRÀN
-- Vị trí: Vài bước ra chợ Ngọc Thụy, công viên, hưởng trọn tiện ích Khai Sơn.
-- Công năng: Nhà dân xây 4 tầng hiện đại, 3 ngủ rộng, móng cọc lên tầng thoải mái.
-- Ưu điểm: Sân chung 3m thoáng sạch, xe để ngoài nhà cực tiện.
-- Nội thất: Đầy đủ, chỉ việc xách vali về ở.
-📞 Liên hệ ngay: *** (Chốt nhanh kẻo lỡ!)</t>
-        </is>
-      </c>
-      <c r="R60" t="n">
         <v>132001655</v>
       </c>
     </row>
@@ -5152,22 +3737,6 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O61" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Nhà xây mới 8 tầng</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Nhà xây mới 8 tầng tháng máy phun nội thất .tầng 1 để 2 xe oto canh hồ điều hòa Long biên,dân trí cao, 50m da cầu Trần Hưng đạo</t>
-        </is>
-      </c>
-      <c r="R61" t="n">
         <v>131693160</v>
       </c>
     </row>
@@ -5222,39 +3791,6 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O62" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ MẶT PHỐ KINH DOANH 66M² 6 TẦNG THANG MÁY ĐƯỜNG VỈA HÈ PHÂN LÔ</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>🔥 SERI NHÀ MẶT PHỐ KINH DOANH LONG BIÊN – 66m² – 6 TẦNG THANG MÁY – VỈA HÈ – GARA – GẦN HỒ ĐIỀU HÒA 31HA 🔥
-💥 Giá từ 17.6 tỷ
-📍 Vị trí vàng – trục chính kinh doanh:
-✔ Cạnh hồ điều hòa 31ha, hồ Đầm Tranh – không gian đẳng cấp
-✔ Kết nối thẳng OCP 1,2,3 – Ecopark – cao tốc Hà Nội Hải Phòng
-✔ Gần Aeon Mall Long Biên, cầu Vĩnh Tuy – di chuyển cực tiện
-🏠 Thông số nổi bật:
-✔ Diện tích 66m²
-✔ 6 tầng thang máy xịn
-✔ Vỉa hè rộng – ô tô tránh – gara riêng
-✔ Full nội thất cao cấp – vào ở/kd ngay
-🚀 Giá trị khai thác:
-✔ Kinh doanh mọi mô hình: showroom, spa, văn phòng
-✔ Dòng tiền ổn định – tăng giá mạnh theo hạ tầng
-✔ Seri nhiều căn – lựa chọn theo nhu cầu &amp; tài chính
-📕 Sổ đỏ chính chủ, sẵn sàng giao dịch
-📞 Alo Em Thiêm xem nhà ngay hôm nay
-#serinhapho #nhamatpho #longbien #kinhdoanhdinh #bdsHanoi #nhadep #thangmay #garaoto #viewho #ecopark #dautuBDS #xuhuongtiktok</t>
-        </is>
-      </c>
-      <c r="R62" t="n">
         <v>131971106</v>
       </c>
     </row>
@@ -5309,26 +3845,6 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>21.068117</v>
-      </c>
-      <c r="O63" t="n">
-        <v>105.90059</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ NGÔ GIA TỰ,LBIEN CÁCH 1 NHÀ RA MẶT PHỐ 45M 3TẦNG NHỈNH 7tỷ</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: • Vị trí vàng: Cách mặt phố chỉ 30m, ngõ thông thoáng. 100m ra Ngô Gia Tự, giao thông thuận tiện nhất quận.
-• Tiện ích sát vách: trường học các cấp chỉ vài bước chân. Dân trí cao, an sinh đỉnh.gần ngay BiG C Long Biên
-• Thiết kế chắc chắn, 3 PN đủ công năng, thoáng trước sau, gió lùa đối lưu cực mát.
-• Pháp lý: Sổ đỏ chính chủ, giao dịch ngay.</t>
-        </is>
-      </c>
-      <c r="R63" t="n">
         <v>131974796</v>
       </c>
     </row>
@@ -5383,37 +3899,6 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O64" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ LÔ GÓC 8 TẦNG THANG MÁY NGÕ THÔNG Ô TÔ VÀO NHÀ 4 PHÒNG NGỦ</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>🔥🔥 BÁN NHÀ LÔ GÓC THẠCH BÀN – 8 TẦNG THANG MÁY – Ô TÔ VÀO NHÀ 🔥🔥
-🏡 Diện tích 50m² – lô góc – thoáng sáng
-🚗 Ngõ ô tô thông – vào nhà
-🏗️ Nhà xây mới 8 tầng – thang máy xịn
-👉 Thiết kế hiện đại:
-T1: Gara ô tô + WC
-T2–5: 4 phòng ngủ rộng + WC khép kín
-T6: Phòng khách + bếp + WC
-T7: Phòng thờ + sân phơi
-T8: Sân chơi
-🌳 Vị trí đẹp – tiện ích đầy đủ:
-Gần chợ Đồng Dinh, Hồ Ben, hồ điều hòa 31ha, trường liên cấp, khu dân cư văn minh
-📕 Sổ đỏ chính chủ, sẵn sàng giao dịch
-💰 Giá đầu tư
-📞 Alo Em Thiêm xem nhà ngay hôm nay
-#bannhathachban #nhalongbien #nhaloogoc #nhathangmay #batdongsanhanoi #nhadep #muabannhadat</t>
-        </is>
-      </c>
-      <c r="R64" t="n">
         <v>131552307</v>
       </c>
     </row>
@@ -5468,34 +3953,6 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>21.048191</v>
-      </c>
-      <c r="O65" t="n">
-        <v>105.86547</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>🌺🌺🌺NGỌC THỤY BỒ ĐỀ  BÁN NHÀ 5TẦNG MỚI TINH  FULL NỘI THẤT   🌺🌺THIẾT KẾ</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🌺🌺🌺NGỌC THỤY BỒ ĐỀ 
-BÁN NHÀ 5TẦNG MỚI TINH 
-FULL NỘI THẤT 
-🌺🌺THIẾT KẾ 
-3Phòng ngủ đầy đủ công năng 
-✳️NHÀ NẰM NGAY TRUNG TÂM NGỌC THỤY 
-VÀI PHÚT RA CHỢ VÀ CÔNG VIÊN 
-🍀GẦN TRƯỜNG QUỐC TẾ VIỆT PHÁP. 
-Nhiều trường học các cấp 🍀KHU HÀNH CHÍNH SỰ NGHIỆP 
-GIAO THÔNG THUẬN TIỆN 
-🍀GIÁ HƠN 8tỷ5
-🌺LH em Hạnh Tran ☎️*** ĐỂ XEM NHÀ VÀ GIAO DỊCH.</t>
-        </is>
-      </c>
-      <c r="R65" t="n">
         <v>131993158</v>
       </c>
     </row>
@@ -5550,34 +4007,6 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>21.040733</v>
-      </c>
-      <c r="O66" t="n">
-        <v>105.89656</v>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>🛍️SHOPHOUSE 2MT Đại Lộ Bốn Mùa Ocean Park 3 TRỤC CHÍNH VÀO DỰ ÁN 51M ✅</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>🔥 SIÊU ƯU ĐÃI ĐẠI LỘ BỐN MÙA VIN3 - GIẢM SỐC CUỐI NĂM🔥
-💰 Giá gốc: ~28 TỶ
-👉 CHIẾT KHẤU NGAY - CHỈ CÒN TỪ 19,8 Ty
-💎 Căn đẹp hiếm có - vị trí đắt giá bậc nhất Đại lộ Bốn Mùa
-✨ Điểm nổi bật:
-- Dt 110m Mt 5m
-- 2 mặt tiền: Mặt tiền Đại lộ Bốn Mùa 51m - trục đường biểu tượng &amp; Mặt tiền đối diện công viên tiện ích Vịnh Tây
-- Không gian sống đẳng cấp, thiết kế sang trọng
-- Phù hợp ở - đầu tư - khai thác kinh doanh
-- Số lượng có hạn, ưu đãi chỉ áp dụng trong thời gian ngắn
-⏰ Cơ hội vàng cho khách hàng nhanh tay
-📞 Inbox hoặc gọi ngay để nhận thông tin chi tiết &amp; chính sách ***.
-#batdongsan #vinhomes #vinhomesoceanpark #vinhomesoceanpark3 #ĐạiLộBốnMùa #OceanCity</t>
-        </is>
-      </c>
-      <c r="R66" t="n">
         <v>130674041</v>
       </c>
     </row>
@@ -5632,28 +4061,6 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>21.049894</v>
-      </c>
-      <c r="O67" t="n">
-        <v>105.89186</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> LÔ GÓC - 3 MẶT THOÁNG - NGUYỄN VĂN LINH- Ô TÔ VÀO NHÀ- THNG MÁY </t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>🔥CỰC HIẾM - LÔ GÓC - 3 MẶT THOÁNG - NGUYỄN VĂN LINH- Ô TÔ VÀO NHÀ- THNG MÁY -- nhà 6 tầng🔥
-🔆VỊ TRÍ ĐẮC ĐỊA - FULL NỘI THẤT- Ô TÔ  VÀO NHÀ🔆
- 🔷Vị trí: Gần Khu Đô thị Sài Đồng hàng xóm với Vinhomes riverside.
-🔷Khu dân cư đông, tiện ích đầy đủ.
-🔷Di chuyển nhanh ra đường 5 kéo dài Liên tỉnh.Giao thông thuận lợi.
-🔷Gần trường học mầm non cho đến THPT , trung tâm Sài Đồng, kinh doanh cho thuê đều hợp lý.
- 📖Sổ đỏ chính chủ – pháp lý rõ ràng</t>
-        </is>
-      </c>
-      <c r="R67" t="n">
         <v>131987872</v>
       </c>
     </row>
@@ -5708,22 +4115,6 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>21.003109</v>
-      </c>
-      <c r="O68" t="n">
-        <v>105.90296</v>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ CỰ KHỐI</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Bán Nhà Tổ 4, Độc Lập, Xuân Khôi, Cự Khối. Diện Tích 55m2, MT 4,87m, ngõ thông rộng gần 3m, cách trục chính 60m. Nhà Yên Tĩnh, Cao, Thoáng làm tầng lửng tối ưu diện tích có thể  ở ngay đc.</t>
-        </is>
-      </c>
-      <c r="R68" t="n">
         <v>131704971</v>
       </c>
     </row>
@@ -5778,29 +4169,6 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>21.041908</v>
-      </c>
-      <c r="O69" t="n">
-        <v>105.873924</v>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ HỒNG TIẾN,LBIEN-38M 5Tầng-Ô TÔ TẢI ĐỖ CỬA-DÂN XÂY-KHU VỰC LÕI</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: _ Vị trí "vàng" tiện ích: Bước chân ra cửa là có đủ: chợ, trường học, công viên và hồ điều hòa (bán kính 100m). Không gian sống trong lành, hạ tầng đồng bộ.
-• Thiết kế hiện đại, thông minh:
-• Tầng 1: Phòng khách sang trọng &amp; khu vực để xe.
-• Tầng 2, 3, 4: Mỗi tầng 1 phòng ngủ khép kín, đảm bảo sự riêng tư tuyệt đối.
-• Tầng 5: Không gian bếp ấm cúng + Phòng thờ + Sân phơi thoáng đãng.
-_ • Giao thông thuận tiện: Đường rộng, ô tô tai 1,5tan chạy qua nhà, ngõ thông thoáng, đi lại cực dễ dàng.
-📍 Pháp lý: Sổ đỏ chính chủ, nở hậu, sẵn sàng sang tên ngay.</t>
-        </is>
-      </c>
-      <c r="R69" t="n">
         <v>131966910</v>
       </c>
     </row>
@@ -5855,29 +4223,6 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O70" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Em chính chủ bán nhà Tư đình dt 60m, gara ôtô, 5 tầng, giá 13.5 tỷ</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Em chính chủ bán nhà tại số 2A ngõ 129/42 Tư đình - Bát khối, dt 60m m, gara ôtô, khu vực đông dân cư, gần trường chợ, bãi xe,...
-Tầng 1: gara ôtô, bếp
-Tầng2: phòng khách và phòng làm việc
-Tầng 3,4: mỗi tầng 2 phòng ngủ
-Tầng 5: phòng thờ và sân phơi
-Em bán giá rẻ rất phù hợp với gia đình có ô tô hoặc đầu tư, chỉ 13.5 tỷ
-Sổ đỏ chính chủ tên em sẵn sàng giao dịch
-LH ***</t>
-        </is>
-      </c>
-      <c r="R70" t="n">
         <v>131358054</v>
       </c>
     </row>
@@ -5932,30 +4277,6 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O71" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>🔥 SIÊU PHẨM NGỌC THỤY - NHÀ MỚI 5 TẦNG - TẶNG FULL NỘI THẤT - 8.5 TỶ</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 SIÊU PHẨM NGỌC THỤY - NHÀ MỚI 5 TẦNG - TẶNG FULL NỘI THẤT - 8.5 TỶ
-• Vị trí: Cực đẹp, 80m ra ô tô tránh, gần Công viên &amp; Chợ Ngọc Thụy.
-• Thông số: 47m² x 5 tầng (3 ngủ khép kín rộng thênh thang).
-• Tình trạng: Nhà chủ tự xây, mới kính koong, đẹp long lanh.
-• Ưu đãi: Chủ tặng lại toàn bộ nội thất cao cấp như ảnh.
-• Pháp lý: Sổ đỏ chính chủ, giao dịch ngay.
-💰 Giá: 8.5 tỷ (Có thương lượng)
-📞 Liên hệ: *** (Xem nhà 24/7)</t>
-        </is>
-      </c>
-      <c r="R71" t="n">
         <v>131981891</v>
       </c>
     </row>
@@ -6010,27 +4331,6 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O72" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>CHỐT NHANH! ĐẤT VÀNG ĐỨC GIANG 105M2 - CHỈ NHỈNH 17 TỶ</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Diện tích: 105m2. Mặt tiền quyền lực: 5.7m (nở hậu nhẹ).
-Hiện trạng: Nhà 2 tầng thiết kế kiểu sân vườn cực chill, khách mua về ở ngay hoặc xây building, biệt thự mini đều tuyệt vời.
-Vị trí: Trung tâm Đức Giang, ngõ thông tứ phía, giao thông thuận tiện. Ngõ rộng, xe 7 chỗ chạy vèo vèo vào tận nhà.
-Tiện ích: Gần BigC Long Biên, Bệnh viện Đức Giang, trường học các cấp... dân trí cao, an ninh tốt.
-Giá chào: Nhỉnh 17 tỷ (Có thương lượng cho khách thiện chí).
-Sổ đỏ chính chủ, pháp lý chuẩn, sẵn sàng giao dịch.</t>
-        </is>
-      </c>
-      <c r="R72" t="n">
         <v>131981586</v>
       </c>
     </row>
@@ -6085,46 +4385,6 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>21.036098</v>
-      </c>
-      <c r="O73" t="n">
-        <v>105.87419</v>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Cực Hiếm bán nhà xây mới 100% oto ngủ trong nhà</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔴 Em bán căn nhà xây mới 100%
-🏠 Địa chỉ: Nguyễn Văn Cừ, Bồ Đề, Long Biên.
-🚘 Ngõ trước nhà 4m, ô tô vào nhà.
-🏣 Nhà xây 7 tầng + thang máy + full nội thất cao cấp.
-🔹 Thiết bị wc INAX.
-🔹 Điều hoà Âm Trần DAIKIN.
-🔹 Xông hơi khép kín.
-* Tầng 1: Sảnh ô tô.
-* Tầng 2: Phòng ngủ Master VIP - phòng Xông Khô.
-* Tầng 3: Phòng ngủ Master
-* Tầng 4: 2 phòng ngủ nhỏ + WC
-* Tầng 5: Phòng Khách + Ban Công
-* Tầng 6: Bếp + Phòng Ăn
-* Tầng 7: Phòng Thờ Lớn + Sân Thượng
-🌆 Vị trí, Giao thông vô cùng thuận lợi:
-- Gần Big C Long Biên, Aeon Mall.
-- Gần Cầu Đông Trù, Vincom Cổ Loa.
-- Gần Bệnh Viện Tâm Anh.
-🎁 Công tơ điện và nước sạch riêng từng nhà.
-🌆Khu dân trí cao, an ninh tốt, hàng xóm thân thiện.
-📕 Sổ đỏ chính chủ không tranh chấp, không quy hoạch.
-💐Giá : 21 tỷ.đã bao gồm: thuế, phí .
-☎️ Liên hệ - .
-🤝</t>
-        </is>
-      </c>
-      <c r="R73" t="n">
         <v>131981274</v>
       </c>
     </row>
@@ -6179,34 +4439,6 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>21.07492</v>
-      </c>
-      <c r="O74" t="n">
-        <v>105.89177</v>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Nhà mới xây cần bán</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: BÁN NHÀ MỚI THƯỢNG THANH – LONG BIÊN – THANG MÁY FUJI
-📐 53m² – 5 tầng – MT 4m
-💰 Giá: 11. tỷ
-✨ Nhà mới xây – thang máy Fuji 5 điểm dừng – thoáng sau cực đẹp
-Thiết kế:
-	•	T1: Phòng khách + bếp rộng, thông thoáng
-	•	T2,3: 2 phòng ngủ master rộng, có phòng thay đồ riêng, cabin tắm
-	•	T4: 2 phòng ngủ rộng
-	•	T5: Phòng thờ, kho, phòng giặt, sân mái kính
-🔥 Nội thất cao cấp: thiết bị Viglacera, đèn sưởi, bình nóng lạnh 30L, cabin tắm.
-📕 Sổ đỏ cất két – sẵn sàng giao dịch
-📞 Liên hệ xem nhà:</t>
-        </is>
-      </c>
-      <c r="R74" t="n">
         <v>131103706</v>
       </c>
     </row>
@@ -6261,37 +4493,6 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O75" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Thượng Thanh 38m2 Xây 4T - Cách Ô tô Tránh 5m - KD đỉnh - Giá 7850 tỷ</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Chủ nhà cần bán gấp siêu phẩm phố Thượng Thanh, thiết kế hiện đại, công năng hoàn hảo, vị trí đắc địa vừa ở vừa kết hợp kinh doanh hái ra tiền!
-📍 Thông tin cơ bản:
-• Diện tích: 38m2.
-• Kết cấu: Xây mới 4 tầng kiên cố, thiết kế hiện đại.
-• Giá chào: 7,850Tỷ (Có thương lượng cho khách thiện chí).
-🏡 Thiết kế tối ưu công năng (4 phòng ngủ):
-• Tầng 1: Thiết kế thông sàn rộng rãi (phù hợp làm mặt bằng kinh doanh, mở tiệm tạp hóa, spa mini, nail...) + WC.
-• Tầng 2 &amp; 3: Mỗi tầng 2 phòng ngủ sáng thoáng + WC. (Tổng 4 phòng ngủ tiện lợi cho gia đình nhiều thế hệ).
-• Tầng 4: Phòng thờ trang nghiêm + Sân phơi đón nắng gió tự nhiên cực kỳ thoáng mát.
-🌟 Vị trí &amp; Tiện ích bạt ngàn:
-• Giao thông cực đỉnh: Vị trí siêu đẹp, ngõ nông rộng, ô tô đỗ cách nhà đúng 5m, di chuyển hay vận chuyển hàng hóa cực kỳ thuận tiện.
-• Tiện ích bao quanh: Khu vực dân trí cao, an ninh tốt. Vài bước chân ra chợ, trường học các cấp, siêu thị, đáp ứng đầy đủ mọi nhu cầu sinh hoạt hàng ngày.
-• Đa giá trị: Ngôi nhà hiếm hoi trong tầm giá vừa sở hữu không gian sống lý tưởng, vừa có mặt bằng kinh doanh sinh lời ngay tại nhà.
-📜 Pháp lý:
-• Sổ đỏ chính chủ, vuông vắn, cất két sẵn sàng giao dịch ngay.</t>
-        </is>
-      </c>
-      <c r="R75" t="n">
         <v>131351191</v>
       </c>
     </row>
@@ -6346,33 +4547,6 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>21.054369</v>
-      </c>
-      <c r="O76" t="n">
-        <v>105.89245</v>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>HOT! Nhà dân xây Đức Giang 44m2x4T, MT4m, ngõ thông 10m, 8.6 tỷ</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Gia đình có nhu cầu chuyển đổi cần bán nhanh căn nhà tự xây vô cùng tâm huyết tại khu vực trung tâm Đức Giang.
-Thông số: Diện tích 44m2, mặt tiền 4m chuẩn phong thủy.
-Tiện ích &amp; Giao thông: + Vị trí đắc địa với ngõ thông thoáng, khoảng cách ra mặt đường ô tô tránh nhau chỉ vỏn vẹn 10m.
-Khu vực dân trí cao, an ninh đảm bảo. Bán kính 500m thừa hưởng trọn vẹn tiện ích: Bệnh viện Đa khoa Đức Giang, chợ truyền thống, hệ thống giáo dục từ mầm non đến THPT. Dễ dàng di chuyển vào trung tâm nội thành.
-Đặc điểm nổi bật: Khác với nhà xây thương mại, đây là nhà do chủ tự xây để ở nên chất lượng vật tư và thi công được chăm chút cực kỳ kỹ lưỡng.
-Thiết kế 4 tầng hiện đại, đáp ứng gia đình đa thế hệ:
-Tầng 1: Không gian sinh hoạt chung gồm Phòng khách tiếp đón bạn bè, Bếp tiện nghi và WC.
-Tầng 2 &amp; 3: Thiết kế mỗi tầng 2 Phòng ngủ (tổng 4 phòng ngủ). Các phòng đều có cửa sổ đón nắng gió tự nhiên, kèm WC chung.
-Tầng 4: Khu vực Tâm linh (Phòng thờ) và Sân phơi đồ.
-Giá bán: 8.6 Tỷ (Cam kết hình ảnh và thông tin chuẩn 100%).
-Sổ đỏ chính chủ, pháp lý minh bạch.
-#NhaDanXay #NhaOToTranh #NhaNgoThong #Nha4Tang #NhaDepLongBien #NhaMoiOTrang</t>
-        </is>
-      </c>
-      <c r="R76" t="n">
         <v>131303250</v>
       </c>
     </row>
@@ -6427,32 +4601,6 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O77" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>THANH AM 52M2 - MT 4.2M - 5 TẦNG - NGÕ THÔNG BA GÁC - 7.6 TỶ 🌟</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Một lựa chọn không thể tuyệt vời hơn cho gia đình tìm kiếm không gian sống chất lượng tại Long Biên!
-🏡 Cấu trúc nhà 5 tầng mới tinh:
-Nhà mới hoàn thiện, thơm phức mùi sơn. Thiết kế tỉ mỉ với mặt tiền 4.2m trên nền diện tích 52m2:
-• Tầng 1: Khu vực tiếp khách và bếp ăn hiện đại.
-• Tầng 2, 3, 4: Hệ thống phòng ngủ thoáng sáng, bố trí hợp lý.
-• Tầng 5: Sân phơi, phòng thờ thanh tịnh.
-📍 Vị trí &amp; Tiện ích:
-• Ngõ trước nhà thông thoáng, ba gác tránh. Cách 20m ra mặt ngõ chính ô tô tránh nhau vù vù.
-• Khu vực Thanh Am không khí trong lành, thừa hưởng tiện ích từ trường học các cấp, chợ dân sinh, đến công viên cây xanh và hồ điều hòa thoáng mát.
-💵 Giá: 7.6 Tỷ. Đã có sẵn nhà đẹp, chỉ chờ chủ nhân mới xách vali đến ở!</t>
-        </is>
-      </c>
-      <c r="R77" t="n">
         <v>131323830</v>
       </c>
     </row>
@@ -6507,26 +4655,6 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>21.058416</v>
-      </c>
-      <c r="O78" t="n">
-        <v>105.89463</v>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ HOA LÂM48M2-6 TẦNG THANG MÁY-NHỈNH 12 TỶ-Ô TÔ ĐỖ CỬA-NGÕ THÔNG</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>* Thông số vàng: Diện tích 48m2, xây dựng 6 tầng hiện đại, thang máy nhập khẩu chạy êm ru.
-Vị trí đắc địa: Nằm tại trung tâm Hoa Lâm, ngõ thông thoáng, ô tô đỗ cửa, di chuyển cực kỳ thuận tiện.
-Thiết kế: Tối ưu công năng với đầy đủ phòng khách, bếp, phòng ngủ rộng rãi, phù hợp cho gia đình đông thành viên.
-Tiện ích: Bao quanh là hệ thống tiện ích 5 sao, trường học, bệnh viện, TTTM chỉ vài bước chân.
-Pháp lý: Sổ đỏ chính chủ, sẵn sàng giao dịch.</t>
-        </is>
-      </c>
-      <c r="R78" t="n">
         <v>131282397</v>
       </c>
     </row>
@@ -6581,32 +4709,6 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>21.045387</v>
-      </c>
-      <c r="O79" t="n">
-        <v>105.881195</v>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hiếm  F0 Nguyễn Sơn ngõ thông, gara ô tô, ..kinh doanh đã ngành nghề, </t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>🔥 F0 Nguyễn Sơn – Hàng hiếm không có căn thứ 2! 🔥
-🏡 Nhà đẹp – vượng khí – 2 thoáng trước sau.
-📐 57m² – Mặt tiền 4,8m cực rộng.
-🚗 Ngõ thông – ô tô vào nhà – gara.
-💼 Ở + kinh doanh cực đỉnh.
-✔️ Sàn &amp; cầu thang gỗ lim nguyên tấm.
-✔️ Khu phân lô dân trí cao, an ninh tốt.
-✔️ Chủ bán để đổi nhà to hơn – cực thiện chí.
-💰 Giá chỉ: 16,5 tỷ (có thương lượng).
-📕 Sổ đỏ chính chủ – giao dịch ngay
-📞 Liên hệ: [SĐ] – xem nhà 24/7</t>
-        </is>
-      </c>
-      <c r="R79" t="n">
         <v>131890075</v>
       </c>
     </row>
@@ -6661,24 +4763,6 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>21.036098</v>
-      </c>
-      <c r="O80" t="n">
-        <v>105.87419</v>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP Bồ Đề 7 tỷ ở ngay</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Nhà đẹp lung linh ở bồ đề ngĩ ô tô. 5m ra ô tô tránh. Nhà dân xây kiên cố chắc chắn 5 tầng. Sử dụng 65m2. Sân rộng thoáng.
-Gần trường học, doanh trại quân đội. An sinh cực đỉnh.</t>
-        </is>
-      </c>
-      <c r="R80" t="n">
         <v>131950619</v>
       </c>
     </row>
@@ -6733,33 +4817,6 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>21.041908</v>
-      </c>
-      <c r="O81" t="n">
-        <v>105.873924</v>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>🚀  BÁN NHÀ LÔ 2 PHỐ HỒNG TIẾN - 6 TẦNG THANG MÁY - GARA 7 CHỖ 🚀</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🚀  BÁN NHÀ LÔ 2 PHỐ HỒNG TIẾN - 6 TẦNG THANG MÁY - GARA 7 CHỖ 🚀
-📍 VỊ TRÍ VÀNG: Sát mặt phố Hồng Tiến, ngõ thông các ngả. Ngay gần BV Tâm Anh &amp; trường Quốc tế Wellspring, khu vực VIP nhất Long Biên.
-🏡 THIẾT KẾ ĐỈNH CAO:
-🏗️ Diện tích: 50m2 x 6 Tầng Thang Máy xịn xò.
-🚗 Tầng 1: Gara ô tô 7 chỗ rộng thênh thang.
-🛋️ Tầng 2: Phòng khách + Bếp hiện đại, sang trọng.
-🛌 Tầng 3, 4, 5: 3 Phòng ngủ Master khép kín, riêng tư.
-🙏 Tầng 6: Phòng thờ + Sân phơi view thoáng đãng.
-⚖️ PHÁP LÝ CHUẨN: Sổ đỏ chính chủ, NỞ HẬU lộc lá, sẵn sàng giao dịch ngay.
-💰 GIÁ CHÀO: 14.5 TỶ (Thương lượng sâu)
-📞 LH EM ĐẠT: *** (Tận tâm - Uy tín - Hỗ trợ 24/7)</t>
-        </is>
-      </c>
-      <c r="R81" t="n">
         <v>131536890</v>
       </c>
     </row>
@@ -6814,30 +4871,6 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O82" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>THẠCH BÀN - CĂN GÓC - NGÕ TO NHƯ  - Ô TÔ ĐỖ CỬA NGÀY ĐÊM</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Vị trí: Thạch Bàn, Long Biên. Căn góc siêu thoáng, ngõ rộng như mặt phố, ô tô vào nhà êm ru hoặc đỗ cửa ngày đêm thoải mái.
-• Thông số: 45m2 x 6 tầng. Thiết kế sang trọng, Thang máy hiện đại.
-• Ưu điểm: Nhà Nở hậu tài lộc. 3 phòng ngủ tràn ngập ánh sáng tự nhiên, không gian sống đẳng cấp.
-• Tiện ích: Bán kính 500m đầy đủ chợ, trường học, Aeon Mall... Tiện ích từ A-Z.
-• Giá chào: Nhỉnh 11 tỷ (giá cực êm).
-• Pháp lý: Sổ đỏ chính chủ, sẵn sàng giao dịch.
-LH em Đạt: *** (Chuyên nhà đất Long Biên)
-#bannhathachban #nhadatlongbien</t>
-        </is>
-      </c>
-      <c r="R82" t="n">
         <v>131666821</v>
       </c>
     </row>
@@ -6892,28 +4925,6 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O83" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>📢📢📢 Mặt bằng kinh doanh 45m2 sầm uất trên đường Nguyễn Văn Hưởng!</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: ✨️Diện tích 45m2/ Cấp 4 (cho thuê)
-- Mặt tiền 6m = hậu, hướng Đông Bắc
-- Đường trước nhà 2 ô tô tránh có vỉa hè, kinh doanh sầm uất, gần ngay trung tâm hành chính Long Biên
-- Pháp lý chuẩn, sẵn sàng giao dịch
-Giá nhỉnh 13 tỷ
-📱Phở bò/ zep lào: Huy Định *** xem đất và tư vấn 24/7</t>
-        </is>
-      </c>
-      <c r="R83" t="n">
         <v>131974535</v>
       </c>
     </row>
@@ -6968,36 +4979,6 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>21.027077</v>
-      </c>
-      <c r="O84" t="n">
-        <v>105.923355</v>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ LONG BIÊN 5 TẦNG Ô TÔ ĐỖ CỬA 6 PHÒNG NGỦ GIÁ ĐẸP</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Nhà xây mới 5 tầng  6 phòng ngủ
- Hoàn thiện nội thất cơ bản, thiết kế hiện đại
- Phù hợp gia đình đông người hoặc vừa ở vừa cho thuê sinh dòng tiền
- Thiết kế chi tiết:
- Tầng 1: Phòng khách + bếp + WC
- Tầng 2  3  4: Mỗi tầng 2 phòng ngủ (Tổng 6 PN)
- Tầng 5: Tum + sân phơi thoáng mát
- Vị trí cực đẹp:
- Cạnh chợ Đồng Dinh  sinh hoạt, kinh doanh thuận tiện
- Gần Hồ Ben &amp; Hồ điều hòa không gian xanh, thoáng mát quanh năm
- Kết nối nhanh Cổ Linh  AEON  cầu Vĩnh Tuy.  Nhà đang xây hoàn thiện, sau khi hoàn thiện như ảnh minh họa.
- Sổ đỏ chính chủ, sẵn sàng giao dịch
- Liên hệ: Trọng Thiêm
- Xem nhà miễn phí  phục vụ uy tín, tận tâm, chuyên nghiệp
-#BanNhaNguyenVanLinh #ChoDongDinh #HoBen #HoDieuHoa #NhaDepLongBien #OToDoCua #BatDongSanLongBien</t>
-        </is>
-      </c>
-      <c r="R84" t="n">
         <v>130137603</v>
       </c>
     </row>
@@ -7052,27 +5033,6 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O85" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ THẠCH BÀN 47M 6 TẦNG CÓ THANG MÁY- NỘI THẤT ĐẸP HƠN 9 TỶ</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>🏠🎁BÁN CĂN NHÀ ĐẸP THẠCH BÀN 47M 6 TẦNG-THANG MÁY- FULL NỘI THẤT XỊN- CHỈ VIỆC XÁCH VALY VỀ Ở- GIÁ HƠN 9 TỶ
-🔶Nhà xây mới 47m xây 6 tầng- Có thang máy 450 kg
-Nhà đã làm nội thất tỉ mỉ, xịn sò. Chỉ việc mang quần áo tới ở ngay.
-🔶Vị trí ngay Thạch Bàn, gần Chợ, trường học...dân cư xung quanh văn minh lịch sự.
-🎉Sổ đỏ chính chủ, có hỗ trợ vay vốn ngân hàng lãi suất thấp.
-☎️Liên hệ:  Em Hiệp để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R85" t="n">
         <v>128520528</v>
       </c>
     </row>
@@ -7127,30 +5087,6 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>21.04372</v>
-      </c>
-      <c r="O86" t="n">
-        <v>105.92593</v>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Vị trí vàng - Khu phân lô - Mặt tiền 6m - 6 tầng thang máy kinh doanh</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>💎 Hàng xóm Vin Riverside – vị trí hiếm, càng giữ càng tăng giá
-📍 75m² – mặt tiền 6m cực đẹp
-🏢 Nhà 5 tầng – thang máy xịn – thiết kế tối ưu
-🚗 Tầng 1 thông sàn: để xe / kinh doanh đỉnh cao
-🛏 6 phòng ngủ rộng – công năng đầy đủ
-🌆 Sân thượng thoáng – view mở cực chill
-👉 Nhà không thiếu – nhưng căn vừa đẹp, vừa “ra tiền” thế này thì rất hiếm
-📕 Sổ đỏ sẵn – xem là muốn chốt
-Liên hệ em để đi xem ngay</t>
-        </is>
-      </c>
-      <c r="R86" t="n">
         <v>131864694</v>
       </c>
     </row>
@@ -7205,25 +5141,6 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>21.068117</v>
-      </c>
-      <c r="O87" t="n">
-        <v>105.90059</v>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>GIÁ ĐẦU TƯ - BIỆT THỰ MINI 68m  VIỆT HƯNG - MẶT TIỀN 6.8M - 4 MẶT THOÁ</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: _ Mặt tiền 6.8m cực khủng, tạo không gian kiến trúc bề thế như biệt thự đơn lập. Nhà thoáng 4 phía, không chung tường, không chạm lưng – đảm bảo sự riêng tư tuyệt đối.
-_ Tiện ích: Thuộc khu vực đáng sống nhất Long Biên, gần Vinhomes, công viên, bệnh viện quốc tế. Giao thông thuận tiện, đường xá bàn cờ thông thoáng.
-_ Thiết kế thông minh, tối ưu diện tích với đầy đủ phòng khách sang trọng, bếp hiện đại và các phòng ngủ tràn ngập ánh sáng</t>
-        </is>
-      </c>
-      <c r="R87" t="n">
         <v>131945553</v>
       </c>
     </row>
@@ -7278,27 +5195,6 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O88" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>📢📢📢Nhà 5 Tầng Ngọc Thụy - Long Biên, Ô Tô 7 Chỗ Đỗ Tận Cửa-8.1 Tỷ</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: ✨️Diện tích 33m2/ 5 tầng
-- Mặt tiền 4.75m = hậu, hướng Đông Nam
-- Trước nhà ô tô ra vào, ngõ thẳng, cách ô tô tránh 5m, gần cầu Long Biên di chuyển thuận tiện
-- Nhà thiết kế 4 tầng 1 tum, 3 ngủ full nội thất
-📱Phở bò/ zep lào: *** Huy Định xem nhà và tư vấn 24/7</t>
-        </is>
-      </c>
-      <c r="R88" t="n">
         <v>131961747</v>
       </c>
     </row>
@@ -7353,28 +5249,6 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O89" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>🔥 SIÊU PHẨM LONG BIÊN 6.8 TỶ - 50M RA Ô TÔ - TƯƠNG LAI RA MẶT PHỐ 🔥</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 SIÊU PHẨM LONG BIÊN 6.8 TỶ - 50M RA Ô TÔ - TƯƠNG LAI RA MẶT PHỐ 🔥
-✅ 4 tầng, thiết kế hiện đại, giếng trời cực thoáng.
-✅ Ngõ thông, 50m ra ô tô tránh. Hưởng trọn tiện ích dự án mở ngõ.
-✅ Cấu trúc: Tầng 1 (PK, Bếp); Tầng 2 (Ngủ Master); Tầng 3 (Ngủ+VS); Tầng 4 (Thờ, Ngủ khách, Sân phơi).
-✅ Giá: 6.8 tỷ (Sổ đỏ đẹp sẵn sàng giao dịch).
-☎️ LH: *** (Đạt) - Cam kết thông tin thật 100%!</t>
-        </is>
-      </c>
-      <c r="R89" t="n">
         <v>131961320</v>
       </c>
     </row>
@@ -7429,33 +5303,6 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O90" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Bàn Toà Chung Cư Mi Ni Việt Hưng . Long Biên. 8 Tầng Thang May</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: CON GÀ ĐẺ TRỨNG VÀNG 🇻🇳
-✅ SIÊU PHẨM VIÊT HƯNG - LONG BIÊN 
-Lô  góc 2 mặt thoáng .
-DT 64/70m2* 8 tầng thang máy – mới kính koong . 19 phòng . Full nội thất 
-💸 Dòng tiền hơn 1 TỶ/năm – có sẵn khách thuê, chỉ việc vận hành
-📍 Trung tâm Việt Hưng – sát Vinhomes – khu thuê cực HOT
-Giấy tờ pháp lý chuẩn. Đầy đủ phòng cháy chữa cháy vvv 
-Giao dịch phút mốt 
-🔥 Zá bán nhanh 15, x Tỷ
-TL sâu cho khách mang tiền đến cọc
-Nhanh tay alo số ĐT/Zalo.</t>
-        </is>
-      </c>
-      <c r="R90" t="n">
         <v>131959427</v>
       </c>
     </row>
@@ -7510,25 +5357,6 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O91" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Chính chủ gửi bán nhà view hồ Bồ Đề</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Chính chủ gửi bán căn nhà 3 tầng mặt hồ Bồ Đề rất đẹp.
-Mặt tiền 6m, nở hậu.
-Diện tích 175m2, ngõ ô tô, view Hồ.
-Thoáng trước sau.</t>
-        </is>
-      </c>
-      <c r="R91" t="n">
         <v>131728993</v>
       </c>
     </row>
@@ -7583,24 +5411,6 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O92" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>🔥 GIẢM SỐC NHÀ PHỐ – CỔ LINH, LONG BIÊN – 7 TẦNG THANG MÁY, GARA Ô TÔ</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>🏡 65m², xây 7 tầng, full nội thất 5★, khu phân lô quân đội an ninh cực tốt – ở sướng, đẳng cấp
-📍 Vị trí đẹp gần Aeon Mall, cầu Trần Hưng Đạo, Him Lam, sân Golf Long Biên – 10 phút sang Hồ Gươm
-💰 Giá hơn 23 tỷ (có thương lượng) – sổ đỏ chính chủ, giao dịch nhanh gọn, hàng hiếm khu vực 🚀</t>
-        </is>
-      </c>
-      <c r="R92" t="n">
         <v>131955401</v>
       </c>
     </row>
@@ -7655,28 +5465,6 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>21.022112</v>
-      </c>
-      <c r="O93" t="n">
-        <v>105.907234</v>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ THẠCH BÀN 52M 4 TẦNG, CÓ SÂN RIÊNG ĐỂ XE- FULL NỘI THẤT 7,8 TỶ</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>🟠✅BÁN NHÀ THẠCH BÀN 52M 4 TẦNG, CÓ SÂN RIÊNG ĐỂ XE- FULL NỘI THẤT 7,8 TỶ ( CÓ THƯƠNG LƯỢNG)
-🏠Căn nhà siêu rẻ 52m 4 tầng tại Thạch Bàn giá 7,8 tỷ. Đầy đủ nội thất giường, tủ, sofa…
-🔸Tầng 1: Sân để xe, phòng khách, bếp
-🔸Tầng 2,3: Mỗi tầng 2 ngủ, vệ sinh khép kín từng phòng.
-🔸Tầng 4: Phòng thờ, sân phơi
-Sổ đỏ chính chủ, full thổ cư
-☎️LH  Em Hiệp để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R93" t="n">
         <v>130634568</v>
       </c>
     </row>
@@ -7731,26 +5519,6 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>21.06897</v>
-      </c>
-      <c r="O94" t="n">
-        <v>105.87928</v>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Nhà 2 tầng 63m2 - Ngọc Thụy (Bồ Đề) - Mặt ngõ to 2 oto tránh nhau</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>Chính chủ bán đất tặng nhà, nhà 2 tầng cũ, mặt ngõ 2 ô tô tránh nhau, đất phân lô quân đội.
-Diện tích 63m², mặt tiền = hậu = 3m6
-Gần chợ, trường học, công viên,...
-Địa chỉ: Số 11, Ngõ 103, Đường Lý Sơn, Phường Ngọc Thụy (Bồ Đề mới), Quận Long Biên, Hà Nội
-Liên hệ sdt: *** (Chị Luyến) - Có thể thương lượng thêm</t>
-        </is>
-      </c>
-      <c r="R94" t="n">
         <v>131954170</v>
       </c>
     </row>
@@ -7805,31 +5573,6 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>21.06897</v>
-      </c>
-      <c r="O95" t="n">
-        <v>105.87928</v>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>🏡 BÁN NHÀ LIỀN KỀ KHAI SƠN – LÔ GÓC 3 MẶT THOÁNG – KINH DOANH ĐỈNH</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>📍 KĐT Khai Sơn City – khu đô thị hiện đại, dân cư đông đúc, kinh doanh sầm uất.
-🔹 Diện tích: 100m²
-🔹 Xây 5 tầng chắc chắn
-🔹 Lô góc 3 mặt thoáng – cực hiếm
-🔹 Phân lô – vỉa hè rộng – ô tô tránh
-🔹 Phù hợp ở kết hợp kinh doanh, mở văn phòng, spa, showroom…
-📕 Sổ đỏ sẵn – giao dịch ngay
-💰 Giá chào: (có thương lượng)
-📞 Liên hệ xem nhà trực tiếp – làm việc chính chủ.
-#KhaiSon #LongBien #NhaLienKe #LoGoc #BatDongSanLongBien #NhaDep #KinhDoanh</t>
-        </is>
-      </c>
-      <c r="R95" t="n">
         <v>130837433</v>
       </c>
     </row>
@@ -7884,32 +5627,6 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>21.040733</v>
-      </c>
-      <c r="O96" t="n">
-        <v>105.89656</v>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ PHÚC ĐỒNG 105M  4 TẦNG 4 NGỦ CÓ SÂN TRƯỚC, SÂN SAU HƠN 11 TỶ</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>🔥✅BÁN NHÀ CHU HUY MÂN – PHÚC ĐỒNG DÂN XÂY   105M  4 TẦNG 4 NGỦ | CÓ SÂN TRƯỚC, SÂN SAU CỰC THOÁNG| FULL ĐỒ GIÁ HƠN 11 TỶ
-🔶Vị trí đường Chu Huy Mân, gần Chợ Phúc Đồng, Khu đô thị mới Sài Đồng Nguyễn Lam
-🏠 🌟Nhà dân xây, thiết kế hợp lý
- • Diện tích: 105m², mặt tiền 4,7m
- • T1: Khách – bếp, sân trước &amp; sau cực thoáng
- • T2–3: Mỗi tầng 2 ngủ + 1 WC
- • T4: Phòng thờ + sân phơi
-👉 Tổng 4 phòng ngủ, đủ nội thất
-📕Pháp lý chuẩn: sổ đỏ riêng full thổ cư, không tranh chấp – không quy hoạch
- • 150m: Trường học, chợ,  300m: AEON Mall Long Biên đi lại cực kỳ thuận tiện
-☎️LH  Em Hiệp để đi xem nhà trực tiếp và được giá ***</t>
-        </is>
-      </c>
-      <c r="R96" t="n">
         <v>129968641</v>
       </c>
     </row>
@@ -7964,27 +5681,6 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>21.023499</v>
-      </c>
-      <c r="O97" t="n">
-        <v>105.917404</v>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Nhà Mới Toanh - Diện tích rộng - Ngõ Ô Tô</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>THẠCH BÀN  LONG BIÊN - NHÀ MỚI TOANH -   DÂN XÂY - Ô TÔ 7 CHỖ ĐỖ CỬA - GẦN TRƯỜNG, CHỢ AONE MALL - HÀNG XÓM KĐT - NGÕ THÔNG -  2 MẶT NGÕ TRƯỚC SAU - DIỆN TÍCH RỘNG GIÁ ĐẦU TƯ 
-+ S 70m x 4 tầng mặt tiền 4m 
-+ Thiết kế 4 phòng ngủ rộng đẹp 
-+ sổ đỏ sang tên ngay 
-+ Giá hơn 10,8 tỷ ( còn bớt)
-+ Liên hệ Khánh để xem nhà</t>
-        </is>
-      </c>
-      <c r="R97" t="n">
         <v>131951571</v>
       </c>
     </row>
@@ -8039,34 +5735,6 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>21.05286</v>
-      </c>
-      <c r="O98" t="n">
-        <v>105.92033</v>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>🏡 LONG BIÊN – NHÀ ĐẸP 6 TẦNG THANG MÁY – Ô TÔ ĐỖ CỬA – 50M² – HƠN 9 TỶ</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🏡 LONG BIÊN – NHÀ ĐẸP 6 TẦNG THANG MÁY – Ô TÔ ĐỖ CỬA – 50M² – HƠN 9 TỶ
-• Diện tích 50m², mặt tiền rộng 5,6m cực kỳ bề thế, hiếm trong phân khúc
-• Nhà xây 6 tầng có thang máy, thiết kế hiện đại – tối ưu công năng sử dụng
-• Không gian thoáng sáng, hình khối đẹp – full nội thất cao cấp, chỉ việc xách vali về ở
-• Ô tô đỗ cửa, giao thông thuận tiện, kết nối nhanh các trục chính Long Biên
-Tiện ích xung quanh:
-• Hưởng trọn tiện ích khu đô thị Vinhomes Riverside
-• Gần Marie Curie School và Chu Văn An High School – môi trường giáo dục top đầu
-• Khu dân cư văn minh, dân trí cao, an ninh tốt, phù hợp an cư lâu dài
-📕 Sổ đỏ chính chủ – pháp lý sạch – giao dịch nhanh gọn
-📞 LH/Zalo: ***
-Gặp trực tiếp chủ nhà – thương lượng thiện chí</t>
-        </is>
-      </c>
-      <c r="R98" t="n">
         <v>131466859</v>
       </c>
     </row>
@@ -8121,24 +5789,6 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>21.036098</v>
-      </c>
-      <c r="O99" t="n">
-        <v>105.87419</v>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Nhà đẹp long biên-5tỷ-ở ngay</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Nhà mới 5 tầng ngõ ô tô 
-Cần thanh khoản ngay để trả ngân hàng.</t>
-        </is>
-      </c>
-      <c r="R99" t="n">
         <v>131920337</v>
       </c>
     </row>
@@ -8193,32 +5843,6 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O100" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>🔥 SIÊU PHẨM NGỌC LÂM - 65M² LÔ GÓC - THANG MÁY - 30M RA PHỐ 🔥</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💎 VỊ TRÍ VÀNG: Cách mặt phố Ngọc Lâm đúng 30m. Ngõ thông, ô tô vào nhà êm ru.
-💎 THÔNG SỐ ĐẸP: Diện tích 65m², Mặt tiền 4.5m cực thoáng.
-💎 THIẾT KẾ 6 TẦNG:u
-• Thang máy nhập khẩu.
-• Lô góc 2 mặt thoáng, phòng nào cũng ngập tràn ánh sáng.
-• Công năng: Gara ô tô, Khách + Bếp, 2 PN Master đại gia + 2 PN nhỏ, Phòng thờ, Sân phơi view cực chill.
-📈 GIÁ TRỊ: Vừa ở đẳng cấp, vừa làm văn phòng/kinh doanh tuyệt đỉnh. Quỹ đất hiếm, tiềm năng tăng giá mạnh.
-⚖️ Pháp lý: Sổ đỏ chính chủ, giao dịch ngay.
-📞 Liên hệ em Đạt: *** 
-(Xem nhà 24/7 - Cam kết thông tin chuẩn 100%)</t>
-        </is>
-      </c>
-      <c r="R100" t="n">
         <v>131456674</v>
       </c>
     </row>
@@ -8273,33 +5897,6 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>21.041908</v>
-      </c>
-      <c r="O101" t="n">
-        <v>105.873924</v>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>💰 DÒNG TIỀN ỔN ĐỊNH ~1,5 TỶ/NĂM  – HIẾM TRONG TẦM GIÁ HƠN 22 TỶ</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>💰 DÒNG TIỀN ỔN ĐỊNH ~1,5 TỶ/NĂM – NHÀ 8 TẦNG THANG MÁY – HIẾM TRONG TẦM GIÁ HƠN 22 TỶ.
-📍 Vị trí trung tâm cực đẹp, Chỉ 1 phút đi bộ tới BV Tâm Anh
-5 phút di chuyển tới phố cổ.
-💥Cách trường quốc tế Wellspring ~500m.
-Nhà 8 tầng hiện đại, thiết kế tối ưu khai thác dòng tiền
-Có thang máy tiện lợi
-💥Diện tích hiếm, giá đầu tư cực tốt trong khu vực.
-🛋 Trang bị full nội thất cao cấp.
-📈 Khai thác kinh doanh sẵn có – dòng tiền ổn định ~1,5 tỷ/năm.
-💵 Giá bán: nhỉnh 22 tỷ (có thương lượng tốt cho khách thiện chí)
-📞 Liên hệ trực tiếp chủ nhà: ***
-👉 Gặp trực tiếp – đàm phán – chốt giá tốt.</t>
-        </is>
-      </c>
-      <c r="R101" t="n">
         <v>131787192</v>
       </c>
     </row>
@@ -8354,33 +5951,6 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O102" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>55M2 NHÀ MỚI – TƯƠNG LAI RA MẶT PHỐ – GIÁ RẺ NHẤT QUẬN LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: CHỐT GẤP: 55M2 NHÀ MỚI – TƯƠNG LAI RA MẶT PHỐ – GIÁ RẺ NHẤT QUẬN LONG BIÊN
-📍 VỊ TRÍ "HÁI RA TIỀN": * Nhà nằm ngay khu vực quy hoạch mở đường 13.5m. Từ nhà ra mặt phố chỉ trong tầm tay.
-• Ngõ thông thoáng, ô tô. Tiềm năng tăng giá X2, X3 cực rõ ràng!
-🏡 NHÀ ĐẸP – Ở NGAY – KHÔNG ĐỐI THỦ:
-• Mới tinh 100%: Thiết kế 5 tầng hiện đại, nội thất cao cấp, chỉ việc xách vali về tận hưởng.
-• Diện tích lý tưởng: 55m² cực rộng, mỗi tầng 1 phòng ngủ lớn riêng tư, ban công thoáng sáng.
-Chỉ 7.85 tỷ cho 55m² nhà mới (Cực hiếm trong phân khúc).
-Sổ đỏ chính chủ, vuông đẹp, sẵn sàng giao dịch trong ngày.
-Vừa ở vừa chờ mở đường, lợi nhuận nhìn thấy ngay trước mắt.
-💰 Giá: 7.85 Tỷ (Có thương lượng cho khách quyết nhanh).
-📞 Alô ngay xem nhà 24/7: *** (Đạt)</t>
-        </is>
-      </c>
-      <c r="R102" t="n">
         <v>131942699</v>
       </c>
     </row>
@@ -8435,23 +6005,6 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>21.058859</v>
-      </c>
-      <c r="O103" t="n">
-        <v>105.85839</v>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>bán nhà dân xây</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Bán nhà trong ngõ cách đường oto tránh 10 m</t>
-        </is>
-      </c>
-      <c r="R103" t="n">
         <v>131922421</v>
       </c>
     </row>
@@ -8506,31 +6059,6 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>21.059677</v>
-      </c>
-      <c r="O104" t="n">
-        <v>105.911804</v>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>biệt thự khu đô thị Việt Hưng, Long Biên mặt phố kinh doanh</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>chính chủ cần bán biệt thự 200m2 kdt Viêt Hưng, Long Biên
-Biệt Thự mặt phố kinh doanh tốt
-200m2 mặt tiền 12m
-gần VinHome, Công viên Long Biên
-Trường học chất lượng cao MarieCurie, Chu Văn An, Bristit, Vinschool, Nguyễn Gia Thiều...
-Bán kính 3km AeonLong Biên, BigC, VinCom Plaza...
-Cần Bán nhanh trong 1 tháng để chuyển mục đích sử dung tiền.
-📞 Lhe Hotline *** ( e Phong )
-#phucloi #nhadep #nhaphucloi #muanhahanoi #datphucloi #BĐS #bdslongbien #longbien #nhalongbien #nhadatphucloi #đấtphanlophucloi #đấtphanloLongBien #bdsPhucLoi #VinhomeLongBien #VinhomeRiverside
-#BdsBacNinh #bdsTuSon</t>
-        </is>
-      </c>
-      <c r="R104" t="n">
         <v>131911061</v>
       </c>
     </row>
@@ -8585,29 +6113,6 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>21.04877</v>
-      </c>
-      <c r="O105" t="n">
-        <v>105.89621</v>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ VŨ ĐỨC THẬN VIỆT HƯNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ VŨ ĐỨC THẬN VIỆT HƯNG LONG BIÊN HÀ NỘI.
-+ Nhà 3 tầng cũ 
-+ Diện tích ; 64m2- MT 6,9m
-+ Hướng tây
-+ hiện đang cho thuê dòng tiền đều hàng tháng 
-+ Đường trước nhà 12m - vỉa hè đường thông tứ ngả 
-+ Tiện ích ; nhà nằm trên mặt phố lớn của long biên kinh doanh sầm uất ngày và đêm - nhà lại gần trường các cấp - chợ - TTTM - và khu vực dân trí cao - mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; *** - Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R105" t="n">
         <v>127171113</v>
       </c>
     </row>
@@ -8662,29 +6167,6 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O106" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng - thang máy nhập khẩu 
-+ Diện tích ; 38m2- MT 3,8m
-+ Nội thất đầy đủ 
-+ Hướng đông nam - quanh năm thoáng mát
-+ Đường trước nhà 3m - ô tô vào nhà - nhà cách 50m là ra tới mặt phố thạch bàn 
-+ Tiện ích ; nhà nằm giữa trung tâm hành chính phường - rùi trường các cấp - TTTM -AEON -Long biên - và khu vực đông dân cư - chỉ mất đúng 10 phút lái xe là sang tới trung tâm thành phố hà nội rùi.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R106" t="n">
         <v>130209609</v>
       </c>
     </row>
@@ -8739,28 +6221,6 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O107" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng mới - thang máy nhập khẩu 
-+ Diện tích ; 36m2- MT 4,6m
-+ Hướng đông bắc 
-+ Hiện nhà đang trong quá trình hoàn thiện 
-+ Tiện ích ngập tràn ; nhà nằm trên mặt phố lớn nhất long biên - kinh doanh sầm uất ngày và đêm - nhà lại ngay cạnh TTTM- AEON -Long biên - euif trường các cấp - và khu vực dân trí cao- chỉ mất tầm 7 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R107" t="n">
         <v>130351826</v>
       </c>
     </row>
@@ -8815,29 +6275,6 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>21.064445</v>
-      </c>
-      <c r="O108" t="n">
-        <v>105.90932</v>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ LIỀN KỀ VIỆT HƯNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ LIỀN KỀ VIỆT HƯNG LONG BIÊN HÀ NỘI.
-+ Nhà 4 tầng liền kề kiên cố
-+ Diện ích ; 198m2- MT 12m
-+ Nội thất cơ bản 
-+ Hướng tây bắc
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả
-+ Tiện ích ngập tràn ; nhà nằm giữa trung tâm phường - rùi trường các cấp - vườn hoa công viên TTTM - và khu vực dân trí cao- chỉ mất đúng 15 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R108" t="n">
         <v>131319869</v>
       </c>
     </row>
@@ -8892,29 +6329,6 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O109" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng - thang máy nhập khẩu 
-+ Diện tích ; 50m2- MT 5m
-+ Nội thất đẹp
-+ Nhà hướng đông 
-+ Đường trước nhà 2,5m - cách 20m ra đường ô tô tránh - xe nhỏ vào nhà 
-+ Tiện ích ; nhà cạnh chợ - hồ công viên - trường cấp 2-3 - và khu vực đông dân cư- nhà cách TTTM -AEON -Long biên 500m - và mất 10 phút lái xe là sang tới trung tâm thành phố hà nội rùi.
-+ Liên hệ ;***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.À NỘI.</t>
-        </is>
-      </c>
-      <c r="R109" t="n">
         <v>131270233</v>
       </c>
     </row>
@@ -8969,28 +6383,6 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>21.030083</v>
-      </c>
-      <c r="O110" t="n">
-        <v>105.88076</v>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ LIỀN KỀ THẠCH BÀN LONG BIÊN.</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ LIỀN KỀ THẠCH BÀN LONG BIÊN.
-+  Nhà xây thô 4 tầng 1 tum 
-+ Diện tích ; 130m2- MT 7,8m  ( nhà 2 mặt tiền trước và sau )
-+ Hướng tây bắc 
-+ Đường trước nhà 12m- vỉa hè đường thông tứ ngả
-+ Tiện ích ngập tràn ; nhà nằm giữa trung tâm hành chính phường - nhà lại gần trường các cấp - TTTM -AEON - Long biên - và khu vực dân trí cao- chỉ mất 10 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R110" t="n">
         <v>131269730</v>
       </c>
     </row>
@@ -9045,28 +6437,6 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>21.045307</v>
-      </c>
-      <c r="O111" t="n">
-        <v>105.86899</v>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Bán nhà Bồ Đề( Ngọc Lâm) - gần cầu - gần ô tô - Long Biên Hà Nội</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>Bán nhà Ngọc Lâm -  sát cầu Chương Dương - 5ph sang phố cổ 
-Diện tích: 30m2 x 6 tầng - 4pn
-Giá: 9.3 tỷ
-Nhà đẹp xây mới 
-Vị trí ngay đầu cầu Chương Dương, gần ô tô, chỉ 5ph sang phố cổ.
-Sổ đỏ vuông vắn, cất két giao dịch ngay
-Liên hệ: Ms Lan</t>
-        </is>
-      </c>
-      <c r="R111" t="n">
         <v>131161945</v>
       </c>
     </row>
@@ -9121,27 +6491,6 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>21.02974</v>
-      </c>
-      <c r="O112" t="n">
-        <v>105.91316</v>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ THẠCH BÀN 60M 5 TẦNG THANG MÁY- SÂN RỘNG- SIÊU THOÁNG</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>🟠✅BÁN NHÀ THẠCH BÀN 60M 5 TẦNG CÓ THANG MÁY- SÂN RỘNG- NGAY GẦN MẶT PHỐ THẠCH BÀN- 2 MẶT THOÁNG- GIÁ HƠN 10 TỶ (CÓ THƯƠNG LƯỢNG)
-🔶Diện tích 60m 5 tầng thiết kế thang máy, Sân rộng rãi tha hồ để xe, trồng cây.
-Nhà lô góc 2 mặt thoáng nên rất thoáng sáng, có sân trước để xe.
-🎉Vị trí vô cùng thuận tiện, Ô tô đỗ cổng, cách vài bước ra mặt phố Thạch Bàn sầm uất ngày đêm. Cách Aeon Mall cầu Vĩnh Tuy 500m. Trường học, Công viên quán xá tấp nập ngay cạnh nhà.
-🎁Giá hơn 10 tỷ, sổ đỏ chính chủ, ko bị quy hoạch. Có hỗ trợ vay vốn ngân hàng lên tới 30 năm
-☎️LH  Em Hiệp để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R112" t="n">
         <v>131737914</v>
       </c>
     </row>
@@ -9196,32 +6545,6 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O113" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Bán nhà đối diện Aeon Mall Long Biên, ô tô vào nhà</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ 2 MẶT TIỀN – 5 TẦNG – FULL NỘI THẤT – Ô TÔ NGỦ TRONG NHÀ – CHÍNH CHỦ
-Thông tin chi tiết:
- • Nhà 2 mặt tiền thoáng vĩnh viễn, đón ánh sáng tự nhiên
- • nhà xây thiết kế 5 tầng chắc chắn, thiết kế hiện đại
- • Full nội thất cao cấp, chỉ việc xách vali về ở
- • Ô tô vào tận nhà, giao thông cực kỳ thuận tiện.
-Cách Aeon Mall Long Biên vài bước chân, khu vực phát triển mạnh
- • Ngay chân cầu Vĩnh Tuy, di chuyển cực nhanh
- • Chỉ 10 phút sang phố cổ / trung tâm
- • Gần chợ, trường học, tiện ích đầy đủ, khu dân trí cao
-Giá bán: nhỉnh 12 tỷ (có thương lượng cho khách thiện chí)</t>
-        </is>
-      </c>
-      <c r="R113" t="n">
         <v>131931379</v>
       </c>
     </row>
@@ -9276,32 +6599,6 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>21.058416</v>
-      </c>
-      <c r="O114" t="n">
-        <v>105.89463</v>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>siêu phẩm mời achi xem qua</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Chính chủ cần bán nhà ngõ 161 hoa lâm
-1. Mặt tiền gần 4m , rộng 35m2( thêm 16m2 sử dụng chung) gồm 5 tầng, 3 phòng ngủ(đều có ban công), 4 vệ sinh, 1 phòng khách,1 tầng có phòng thờ sân thượng
-2. Nhà đầy đủ nội thất giường tủ, điều hoà, nóng lạnh ( riêng tầng 4 phòng ngủ gia chủ có thể tự thiết kế theo ý mình phòng tắm vệ sinh đủ thiết bị)
-3. khoảng 50m ra ngõ oto tránh xe máy
-4. Nhà 2 mặt tiền thông thoáng gần chợ gần tasco mall gần trường học bệnh viện
-Giá: 9.xx tỷ có thương lượng
-lh zl
-***
-***
-hoặc ib trực tiếp mess</t>
-        </is>
-      </c>
-      <c r="R114" t="n">
         <v>131930297</v>
       </c>
     </row>
@@ -9356,37 +6653,6 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>21.043814</v>
-      </c>
-      <c r="O115" t="n">
-        <v>105.872314</v>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>HÀNG HIẾM GIA THUỴ-6 TẦNG THANG MÁY FULL ĐỒ</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🏡 TIN 2 – HÀNG HIẾM GIA THỤY – 6 TẦNG THANG MÁY FULL ĐỒ
-💥 Siêu phẩm không có căn thứ 2
-🔥 Nhà đẹp long lanh – thiết kế hiện đại
-📍 Ngõ thông ô tô
-🚗 Đi lại cực thuận tiện
-💎 Điểm nổi bật:
-* Nhà xây mới 100%
-* Nội thất cao cấp, sang xịn
-* Phòng nào cũng có ánh sáng tự nhiên
-🏠 Công năng chuẩn:
-* 5PN rộng rãi
-* Phòng khách + bếp cực đẹp
-* Phòng thờ + sân phơi
-📈 Tiềm năng tăng giá cực tốt khu Gia Thụy – Long Biên
-🌹 Chủ nhà thiện chí – sẵn sàng giao dịch nhanh</t>
-        </is>
-      </c>
-      <c r="R115" t="n">
         <v>131890115</v>
       </c>
     </row>
@@ -9441,27 +6707,6 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>21.016344</v>
-      </c>
-      <c r="O116" t="n">
-        <v>105.91444</v>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Cổ Linh- Thạch Bàn. bán nhà 5 tầng mới koong, hàng hiếm giá hời !</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>CC cần bán nhà xây mới tinh tại Cổ Linh- Thạch Bàn, vị trí đẹp, dân cư đông đúc, an ninh tốt. Nhỏ tiền, siêu hiếm quanh khu vưc.
-+ Diện tích 30m x5 tầng với 3 PN, thiết kế hiện đại, công năng tối ưu, nội thất cơ bản, xịn sò, chỉ việc xách vali về ở.
-+ Nhà gần chợ, gần hồ &amp; công viên, cách 10m ra oto . Đi lại thuận tiện, 5 phút ra AEON vui chơi mua sắm thỏa thích.
-+ Phù hợp cho gia đình trẻ hay gia đình nhỏ, vừa ở vừa đầu tư giữ tiền.
-+ Giá chỉ 6,6 tỷ- có TL, sổ đỏ cất két.
-Xem nhà miễn phí alo Dũng - Chuyên Bđs Long Biên, nhiều quỹ căn ngon bất ngờ .</t>
-        </is>
-      </c>
-      <c r="R116" t="n">
         <v>131800493</v>
       </c>
     </row>
@@ -9516,28 +6761,6 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>21.022837</v>
-      </c>
-      <c r="O117" t="n">
-        <v>105.88859</v>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>ÁN NHÀ MỚI TINH - BÁT KHỐI, TƯ ĐÌNH - VỊ TRÍ ĐÓN SÓNG CẦU TR.HƯNG ĐẠO</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>Cc cần bán căn nhà mới tinh tại Bát Khối- Tư Đình, khu vực phát triển mạnh,  vài bước chân ra cầu Trần Hưng Đạo, tiềm năng tăng giá cao.
- Diện tích 53m x 5 tầng, thiết kế hiện đại với 4 phòng ngủ, 2 mặt thoáng vĩnh viễn, ánh sáng ngập tràn và thông thoáng.
-+ Trang bị thang máy nhập khẩu chạy vèo vèo, oto 7chỗ đỗ xịch cửa, cực kỳ tiện lợi sinh hoạt.
-+ Vị trí đẹp, chỉ vài trăm mét ra đón cầu Trần Hưng Đạo đang xây dựng, kết nối trung tâm phố cổ nhanh chóng.
-+ Nhà Full nội thất xịn sò: giường tủ, bàn ghế đủ cả - mua về ở ngay đón tết
-+ Giá bán nhanh:11,99 tỷ có TL với khách thiện chí.
-Xem nhà miễn phí alo Dũng- Chuyên Bđs Long Biên, nhiều quỹ căn ngon bất ngờ !</t>
-        </is>
-      </c>
-      <c r="R117" t="n">
         <v>131801545</v>
       </c>
     </row>
@@ -9592,27 +6815,6 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>21.016344</v>
-      </c>
-      <c r="O118" t="n">
-        <v>105.91444</v>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>CỔ LINH -THẠCH BÀN.BÁN NHÀ MỚI TINH - GẦN HỒ C.VIÊN, TT THỂ THAO YTE</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>Cc cần bán căn nhà mới tinh , nhà đẹp ,vị trí đẹp tại Thạch Bàn . Giá cực hợp lý.
-+Diện tích 50m x6 tầng, mặt tiện rộng 10m, thiết kế bề thế, sân trước nhà cực rộng, thoáng mát ở sướng, oto đỗ xịch cổng, chỉ 1 nhà ra oto tránh.
-+ Thang máy nhập khẩu chạy vèo vèo, full nội thát cao cấp: giường tủ , bàn ghế xịn sò- vào ở ngay.
-+ Khu vực hiếm nhà bán, xung quanh là Hồ công viên dạo bộ- Chợ- trường học - trung tâm thể thao và TT y tế phường,  tiện ích ngập tràn.
-+ Giá bán nhanh chỉ 11 tỷ - có ra lộc. phù hợp để ở hoặc đầu tư giữ tiền.
-xem nhà miến phí Liên hệ Dũng - chuyên Bđs Long Biên, nhiều qũy căn ngon bất ngờ !</t>
-        </is>
-      </c>
-      <c r="R118" t="n">
         <v>131802311</v>
       </c>
     </row>
@@ -9667,28 +6869,6 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>21.00597</v>
-      </c>
-      <c r="O119" t="n">
-        <v>105.89656</v>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ MỚI TINH, VIEW HỒ 30HA CỰ KHỐI, LONG BIÊN - GIÁ CỰC HỜI .</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>Cc cần bán căn nhà mới tinh tại Cự Khối- Long Biên, view hồ 30ha.  Khu vực đang phát triển mạnh, dân cư đông đúc, an ninh tốt. Giá thu hồi vốn. 
-+ Diện tích 37m x 5 tầng, thiết kế hiện đại, công năng tối ưu cho gia đình trẻ
-+ Vị trí nhà gần chợ, gần trường học các cấp, gần hồ điều hòa 30ha đang thi công rầm rộ, tương lai có không gian sống trong lành mát mẻ quanh năm.
-+ Nhà xây mới chắc chắn, VF3 vào nhà, hàng cực hiếm trong tầm tiền. 
-+ Giá rẻ bán nhanh , chỉ còn 7,1 tỷ. Cơ hội hiếm có, 
- Mua ở hoặc đầu tư giữ tiền với căn nhà này đều rất phù hợp
-Liên hệ Dũng sớm để xem nhà miễn phí ag.</t>
-        </is>
-      </c>
-      <c r="R119" t="n">
         <v>130715733</v>
       </c>
     </row>
@@ -9743,39 +6923,6 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>21.022387</v>
-      </c>
-      <c r="O120" t="n">
-        <v>105.89911</v>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>chính chủ em bán nhà 8 tầng xây mới ,79,1m2 , thang máy , lô góc</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💶💶💶chính chủ em  bán căn nhà 8 tầng x 79,1m2 , số 51 ngõ 405 bát khối, phường long biên , hà nội , đường thông trải nhựa rộng 5m 
-☎️☎️☎️liên hệ : *** em Tuấn Dương
-🔑 nhà xây 8 tầng, thang máy 630kg , full nội thất , lô góc 
-☺️ mặt tiền = hậu rộng 5,1 m , vuông vắn không lỗi phong thuỷ 
-🌅hướng nhà : Đông nam ( mát mẻ quanh năm )
-🚘🚘🚘ngõ trước nhà rộng 5 m thông ô tô tránh nhau , thông ra bát khối và aeon long biên , đường cổ linh 
-🔑thiết kế :
-* tầng 1 : kinh doanh , gara để được 3 ô tô 
-* tầng 2 : phòng khách , bếp , vệ sinh ( full nội thất điều hoà , bàn ghế , thiết bị bếp , tivi , tủ lạnh …
-* tầng 3,4,5,6 : 4 phòng ngủ mater rộng ( full nội thất giường tủ , điều hoà âm trần ) 
-* tầng 7 : phòng thờ, sân phơi ( có mái tôn , hàng rào bảo vệ ) 
-* tầng 8 : tum , sân chơi , trồng cây 
-🔑nhà xây độc lập , móng cọc bê tông chắc chắn 
-📕sổ đỏ chính chủ , không tranh chấp , không quy hoạch, sẵn sàng sang tên 
-💶hỗ trợ ngân hàng 70% giá trị nhà , trả góp từ 1 đến 30 năm, lãi suất ưu đãi .
-💶giá bán : 21,6tỷ ( có thương lượng) 
-☎️☎️☎️liên hệ chính chủ  ***</t>
-        </is>
-      </c>
-      <c r="R120" t="n">
         <v>131201136</v>
       </c>
     </row>
@@ -9830,27 +6977,6 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>21.010485</v>
-      </c>
-      <c r="O121" t="n">
-        <v>105.90943</v>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Nhà ở phố Xuân Đỗ, Cự Khối, Long Biên, Hà Nội</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: NH Land mở bán căn lô góc 131/9 phố Xuân Đỗ 32.5m 5 tầng 1 tum thang máy, full nội thất, ô tô đỗ cửa ngõ thông thẳng ra hồ điều hoà lớn nhất Long Biên. 
-- Vị trí cực đẹp 100m có hồ điều hoà, chợ dân sinh, trường học các cấp
-- Sổ đỏ chính chủ, hỗ trợ vay bank 
-- Mua sớm được giá tốt
-- Giá bán 9.1 tỷ có thương lượng</t>
-        </is>
-      </c>
-      <c r="R121" t="n">
         <v>131922532</v>
       </c>
     </row>
@@ -9905,32 +7031,6 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>21.062166</v>
-      </c>
-      <c r="O122" t="n">
-        <v>105.91639</v>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>HIẾM THẬT SỰ  NHÀ 40M KẺ TẠNH GIANG BIÊN VIỆT HƯNG 3 TẦNG CHỈ 6 TỶ</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>HIẾM THẬT SỰ  NHÀ 40M KẺ TẠNH GIANG BIÊN VIỆT HƯNG 3 TẦNG CHỈ 6 TỶ 
-Nhà đẹp gần như KHÔNG có đối thủ trong phân khúc:
-Khu vực kinh doanh tấp nập ngày đêm
-Nhà 3 tầng  3PN  ở ngay hoặc khai thác luôn
-Nằm đúng khu dân cư đông đúc phường Việt Hưng
-Gần chợ, trường học cấp 1,2,3
-5 phút ra Ngô Gia Tự  trục huyết mạch đi nội đô
-Phù hợp mọi mô hình: ở hoặc cho thuê
- Sổ đỏ vuông vắn  pháp lý sạch  sẵn sàng giao dịch ngay
- Giá chào: 6 tỷ (có thương lượng cho khách thiện chí)
- Liên hệ: Tuấn Thổ Cư  *** (Zalo/Call)</t>
-        </is>
-      </c>
-      <c r="R122" t="n">
         <v>131902599</v>
       </c>
     </row>
@@ -9985,27 +7085,6 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>21.055147</v>
-      </c>
-      <c r="O123" t="n">
-        <v>105.90521</v>
-      </c>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>Nhà Việt Hưng 32m x 5 tầng full nội thất hơn 6 tỷ</t>
-        </is>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>🏠🏕️Nhà Việt Hưng hàng xóm Vinhomes oto đỗ cổng giá 6,85 tỷ.
-🏙️Nhà xây mới sân 30m2 chung 2 nhà 15m ra đường oto.
-⚓Tầng: 1 phòng khách và bếp + nhà vệ sinh.
-⚓Tầng 2,3,4: mỗi tầng 1 phòng ngủ và vệ sinh đã đầy đủ nội thất.
-⚓Tầng 5 phòng thờ và sân phơi.
-☎️📞LH  Xuân Vinh xem nhà 24/7.</t>
-        </is>
-      </c>
-      <c r="R123" t="n">
         <v>131874256</v>
       </c>
     </row>
@@ -10060,32 +7139,6 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O124" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Bán nhà mặt ngõ to Tư Đình, 52m2 x 6 tầng thang máy, xe 7 chỗ vào nhà</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cần bán nhà mặt ngõ to phố Tư Đình, Long Biên, Hà Nội:
-- Nhà 52m2 x 6 tầng mới, đẹp, thang máy
-- Ngõ to ô tô 7 chỗ vào nhà, nhà có Gara ô tô.
-- Ngõ ngắn cách trục chính khoảng 20m
-- Nhà dân xây riêng biệt, độc lập
-- Full nội thất cao cấp.
-- Vị trí trung tâm cách chợ khoảng 100m, mầm non cấp 1, 2 khoảng 300m
-- Pháp lý: SĐCC
-- Giá bán: 16.3 tỷ (có thương lượng)
-- Liên hệ xem nhà: *** Mr Huấn, xin cảm ơn!
-</t>
-        </is>
-      </c>
-      <c r="R124" t="n">
         <v>131894499</v>
       </c>
     </row>
@@ -10140,30 +7193,6 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>21.05286</v>
-      </c>
-      <c r="O125" t="n">
-        <v>105.92033</v>
-      </c>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Nhà Đẹp TT Phúc Lợi Long Biên</t>
-        </is>
-      </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Nhà Đẹp . Giá đầu Tư. Tặng nội thất.
-🌹 TT Phúc Lợi. Long Biên. 
-Dt 45m2mt 4.8m. 5 tầng. 3 ngủ. Nội thất đủ đầy. 
-Không gian tối ưu. Gia đình ở thoải mái 
-Ngõ nông . Di chuyển thuận lợi 
-Bán kính 300m. Tiện ích bao quanh 
-Zá mong muốn 7.15 tỷ
-Lh xem nhà ***</t>
-        </is>
-      </c>
-      <c r="R125" t="n">
         <v>131914431</v>
       </c>
     </row>
@@ -10218,27 +7247,6 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O126" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Nhà Mặt Phố Thạch Bàn Cách 50m 5 Tầng Ngõ Ít Nhà – Nhỉnh 6 tỷ</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>-	Diện tích 32m2/ 5 tầng
--	Mặt tiền đẹp, hướng Đông Nam
--	Đường trước nhà 2.5m, 20m ra ngõ thông ô tô, ngõ nông đẹp ít nhà
--	Thiết kế 4 tầng 1 tum, 3 phòng ngủ đầy đủ công năng
--	Sổ đỏ chính chủ, ko tranh chấp quy hoạch
-Phở bò/zép lào: Huy Định *** xem nhà và tư vấn miễn phí 24/7</t>
-        </is>
-      </c>
-      <c r="R126" t="n">
         <v>127352133</v>
       </c>
     </row>
@@ -10293,32 +7301,6 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O127" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Bán nhà Bồ Đề, 45m2 x 4 tầng đẹp, MT: 4m, ngõ ô tô vào</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cần bán nhà Bồ Đề, Hà Nội:
-- Ngõ trước nhà rộng ô tô vào thoải mái.
-- Nhà 2 mặt thoáng
-- Cách trục chính container tránh khoảng 30m.
-- Nhà 45m2 x 4 tầng đẹp, MT 4m vuông vắn, full nội thất cao cấp...
-- Vị trí trung tâm cách cầu Chương Dương khoảng 1.3km
-- Khu dân cư yên tĩnh, dân trí cao, an ninh đảm bảo.
-- Pháp lý: SĐCC chuẩn chỉ
-- Giá bán: 8 tỷ 650tr (có thương lượng).
-- Liên hệ xem nhà: *** Mr Huấn (41 tuổi), xin cảm ơn!
-</t>
-        </is>
-      </c>
-      <c r="R127" t="n">
         <v>131873785</v>
       </c>
     </row>
@@ -10373,34 +7355,6 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>21.03543</v>
-      </c>
-      <c r="O128" t="n">
-        <v>105.9021</v>
-      </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>BÁN BIỆT THỰ KHU ĐÔ THỊ SÀI ĐỒNG – LONG BIÊN -GIÁ 82 TỶ</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>📍 Địa chỉ: KĐT Sài Đồng – Phúc Lợi, Long Biên, Hà Nội
-📐 Diện tích: ~302,8m² – Lô đẹp, khu NO5
-THÔNG TIN NỔI BẬT
-Biệt thự vị trí đẹp trong khu đô thị quy hoạch đồng bộ, dân trí cao
-Khu vực yên tĩnh, gần công viên – phù hợp ở và đầu tư lâu dài
-Hạ tầng hoàn thiện, đường rộng, ô tô vào tận cửa
-KẾT NỐI GIAO THÔNG THUẬN LỢI
-Gần cầu Vĩnh Tuy – di chuyển nhanh vào trung tâm
-Kết nối thuận tiện các khu: Vinhome Riverside, Aeon Mall Long Biên
-Gần trường học, ngân hàng, khu thương mại
-PHÁP LÝ
-Sổ đỏ riêng, pháp lý rõ ràng
-Sẵn sàng giao dịch ngay</t>
-        </is>
-      </c>
-      <c r="R128" t="n">
         <v>131878850</v>
       </c>
     </row>
@@ -10455,39 +7409,6 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>21.041388</v>
-      </c>
-      <c r="O129" t="n">
-        <v>105.90136</v>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>chính chủ bán nhà 35m2 x 6 tầng số 23C phố mai phúc , thanh máy</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🏡🏛️🏝️ BÁN NHÀ ĐẸP XÂY MỚI 6 Tầng x 35/40m2 , THANG MÁY 450 kg , full nội thất, ô tô cách nhà 20m , giá  9 tỷ 280 triệu ( có thương lượng)
-☎️☎️☎️liên hệ *** em Tuấn Dương ( zalo ) 
-🌉Địa Chỉ  số 23 C phố mai phúc, phúc đồng ,Long biên , ngay cổng công an giao thông cũ , cách đường 2 ô tô tránh nhau chỉ 15m  , ô tô dừng đỗ ngày đêm  
-📕 Diện tích 35m2 , từ tầng 2 40m2 , mặt tiền 5,5m hậu 5,5m vuông vắn 
-🏤🏗️ Nhà xây mới , xây 6 tầng, thang máy 450kg nhập khẩu 
-✍🏻Tầng 1: vệ sinh, bếp full bàn ghế , tủ bếp 
-✍🏻Tầng 2 : phòng khách , phòng sinh hoạt chung 
-tặng bàn ghế sofa , vách tivi sang trọng 
-✍🏻Tầng 3,4,5 : 3 phòng ngủ rộng full nội thất giường tủ, vệ sinh khép kín 
-✍🏻Tầng 6: phòng thờ rộng, sân phơi ( có mái tôn , hàng rào bảo vệ ) 
-💥💥💥 Thang máy 450 kg, đã kiểm định , nhập khẩu 
-🛣️🚖🚚 Đường trước nhà rộng 3 m  
-📔Pháp lý: SĐCC, GPXD, sẵn sàng sang tên 
-💸💸💸 Giá bán : 9 tỷ280 triệu Hỗ trợ vay NH từ 1-20 năm.
-💶hỗ trợ chứng minh thu nhập cho các khách hàng không có bảng lương, lao động tự do 
-☎️liên hệ : *** em Tuấn Dương ❤️❤️❤️Trân trọng cảm ơn!!!
-🌹🌹🌹có hoa hồng cho anh chị em giới thiệu 🌹🌹🌹</t>
-        </is>
-      </c>
-      <c r="R129" t="n">
         <v>131703123</v>
       </c>
     </row>
@@ -10542,38 +7463,6 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O130" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>chính chủ bán nhà 6 tầng x 51,9m2 , ngõ 206 cổ linh ( 353 bát khối )</t>
-        </is>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💶💶💶chính chủ em bán căn nhà mới 6 tầng x 51,9m2 , thang máy , đường thông rộng 4m , tại số 17A ngõ 353 đường bát khối ( ngõ 206 cổ linh ) long biên 
-📕Diện tích 51,9m2 , xây 6 tầng , full nội thất 7 phòng ngủ 
-☺️ mặt tiền = hậu 3,6m , vuông vắn không lỗi phong thủy 
- 🌅hướng Đông bắc ( tây tứ trạch ) trước nhà là biệt thự thoáng sáng 
-✍🏻thiết kế : 
-_ tầng 1 : gara ô tô 7 chỗ , phòng bếp 
-_ tầng 2 : phòng khách , 1 phòng ngủ , vệ sinh 
-_ tầng 3,4,5 : 6 phòng ngủ ,3 vệ sinh 
-_ tầng 6 : phòng thờ, sân phơi 
-* thanh máy nhập khẩu 450kg , chạy êm ru 
-🚘🌉ngõ thông ra cổ linh , bát khối , aeon , ô tô 7 chỗ vào nhà 
-📕sổ đỏ chính chủ , không tranh chấp , không quy hoạch 
-🌉vị trí gần cầu vĩnh tuy cách 300m , aeon 200m , đường đê bát khối 100m , giao thông thuận tiện , đủ tiện ích 
-💶giá bán : 14,X tỷ (có thương lượng )
-🌹có hoa hồng cho anh chị em giới thiệu 
-☎️liên hệ chính chủ *** , *** em Tuấn Dung</t>
-        </is>
-      </c>
-      <c r="R130" t="n">
         <v>131050808</v>
       </c>
     </row>
@@ -10628,29 +7517,6 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>21.003109</v>
-      </c>
-      <c r="O131" t="n">
-        <v>105.90296</v>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ XUÂN KHÔI – LONG BIÊN | 45,9m² | GIÁ RẺ</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>Cần bán nhà ngõ phố Xuân Khôi – P. Long Biên, Hà Nội
-Diện tích: 45,9m², sổ đỏ chính chủ
-Vị trí: ngoài đê, pháp lý rõ ràng, bao check quy hoạch
-Gần Aeon Mall Long Biên, Bát Tràng, Ecopark… di chuyển thuận tiện
-Khu dân cư yên tĩnh, phù hợp ở lâu dài, phù hợp gia đình nhỏ, kinh tế ít hoặc đầu tư giữ tiền cho thuê.
-💰 Giá bán: 3,3 tỷ (có thương lượng)
-📞 Liên hệ: ***
- (chính chủ)</t>
-        </is>
-      </c>
-      <c r="R131" t="n">
         <v>131623359</v>
       </c>
     </row>
@@ -10705,34 +7571,6 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O132" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>💎 CỰC HIẾM - LÔ GÓC NGỌC THỤY - FULL NỘI THẤT THÔNG MINH - CHỈ 5.6 TỶ</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>💎 CỰC HIẾM - LÔ GÓC NGỌC THỤY - FULL NỘI THẤT THÔNG MINH - CHỈ 5.6 TỶ
-VỊ TRÍ VÀNG - SỐNG TIỆN NGHI
-• Vị trí trung tâm, lô góc 2 mặt thoáng, ngõ rộng thênh thang, giao thông cực kỳ thuận tiện.
-• Tiện ích: Bước chân ra cửa là không thiếu thứ gì; khu vực dân trí cao, an ninh tuyệt đối, hàng xóm văn minh.
-THIẾT KẾ HIỆN ĐẠI – TỐI ƯU CÔNG NĂNG (5 TẦNG)
-• Tầng 1: Không gian mở sang trọng với Phòng khách &amp; Bếp hiện đại.
-• Tầng 2: Master suite đẳng cấp, ban công rộng, bồn tắm xịn xò thư giãn.
-• Tầng 3, 4: Mỗi tầng 1 phòng ngủ rộng, tràn ngập ánh sáng tự nhiên, vệ sinh khép kín.
-• Tầng 5: Phòng thờ trang nghiêm &amp; Sân phơi Chill, view toàn cảnh cực đẹp.
-NỘI THẤT THÔNG MINH: Nhà trang bị đầy đủ đồ dùng hiện đại, thiết kế tinh tế, khách mua chỉ việc xách vali về ở ngay.
-PHÁP LÝ: Sổ đỏ chính chủ, sẵn sàng giao dịch.
-💰 Giá chào: 5.6 tỷ (Có thương lượng).
-📞 Liên hệ ngay Đạt: *** (Tư vấn và xem nhà miễn phí 24/7).</t>
-        </is>
-      </c>
-      <c r="R132" t="n">
         <v>131897624</v>
       </c>
     </row>
@@ -10787,24 +7625,6 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O133" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>7 tầng thang máy - khu TĐC Thạch Bàn full nội thất - để ở &amp; kinh doanh</t>
-        </is>
-      </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>Nhà phân lô khu TĐC, Thạch Bàn, gần chợ Thạch Bàn, Aeon mall, lên cầu Vĩnh Tuy chỉ vài phút di chuyển
-Diện tích 60m2, mặt tiền 5m, xây 7 tầng thang máy - full nội thất siêu đẹp
-☎️ Liên hệ Em Lan  làm việc chính chủ.</t>
-        </is>
-      </c>
-      <c r="R133" t="n">
         <v>131572356</v>
       </c>
     </row>
@@ -10859,27 +7679,6 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>21.028515</v>
-      </c>
-      <c r="O134" t="n">
-        <v>105.91935</v>
-      </c>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>Nhà Phố , Long Biên</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 Nhà Phố Long Biên, Ô TÔ ngủ trong nhà!
-🔥 Lô Góc, kinh doanh hoặc ở quá hợp lý.
-🔥 Vị trí : Khu đô thị Sài Đồng, Vinhome Riveside . trường học c1,c2, c3.
-✅ Nhà xây mới , sổ đỏ đẹp, giao dịch trong ngày
-☎️ Alo em để về số 1 ạ</t>
-        </is>
-      </c>
-      <c r="R134" t="n">
         <v>131894503</v>
       </c>
     </row>
@@ -10934,32 +7733,6 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>21.04649</v>
-      </c>
-      <c r="O135" t="n">
-        <v>105.84058</v>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>Bán nhà ngõ 137 Xuân Đỗ, 30m nhà mới 5 tầng, 3PN, giá chỉ 5,9 tỷ.</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nhà 5 tầng mới xây, full nội thất cực đẹp, chỉ cần xách vali về ở.
-Căn nhà có diện tích 30m2, từ tầng 2 diện tích 33m2, thoáng trước và sau. 
-Vị trí đẹp, khu vực mới mở đường, phát triển từng ngày. Nhà gần phố ô tô tránh, giao thông rất thuận tiện.
-Chi tiết thông số căn nhà:
-- Tầng 1: Phòng Khách + Bếp
-- Tầng 2, 3, 4: Mỗi tầng 1 phòng ngủ rộng + WC
-- Tầng 5: Phòng thờ, Bếp, Sân phơi
-Pháp lý: Sổ đỏ
-Giá: 5,9 tỷ VNĐ, pháp lý Sổ đỏ sẵn sàng trao tay.
-Liên hệ ngay em Thành - *** để được tư vấn, xem nhà miễn phí. 
-</t>
-        </is>
-      </c>
-      <c r="R135" t="n">
         <v>131891739</v>
       </c>
     </row>
@@ -11014,31 +7787,6 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O136" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>NHÀ NGỌC THỤY – LONG BIÊN – 45M – THANG MÁY – FULL NỘI THẤT – GIÁ 9 TỶ</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: NHÀ NGỌC THỤY – LONG BIÊN – 45M – THANG MÁY – FULL NỘI THẤT – GIÁ 9 TỶ
-Nhà trong đê khu Mipec Riverside Long Biên, vị trí dân cư đông đúc, tiện ích đầy đủ
-Diện tích 45m², xây 4.5 tầng chắc chắn, thiết kế 4 phòng ngủ, full nội thất dọn đến ở ngay
-Ngõ trước nhà rộng 2.5m, cách 30m ra ô tô tránh dừng đỗ ngày đêm
-Khu vực yên tĩnh, phù hợp ở gia đình hoặc cho thuê
-Kết nối nhanh sang phố qua cầu, di chuyển thuận tiện
-Giá chào khoảng 9 TỶ
-Sổ đỏ chính chủ
-Liên hệ  Minh BĐS - Đông Hà Nội</t>
-        </is>
-      </c>
-      <c r="R136" t="n">
         <v>131891051</v>
       </c>
     </row>
@@ -11093,29 +7841,6 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>21.04023</v>
-      </c>
-      <c r="O137" t="n">
-        <v>105.87803</v>
-      </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>nhà ngõ thoáng ngay chân cầu vượt hồng tiến , hoàng như tiếp</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Chính chủ cần bán ( gặp chủ nhà)
-Nhà ngõ 72 Hoàng Như Tiếp, xe 7 chỗ chạy thông từ Hồng tiến sang Hoàng Như Tiếp, oto v3 đỗ trong sân nhà.
-Nhà hướng đông nam, rộng 72m vuông, mặt tiền 3.05m, dài 25m,  xây 4 tầng kiên cố, móng và hệ thống kết cấu riêng biệt , mỗi sàn có 2 phòng ngủ, trừ tầng 1&amp;4. 
-Sau nhà có 1m đất lưu không ( có trong sổ). Trước nhà thụt vào để ngõ rộng, có sân vườn đầy đủ và sạch sẽ
-Chủ nhà là người trí thức cũ ( đầu ngành khoa học, có địa vị cao trong xã hội) nay muốn bán vì muốn ở gần con cái
-Ngôi nhà mang lại sự may mắn và sự thịnh vượng nhất định, nhưng nay ông bà tuổi cao, không leo cầu thang mà muốn ở một mặt sàn nên chuyển đổi. 
- Rất mong gặp được người mua phù hợp, lành tâm tốt tính</t>
-        </is>
-      </c>
-      <c r="R137" t="n">
         <v>131709171</v>
       </c>
     </row>
@@ -11170,30 +7895,6 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O138" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>🚨 BÁN NHÀ TRƯỜNG LÂM - 6 TẦNG THANG MÁY - 53M2 - GARA Ô TÔ - 12.5 TỶ 🚨</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>✨ Nhỉnh 12 tỷ có ngay nhà đẹp 6 tầng, 53m2 tại tâm điểm Trường Lâm, Long Biên.
-🚘 Gara ô tô vào nhà, thang máy xịn xò chạy vèo vèo.
-🏡 Thiết kế hiện đại, tối ưu công năng. Vừa ở vừa kinh doanh, làm phòng khám, văn phòng hoặc cho thuê lấy dòng tiền cực tốt.
-🌟 Tiện ích bủa vây:
-Sát vách Bệnh viện Đa khoa Đức Giang, Trung tâm hành chính quận (Công an, UBND).
-Vài bước chân ra KĐT Việt Hưng, Vinhomes Riverside, chợ, siêu thị và các trường học điểm của khu vực.
-Giao thông hình bàn cờ, kết nối Ngô Gia Tự, Nguyễn Văn Cừ vô cùng thuận tiện.
-💰 Giá chào: 12.5 Tỷ (Làm việc trực tiếp chính chủ).
-📕 Sổ đỏ cất két, pháp lý chuẩn chỉnh.</t>
-        </is>
-      </c>
-      <c r="R138" t="n">
         <v>131200060</v>
       </c>
     </row>
@@ -11248,35 +7949,6 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>21.044842</v>
-      </c>
-      <c r="O139" t="n">
-        <v>105.86866</v>
-      </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>TRUNG TÂM NGỌC LÂM – 7 TẦNG– 55M2 – MT 4.5M – NHỈNH 24 TỶ- KD</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>- Vị trí: Căn nhà tọa lạc trên phố Ngọc Lâm – trung tâm quận Long Biên, khu vực phát triển sầm uất, dân trí cao. Vị trí đẹp, ngõ thông thoáng, ô tô ra vào thuận tiện.
-Kết nối tới các tuyến phố lớn như: Nguyễn Văn Cừ, Bồ Đề, Nguyễn Sơn, Hồng Tiến…
-Di chuyển dễ dàng sang phố cổ qua cầu Chương Dương, cầu Long Biên, chỉ vài phút vào trung tâm Hoàn Kiếm.
--Tiện ích: Gần trường học các cấp, Trường quốc tế Wellspring, Bệnh Viên Tâm Anh, trung tâm thương mại Mipec Long Biên, Tasco, Aeon Long Biên,...
-Xung quanh đầy đủ tiện ích: Ngân hàng, quán ăn, chợ dân sinh, café… khu vực đáng sống, an ninh tốt.
--Thiết kế:
-+Diện tích: 55m2
-+Mặt tiền: 4.4m
-+Xây dựng: 7 tầng hiện đại, có thang máy, full nội thất. Xách vali vào ở được ngay.
-+Công năng tối ưu: Phù hợp vừa ở vừa kinh doanh, cho thuê hoặc làm văn phòng.
--Pháp lý: Sổ đỏ chính chủ, vuông đẹp, pháp lý chuẩn sẵn sàng giao dịch. 
-🏠 Ghiền nhà Long Biên - Xem là ghiền, chốt liền tay!
-📞 Hotline xem nhà 24/7 ( Em Mai) ***
-Chuyên nhà phố: Nguyễn Văn Cừ, Ngọc Lâm, Bồ Đề, Lâm Hạ, Hoàng Như Tiếp, Cổ Linh, Việt Hưng...</t>
-        </is>
-      </c>
-      <c r="R139" t="n">
         <v>131887456</v>
       </c>
     </row>
@@ -11331,34 +8003,6 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O140" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>Bán nhà Hồng Tiến 52m2 x 6 tầng, Ô tô vào nhà, 2 mặt thoáng, thang máy</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>Bán nhà gần ngã ba Hồng Tiến, Bồ Đề, Long Biên, Hà Nội:
-- Nhà 2 mặt thoáng.
-- Ngõ to Ô tô vào nhà.
-- Ngõ ngắn, cách phố 20m, cách cầu Trần Hưng Đạo 500m.
-- Nhà 52m² x 6 tầng mới, thang máy nhập khẩu 500kg.
-- Nhà dân xây riêng biệt độc lập, móng ép cọc chắc chắn, kết cấu, điện, nước và chống thấm rất cẩn thận.
-- Full nội thất nhập nhẩu cao cấp.
-- Công năng: 5 phòng ngủ, 5 vệ sinh, Gara ô tô, khách bếp, phòng thờ, giặt sấy, sân phơi...
-- An ninh &amp; dân trí: Khu phân lô cho cán bộ, dân trí cao, an ninh đảm bảo; hàng xóm đều là công an, bộ đội, giáo viên, hàng không và văn phòng.
-- Pháp lý: SĐCC
-- Giá bán: 16.3 tỷ (có thương lượng)
-- Liên hệ xem nhà: *** Mr Huấn (41 tuổi)
-Cảm ơn đã dành thời gian xem tin!</t>
-        </is>
-      </c>
-      <c r="R140" t="n">
         <v>131852102</v>
       </c>
     </row>
@@ -11413,32 +8057,6 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>21.058859</v>
-      </c>
-      <c r="O141" t="n">
-        <v>105.85839</v>
-      </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>Bán nhà Ngọc Thụy, 50m2 x 6 tầng, ô tô tránh, 2 mặt thoáng, thang máy</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cần bán nhà Ngọc Thụy, Bồ Đề, Hà Nội:
-- Nhà 2 mặt thoáng vĩnh viễn.
-- DT 50m2 x 6 tầng thang máy, thiết kế thông phòng
-- Đường trước ô tô tránh nhau, ô tô chạy thông 2 đầu, xe 7 chỗ đánh vào trong nhà
-- Nhà xây riêng biệt, chắc chắn.
-- Vị trí trung tâm gần chợ Ngọc Thụy (trong đê)
-- Nhà mới full nội thất nhập khẩu cao cấp, full sàn gỗ, tủ bếp, nóng lạnh, điều hòa, giường, tủ, bàn trang điểm...
-- Pháp lý: SĐCC
-- Giá bán: 13 tỷ 950tr (có thương lượng)
-- Liên hệ xem nhà: *** Mr Huấn (41 tuổi), xin cảm ơn!
-</t>
-        </is>
-      </c>
-      <c r="R141" t="n">
         <v>131851589</v>
       </c>
     </row>
@@ -11493,31 +8111,6 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>21.044842</v>
-      </c>
-      <c r="O142" t="n">
-        <v>105.86866</v>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>Bán nhà Ngọc Lâm 75m2 x 7 tầng, MT: 5m, ô tô tránh</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>Cần bán nhà mặt ngõ Ngọc Lâm, Bồ Đề, Hà Nội:
-- Mặt ngõ thông ô tô tránh ô tô 7 chỗ vào nhà
-- Nhà 75m2 x 7 tầng thang máy
-- MT = Hậu 5m vuông vắn
-- Full nội thất cao cấp
-- Vị trí trung tâm, ra phố cổ sầm uất rất gần
-- Pháp lý: SĐCC
-- Giá bán 18.6 tỷ
-- Liên hệ xem nhà: *** Mr Huấn, xin cảm ơn!
-P/S: Thông tin chính xác!</t>
-        </is>
-      </c>
-      <c r="R142" t="n">
         <v>131851618</v>
       </c>
     </row>
@@ -11572,32 +8165,6 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>21.02477</v>
-      </c>
-      <c r="O143" t="n">
-        <v>105.90748</v>
-      </c>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Bán nhà ngọc trì thạch bàn long biên hn</t>
-        </is>
-      </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP - GIÁ TỐT - CHÍNH CHỦ Cần Bán Nhà Vị Trí Đẹp Tại Ngọc Trì, Thạch Bàn Long Biên, Hà Nội
-Diện tích: 33,1 m2
-Giá bán : 8,3 tỷ
-KẾT CẤU nhà 5 tầng gồm 5 phòng ngủ, 3 phòng wc
-Nhà đã lắp hệ thống điện năng lượng mặt trời để sinh hoạt
-TIỆN ÍCH an sinh xã hội đầy đủ, gần trường , gần chợ, siêu thị, bệnh viện...
-THÍCH HỢP định cư lâu dài.Khu vực dân cư đông đúc, an ninh đảm bảo, giao thông thuận lợi
-GIAO THÔNG thuận tiện, đi lại dễ dàng
-PHÁP LÝ Sổ đỏ, thủ tục sang tên nhanh chóng
-TIỀM NĂNG : Nhà Đất luôn tăng giá theo tình hình chung BĐS khu vực, đảm bảo sinh lời
-Liên hệ: ***</t>
-        </is>
-      </c>
-      <c r="R143" t="n">
         <v>131451686</v>
       </c>
     </row>
@@ -11652,27 +8219,6 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O144" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>Bán nhà ngọc thụy long biên 66m 6 tầng thang máy giá 12 tỷ 990 triệu</t>
-        </is>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥12 TỶ 990 triệu 🔥🔥🔥
-Nhà đẹp, giá rẻ tại Ngọc Thuỵ - Long Biên. Gần kđt khai sơn, trường quốc tế Việt Pháp và công viện xung quanh nhiều tiện ích. Vài bước chân ra ô tô tránh 
-💪DT 66m xây  6tầng - mt 5m - thang máy - full nội thất.Thiết kế lên tới 4 phòng ngủ và 1 phòng thờ .công năng cực kỳ hoàn hảo 
-🏠Giá rẻ đầu tư cực ngon 👈
-Sổ đỏ vuông đẹp pháp lý chuẩn sẵn sàng giao dịch.
-☎️liên hệ zalo</t>
-        </is>
-      </c>
-      <c r="R144" t="n">
         <v>131878313</v>
       </c>
     </row>
@@ -11727,28 +8273,6 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>21.0472</v>
-      </c>
-      <c r="O145" t="n">
-        <v>105.91091</v>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>🏘️BÁN NHÀ PHỐ CHU HUY MÂN - 106M2 - SÁT VINHOMES - CHỈ 12.X TỶ💰💰</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🏘️BÁN NHÀ PHỐ CHU HUY MÂN - 106M2 - SÁT VINHOMES - CHỈ 12.X TỶ💰💰
-📍 Vị trí: Phố Chu Huy Mân, cạnh Vinhomes, Aeon Mall.
-🏡 Nhà đẹp: 4 tầng, 2 mặt thoáng, sân trước sau rộng.
-💎 Thông số: 106m2, MT 4.7m. Sổ vuông, cất két.
-💰 Giá: Nhỉnh 12 tỷ (Cực hiếm).
-📞 Lh em Đạt: ***</t>
-        </is>
-      </c>
-      <c r="R145" t="n">
         <v>131874603</v>
       </c>
     </row>
@@ -11803,26 +8327,6 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O146" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>💎 BÁN NHÀ CỔ LINH 80M2 - THANG MÁY - GARA Ô TÔ - NHỈNH 16 TỶ 💎</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>✅ Thông số: 80m2 x 7 tầng. Gara ô tô, thang máy, phòng Master.
-✅ Vị trí: Ngõ nông, sát vách Aeon Mall, hạ tầng đồng bộ.
-✅ Pháp lý: Sổ vuông đẹp, sẵn sàng công chứng.
-✅ Giá: Nhỉnh 21 tỷ (Thương lượng chính chủ).
-☎️ LH Em Đạt: *** (Xem nhà 24/7)</t>
-        </is>
-      </c>
-      <c r="R146" t="n">
         <v>131709949</v>
       </c>
     </row>
@@ -11877,29 +8381,6 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>21.054022</v>
-      </c>
-      <c r="O147" t="n">
-        <v>105.88715</v>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>VIP-NGUYỄN VĂN CỪ-7T-55M-Ô TÔ-THANG MÁY-FULL NỘI THẤT CAO CẤP-PHÂN LÔ</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>Bán nhà riêng khu VIP trung tâm Gia Thụy Long Biên
-Nhà phố Nguyễn Văn Cừ - Long Biên - Phân lô ô tô tránh.
-- Diện tích 55m2, mặt tiền 5m, TTM
-- Phân lô ô tô tránh thông bàn cờ, gần phố Nguyễn Văn Cừ, Nguyễn Sơn, Gia Thụy, Đảo Sen, Cầu Trần Hưng Đạo, Bv Tâm Anh, Hồng Tiến, Trường quốc tế Welspring, Việt Pháp, Aeon Long Biên, Cầu Chương Dương, Vĩnh Tuy tiện ích xung quanh
-- Thiết 7 tầng, 4 ngủ, thang máy 650kg, Gara 3 xe ô tô, Hoàn thiện Full nội thất cao cấp
-- Sổ riêng cất két, pháp lý chuẩn, sẵn sàng giao dịch ngay
-- Giá nhỉnh thương lượng trực tiếp chủ
-Liên hệ trực tiếp : ***</t>
-        </is>
-      </c>
-      <c r="R147" t="n">
         <v>130883151</v>
       </c>
     </row>
@@ -11954,35 +8435,6 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O148" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>LÔ GÓC Ô TÔ TIẾP CẬN - HÀNG XÓM MIPEC - NGÕ NÔNG - CHỈ 7.5 TỶ</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🌹🌹 LÔ GÓC Ô TÔ TIẾP CẬN - HÀNG XÓM MIPEC - NGÕ NÔNG - CHỈ 7.5 TỶ
-Vị trí cực đẹp tại khu vực Ngọc Thụy, Long Biên, ngay sát Mipec Riverside, cách cầu Long Biên chỉ vài bước chân. Nhà lô góc thoáng sáng, ngõ nông, rất hiếm trong phân khúc!
-💎 Thông Tin Nổi Bật:
-• Vị trí: Cách Mipec Riverside vài chục mét, gần khu ẩm thực Ngọc Lâm, thuận tiện di chuyển sang phố cổ.
-• Thông số: Lô góc thoáng đãng, thiết kế hiện đại, nhà còn rất mới.
-• Dòng tiền: Đang có sẵn hợp đồng cho thuê, mua về là có thu nhập ngay.
-• Pháp lý: Sổ đỏ chính chủ, sẵn sàng giao dịch.
-🏠 Thiết Kế Tối Ưu:
-• Tầng 1: Phòng khách sang trọng, bếp ấm cúng và WC.
-• Tầng 2, 3, 4: Mỗi tầng là 1 phòng ngủ rộng + WC khép kín (tổng 3 ngủ).
-• Tầng tum: Phòng thờ trang nghiêm và sân phơi thoáng mát.
-💰 Giá chào: 7.5 tỷ (có thương lượng).
-📞 Liên hệ xem nhà ngay: *** (Đạt)</t>
-        </is>
-      </c>
-      <c r="R148" t="n">
         <v>131865724</v>
       </c>
     </row>
@@ -12037,33 +8489,6 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O149" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>NGỌC THỤY - PHÂN LÔ QUÂN ĐỘI - SÁT KHAI SON CITY - CHỈ 8.5 TỶ</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💎 NGỌC THỤY - PHÂN LÔ QUÂN ĐỘI - SÁT KHAI SON CITY - CHỈ 8.5 TỶ ✅
-🔥 ĐIỂM VÀNG ĐẮT GIÁ:
-• Vị trí cực đẹp: Sát vách Học viện Hậu Cần, KĐT Khai Sơn, hưởng trọn tiện ích hồ điều hòa &amp; công viên.
-• Ngõ thông - Dân trí cao: Khu phân lô an ninh tuyệt đối, hàng xóm văn minh.
-• Tiện lợi: Ô tô đỗ cách nhà 20m, di chuyển cực thoáng.
-🏠 NHÀ DÂN XÂY - CHẮC CHẮN:
-• Kết cấu 3 tầng khung cột bền bỉ (3PN + Sân phơi).
-• Nhà giữ gìn kỹ, chỉ cần sơn nhẹ là long lanh như mới.
-⚖️ SỔ ĐỎ PHÂN LÔ - SẴN SÀNG GIAO DỊCH.
-💰 GIÁ CHỐT: 8.5 TỶ
-📞 LH NGAY: *** (Em Đat - Xem nhà 24/7)</t>
-        </is>
-      </c>
-      <c r="R149" t="n">
         <v>131865242</v>
       </c>
     </row>
@@ -12118,33 +8543,6 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>21.058727</v>
-      </c>
-      <c r="O150" t="n">
-        <v>105.91411</v>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>🔥 VIỆT HƯNG – 90M2 – MT 6M – 5 TẦNG THANG MÁY – Ô TÔ, VỈA HÈ – KINH DO</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 VIỆT HƯNG – 90M2 – MT 6M – 5 TẦNG THANG MÁY – Ô TÔ, VỈA HÈ – KINH DOANH ĐỈNH
-💎 Ở + kinh doanh + giữ tiền – tặng nội thất
-📍 Cách trục chính 30m – đối diện quy hoạch chung cư – gần Vin Riverside
-🏢 Thiết kế:
- • T1: Thông sàn (gara / showroom)
- • T2–4: Khách + bếp + 6PN khép kín
- • T5: Sân thượng thoáng
-🚀 Hợp: công ty, VP, spa, showroom, ở + cho thuê
-🌆 Tiện ích đầy đủ – khu vực phát triển mạnh
-📕 Sổ đỏ sẵn – giao dịch nhanh
-📞 *** – Em Mùi (Thổ địa Long Biên)</t>
-        </is>
-      </c>
-      <c r="R150" t="n">
         <v>131829760</v>
       </c>
     </row>
@@ -12199,27 +8597,6 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>21.04372</v>
-      </c>
-      <c r="O151" t="n">
-        <v>105.92593</v>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Biệt thự liền kề Long Biên hàng xóm RiverSide</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP - VỊ TRÍ ĐẮC ĐỊA - CƠ HỘI ĐẦU TƯ SINH LỜI TẠI LONG BIÊN 🏡
-Tìm đâu ra căn biệt thự mặt đường lớn, hàng xóm RiverSide mà giá chỉ hơn 23 tỷ?
-• Diện tích sử dụng cực lớn 85m2 với 6 tầng kiên cố, có sẵn thang máy.
-• Mặt tiền thoáng sáng, vỉa hè rộng rãi là điểm cộng lớn cho việc kinh doanh.
-✨ Chủ nhà thiện chí, sổ đỏ cất két.
-👉 Gọi ngay: *** (Zalo)</t>
-        </is>
-      </c>
-      <c r="R151" t="n">
         <v>131860533</v>
       </c>
     </row>
@@ -12274,26 +8651,6 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>21.051413</v>
-      </c>
-      <c r="O152" t="n">
-        <v>105.92261</v>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>PHÚC LỢI- MẶT TIỀN 5.1M- AN CƯ ĐỈNH CAO TRONG TẦM GIÁ</t>
-        </is>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>Siêu phẩm nhà tại trung tâm Phúc lợi. Vị trí gần trường mầm non, cấp 1,2,3 . cách đường lớn 15m, các winmart, chợ dân sinh 3 phút đi bộ. 
-Nhà mới xây, trông như mới. Thiết kế khung cột bê tông chắc chắn vững trãi, an cư lâu dài. 
-Nội thất cơ bản , trung thực trong hình. đầy đủ cho mọi nhu cầu sử dụng cơ bản. 
-sổ đỏ cất két, chủ nhà thân thiện , cưucj kỳ uy tín
-LH E Tổng ***  để xem nhà ngay trong hôm nay</t>
-        </is>
-      </c>
-      <c r="R152" t="n">
         <v>131860241</v>
       </c>
     </row>
@@ -12348,25 +8705,6 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>21.038532</v>
-      </c>
-      <c r="O153" t="n">
-        <v>105.91242</v>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Nhà ở vị trí  đẹp,trước mặt là hồ Sài Đồng đẹp mát,nhà vỉa hè,ôtô .</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>Bán đất tặng nhà 3 tầng, trước mặt hồ Sài Đồng mát mẻ, đường có vỉa hè, ô tô dừng đỗ ngày đêm.
-📐 160m² – MT 14m – lô góc – chia 2 lô đẹp
-💰 Giá 47,4 tỷ – sổ đỏ sẵn, giao dịch ngay.
-📞 Liên hệ xem đất sớm – hàng đẹp hiếm khu vực!</t>
-        </is>
-      </c>
-      <c r="R153" t="n">
         <v>130737869</v>
       </c>
     </row>
@@ -12421,38 +8759,6 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O154" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>🔥 TUYỆT PHẨM NGỌC THỤY – 3 MẶT THOÁNG – Ô TÔ ĐỖ CỔNG – CHỈ 6.99 TỶ 🔥</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 TUYỆT PHẨM NGỌC THỤY – 3 MẶT THOÁNG – Ô TÔ ĐỖ CỔNG – CHỈ 6.99 TỶ 🔥
-Cơ hội hiếm có sở hữu căn nhà "thông số vàng" tại phân khúc cực hot, tầm tiền dễ tiếp cận nhất khu vực!
-• Thông số ấn tượng: Diện tích 32m2 x 4 tầng, mặt tiền rộng 3.9m.
-• Vị trí "Kim Cương": * Trung tâm Ngọc Thụy, bước chân ra là chợ, trường học các cấp.
-• Chỉ vài phút tới trường Quốc tế Pháp (Yersin), công viên Ngọc Thụy, KĐT Khai Sơn, Big C Long Biên.
-• Tiện ích ngập tràn, giao thông cực kỳ thuận tiện vào phố cổ.
-• Điểm khác biệt ***:
-• 3 mặt thoáng vĩnh viễn: Bên cạnh là vườn, phía sau có mặt thoáng ⇒ Nhà luôn ngập tràn ánh sáng tự nhiên và sinh khí.
-• Ngõ thông thoáng, dân trí cao.
-• Thiết kế thông minh &amp; chắc chắn:
-• Cầu thang cuối tối ưu diện tích, không gian cực rộng rãi.
-• 3 Phòng ngủ tiện nghi. Đặc biệt: Tầng 1 thiết kế linh hoạt có giường ngủ cho người cao tuổi.
-• Khung cột bê tông chắc chắn, khách mua có thể lên thêm tầng thoải mái theo nhu cầu.
-• Pháp lý: Sổ đỏ vuông đẹp như phân lô, sẵn sàng giao dịch ngay.
-💰 Giá chào: 6.99 tỷ (Thương lượng trực tiếp).
-📞 Liên hệ: *** để xem nhà trực tiếp và nhận giá ***!</t>
-        </is>
-      </c>
-      <c r="R154" t="n">
         <v>131846001</v>
       </c>
     </row>
@@ -12507,34 +8813,6 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O155" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>Bán Nhà Thạch Bàn - Long Biên, 47m x 5 Tầng Dân Xây, Đường Ô tô tránh,</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Bán Nhà Thạch Bàn - Long Biên, 47m x 5 Tầng Dân Xây, Đường Ô tô tránh, Kinh Doanh.
-+ Vị trí trung tâm, gần Aeon Long Biên, trục vành đai vào
-Nội đô hay đi tỉnh đều tiện.
-+ Nhà 5 tầng thiết kế:
-- Tầng 1: phòng khách, bếp, vệ sinh
-- Tầng 2: phòng ngủ nhỏ
-- Tầng 3: 2 phòng ngủ - vệ sinh ngoài
-- Tầng 4: 2 phòng ngủ - vệ sinh ngoài
-- Tầng 5: sân phơi - trước sau.
-+ Sổ đỏ chính chủ, ko tranh chấp, quy hoạch
-Giá nhỉnh 12 tỷ (có thương lượng)
-Liên hệ: Mr Tùng để đi xem nhà trực tiếp và miễn phí</t>
-        </is>
-      </c>
-      <c r="R155" t="n">
         <v>131792819</v>
       </c>
     </row>
@@ -12589,26 +8867,6 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>21.042528</v>
-      </c>
-      <c r="O156" t="n">
-        <v>105.9024</v>
-      </c>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>Bán nhà mặt phố Nguyễn Lam - Phúc Đồng - 8 tầng thang máy - full NT</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>Căn nhà ở vị trí HoT nhất khu vực Phúc Đồng - Long Biên, nơi có rất nhiều người đang săn tìm. Bán kính 300m là các đại đô thị, chung cư cao cấp đã và đang hoạt động với lượng dân cư cực kỳ đông đúc, giàu có như Vin Riverside , Hope Residence , Nobel CRYSTAL .....
-Căn nhà mặt phố với mặt tiền quyền lực. Xây 8 tầng thang máy. Full nội thất.
-Thiết kế vừa có thể ở, vừa kinh doanh.
- Pháp lý sạch. Sổ sẵn giao dịch
-Liên hệ em Lan để đi xem trực tiếp</t>
-        </is>
-      </c>
-      <c r="R156" t="n">
         <v>131690803</v>
       </c>
     </row>
@@ -12663,29 +8921,6 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>21.02167</v>
-      </c>
-      <c r="O157" t="n">
-        <v>105.91418</v>
-      </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ 6 TẦNG THANG MÁY GẦN CHỢ ĐỒNG DINH, THẠCH BÀN FULL NỘI THẤT</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>🔥 NHÀ ĐẸP LONG BIÊN – 35m² – 6 TẦNG THANG MÁY – GẦN Ô TÔ – 8,x TỶ 🔥
-Diện tích: 35m²
-6 tầng thang máy, 3 phòng ngủ khép kín
-Cách ô tô tránh 20m
-Vài bước chân ra đến Aeon, Cổ Linh, cầu Vĩnh Tuy. Tiện ích ngập tràn. Xung quanh là trường liên cấp Thạch Bàn
-💰 Giá: 8,x tỷ (có TL)
-📕 Sổ đỏ chính chủ, sẵn sàng giao dịch
-📞 Alo Em Thiêm xem nhà ngay hôm nay</t>
-        </is>
-      </c>
-      <c r="R157" t="n">
         <v>131568270</v>
       </c>
     </row>
@@ -12740,44 +8975,6 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O158" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ TÁI ĐỊNH CƯ CỔ LINH LÔ GÓC 6 TẦNG THANG MÁY, GARA Ô TÔ FULL NT</t>
-        </is>
-      </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>🏡🚗 SIÊU PHẨM CỔ LINH – 6 TẦNG THANG MÁY – LÔ GÓC – Ô TÔ ĐỖ CỬA NGÀY ĐÊM 🚗🏡
-💎 Phân lô VIP – Ngõ thông – Ở &amp; Kinh doanh đều đỉnh 💎
-📍 Vị trí đẹp phố Cổ Linh – khu tái định cư văn minh
-🌳 Gần vườn hoa – 200m ra hồ công viên lớn nhất quận đang xây dựng
-🛍 Vài phút tới AEON Mall Long Biên
-🏘 Cạnh khu Elegant Park – khu triệu đô, tiềm năng tăng giá mạnh
-📐 Diện tích: 40m² – Lô góc cực thoáng
-🚘 Ô tô đỗ cửa ngày đêm – Ngõ phân lô bàn cờ
-✨ Thiết kế 6 tầng thang máy cao cấp – Nội thất xịn sò:
-🔹 Hệ thống điện thông minh thương hiệu
-🔹 Cửa cuốn Audor điều khiển từ xa
-🔹 Tủ bếp gỗ phủ Acrylic kịch trần
-🔹 Bếp từ nhập khẩu Đức
-🔹 Sàn gỗ lát xương cá sang trọng
-🔹 Điều hoà LG full phòng
-🧱 Công năng chuẩn chỉnh:
-T1: Gara ô tô, WC, thang máy, thang bộ
-T2: Phòng khách + bếp + ban công thoáng
-T3,4,5: Phòng ngủ rộng, WC riêng, ban công view đẹp
-T6: Phòng thờ + sân phơi
-💰 Giá 13.4 tỷ (có thương lượng)
-📕 Sổ đỏ chính chủ, sẵn sàng giao dịch – nở hậu cực lộc 💎
-📞 Gọi em Trọng Thiêm 👉 Xem nhà miễn phí – Phục vụ uy tín, tận tâm, chuyên nghiệp</t>
-        </is>
-      </c>
-      <c r="R158" t="n">
         <v>130823421</v>
       </c>
     </row>
@@ -12832,28 +9029,6 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>21.055147</v>
-      </c>
-      <c r="O159" t="n">
-        <v>105.90521</v>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Bán nhà Việt Hưng- gần 70mv - 8.x tỷ - Camry đỗ tận cửa</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: - nhà dân xây chắc chắn, không phải nhà thương mại
-- nhà đơn lập, không sân chung, cổng chung, tường chung, móng chung
-- 1 ngoặt từ ngõ vào nhà, đường trước nhà thông ra chợ, trường học.
-- xung quanh nhà biệt thự của quan chức, chủ doanh nghiệp.
-- sổ vuông vắn, chủ thiện mót b-á-n.
-liên hệ *** để xem nhà và gặp chủ nhà</t>
-        </is>
-      </c>
-      <c r="R159" t="n">
         <v>131727185</v>
       </c>
     </row>
@@ -12908,23 +9083,6 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>21.00597</v>
-      </c>
-      <c r="O160" t="n">
-        <v>105.89656</v>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Nhà HOT</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Bán nhà 2 mặt Ô tô để trong nhà với đầy đủ tiện nghi công năng, người mua chỉ cần xách Vali về ở</t>
-        </is>
-      </c>
-      <c r="R160" t="n">
         <v>131825524</v>
       </c>
     </row>
@@ -12979,44 +9137,6 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O161" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>🏡 NHÀ ĐẸP TĐC NGỌC THỤY – 7 TẦNG THANG MÁY – KINH DOANH CỰC ĐỈNH ✨</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🏡 NHÀ ĐẸP TĐC NGỌC THỤY – 7 TẦNG THANG MÁY – KINH DOANH CỰC ĐỈNH ✨
-📍 Vị trí siêu đẹp tại khu TĐC Ngọc Thụy, trung tâm quận Long Biên  
-🚗 Trước nhà rộng, 2 ô tô tránh nhau thoải mái  
-🔄 Phân lô, ngõ thông, phù hợp ở kết hợp kinh doanh mọi loại hình
-🔹 Diện tích sổ: 40m²  
-🔹 Diện tích xây dựng: 50m²   
-🔹 Kết cấu: 7 tầng hiện đại  
-🔹 Trang bị: thang máy xịn, công năng đầy đủ
-🌳 Khu vực đáng sống bậc nhất Ngọc Thụy:
-✅ Sát công viên Ngọc Thụy nghìn tỷ  
-✅ Gần chợ dân sinh  
-✅ Gần Khai Sơn Hill  
-✅ Hạ tầng đồng bộ, tiện ích không thiếu thứ gì
-💼 Phù hợp:
-🏠 Ở sướng  
-🛍️ Kinh doanh tốt  
-🏢 Làm văn phòng, spa, phòng khám, căn hộ dịch vụ đều đẹp
-💰 Giá chào: 16,5 tỷ  
-🤝 Còn thương lượng tốt với khách thiện chí
-━━━━━━━━━━━
-☎️ LH em Đoan dẫn xem nhà - KHÔNG ĐĂNG ẢO : *** (gọi/zalo)
-📹Tiktok nhiều nhà đẹp: CỘ CỘ TÊN LÀ ĐOAN BĐS LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="R161" t="n">
         <v>131789880</v>
       </c>
     </row>
@@ -13071,28 +9191,6 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O162" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>Ngọc Thụy- 42m2 nhỉnh 10 tỷ</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Ngọc Thụy- 42m2 nhỉnh 10 tỷ.
-Gần chợ, gần công viên, lên cầu Long Biên chưa tới 5p
-Nhà dân xây chắc chắn
-━━━━━━━━━━━
-☎️ LH em Đoan dẫn xem nhà - KHÔNG ĐĂNG ẢO : *** (gọi/zalo)
-📹Tiktok nhiều nhà đẹp: CỘ CỘ TÊN LÀ ĐOAN BĐS LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="R162" t="n">
         <v>131792134</v>
       </c>
     </row>
@@ -13147,35 +9245,6 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>21.038532</v>
-      </c>
-      <c r="O163" t="n">
-        <v>105.91242</v>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>🔥 SIÊU PHẨM CĂN GÓC SÀI ĐỒNG – GIẢM SỐC 1 TỶ – HIẾM CÓ KHÓ TÌM 🔥</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 SIÊU PHẨM CĂN GÓC – GIẢM SỐC 1 TỶ – HIẾM CÓ KHÓ TÌM 🔥
-🏡 52m² – 7 TẦNG – THANG MÁY – GARA Ô TÔ – FULL NỘI THẤT
-📍 Vị trí trung tâm Sài Đồng – sát trục Nguyễn Văn Linh
-👉 Kết nối nhanh – tiện ích ngập tràn – ở &amp; kinh doanh đều đỉnh
-• Căn góc 2 mặt thoáng – cực kỳ hiếm
-• Mặt tiền đẹp – phù hợp spa, văn phòng, kinh doanh nhỏ
-• Gara ô tô trong nhà
-• Thang máy hiện đại – full nội thất cao cấp
-• Nhà mới – vào ở ngay
-💰 Chủ thiện chí – giảm ngay 1 TỶ cho khách chốt nhanh
-━━━━━━━━━━━
-☎️ LH em Đoan dẫn xem nhà - KHÔNG ĐĂNG ẢO : *** (gọi/zalo)
-📹Tiktok nhiều nhà đẹp: CỘ CỘ TÊN LÀ ĐOAN BĐS LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="R163" t="n">
         <v>131792236</v>
       </c>
     </row>
@@ -13230,34 +9299,6 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>21.021278</v>
-      </c>
-      <c r="O164" t="n">
-        <v>105.90515</v>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>CHÍNH CHỦ BÁN NHÀ THẠCH BÀN, LONG BIÊN 44M², 4 TẦNG GẦN AEON MALL</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>CHÍNH CHỦ BÁN NHÀ THẠCH BÀN, LONG BIÊN 44M², 4 TẦNG GẦN AEON MALL CÓ SÂN 9,5 TỶ
-Chính chủ cần bán nhà tại số 6A, ngõ 227/28/2 Thạch Bàn, Long Biên, Hà Nội.
-* Thông tin chi tiết:
-- Diện tích: 44m²
-- Kết cấu: Nhà 4 tầng, gồm 4 phòng ngủ
-- Có sân riêng thoáng mát
-- Ngõ nông, cách ô tô ~30m
-* Vị trí &amp; tiện ích:
-- Cách Aeon Mall Long Biên chỉ 300m
-- Khu dân cư đông đúc, an ninh tốt
-- Gần chợ, trường học, đầy đủ tiện ích sinh hoạt
-Pháp lý: Sổ đỏ chính chủ, rõ ràng
-Giá bán: 9,5 tỷ</t>
-        </is>
-      </c>
-      <c r="R164" t="n">
         <v>131778639</v>
       </c>
     </row>
@@ -13312,44 +9353,6 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O165" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>🔥 CHÍNH CHỦ BÁN ĐẤT PHỐ BỒ ĐỀ – LONG BIÊN HÀ NỘI 🔥</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>🔥 CHÍNH CHỦ BÁN ĐẤT PHỐ BỒ ĐỀ – LONG BIÊN HÀ NỘI 🔥
-📍 Vị trí:  Ngõ 193 Bồ Đề , quận Long Biên, Hà Nội -📐 Diện tích: 31.2m² -📏 Mặt tiền: ~3.1m – đất vuông vắn , nhà mới đẹp 
-✨ ƯU ĐIỂM NỔI BẬT:
-* Sổ đỏ chính chủ, pháp lý rõ ràng, sang tên nhanh
-* Đất nhà ở , sử dụng lâu dài
-* Khu dân cư đông đúc, an ninh tốt
-* Ngõ thông thoáng, đi lại thuận tiện
-🚗 KẾT NỐI SIÊU TIỆN:
-* Gần cầu Chương Dương – sang phố cổ chỉ 10 phút 
-* Chỉ 5 phút tới AEON Mall Long Biên
-* Ra mặt đường Hồng Tiến chỉ 2 phút
-* Gần chợ Ngọc Lâm, tiện sinh hoạt hàng ngày
-* Xung quanh nhiều trường học quốc tế ( trường Hồng Tiến , Ái mộ , Nguyễn Gia Thiều đủ các cấp …)
-* Quán Ăn Uống đông đúc , sầm uất 
-🏡 Phù hợp: -✔ Dọn về chỉ việc ở không cần sửa chữa  -✔ Đầu tư giữ tiền hoặc cho thuê
-💰 Giá bán: 9,5 tỷ  (có thương lượng nhẹ)
-📞 Liên hệ ngay: ***  -👉 Làm việc trực tiếp chính chủ – không qua trung gian -
-#bannha #datlongbien #bode #chinhchu #batdongsan</t>
-        </is>
-      </c>
-      <c r="R165" t="n">
         <v>131818838</v>
       </c>
     </row>
@@ -13404,37 +9407,6 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O166" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>7𝘅 𝗧𝘆̉❗️ 𝗡𝗚𝗢̣𝗖 𝗧𝗛𝗨̣𝗬 𝟱 𝘁𝗮̂̀𝗻𝗴– 4 PHÒNG NGỦ RỘNG – Ô TÔ 7 CHỖ ĐỖ CỬA –</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Do chuyển công tác sang khu Mỹ Đình nên gia đình cần nhượng lại căn nhà tâm huyết tại Ngọc Thụy.
-🏡 BÁN NHÀ NGỌC THỤY – NGÕ Ô TÔ – CỰC THOÁNG – 32m² – 5 TẦNG – 50m RA PHỐ
-	•	Diện tích: 31,8 m²
-	•	Mặt tiền: 3,57 m
-	•	Nhà 4 tầng + 1 tum, xây 2019 còn rất mới
-	•	Tầng 1: khách + bếp
-	•	Tầng 2,3,4: mỗi tầng 1 phòng ngủ + 1 WC
-	•	Tầng 5: phòng thờ + sân phơi
-Ưu điểm:
-	•	Nhà mặt ngõ cực thoáng, đối diện nhà văn hóa
-	•	Ngõ ô tô quay đầu ô tô đỗ cách nhà 10 m
-	•	Chỉ 50 m ra đường chính Ngọc Thụy
-	•	Đi sang phố cổ rất nhanh qua Cầu Chương Dượng
-💰 Giá: 8,4tỷ
-📞 Liên hệ: ***</t>
-        </is>
-      </c>
-      <c r="R166" t="n">
         <v>131788470</v>
       </c>
     </row>
@@ -13489,34 +9461,6 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O167" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>NHÀ NGỌC THỤY - CẠNH TRƯỜNG PHÁP - Ô TÔ ĐỖ CỔNG - GIÁ CHỈ 7.2 TỶ</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>NHÀ NGỌC THỤY - CẠNH TRƯỜNG PHÁP - Ô TÔ ĐỖ CỔNG - GIÁ CHỈ 7.2 TỶ
-Vị trí đắc địa – Tiện ích ngập tràn:
-• Vị trí: Nhà nằm tại khu vực trung tâm Ngọc Thụy, thông ngõ cực kỳ thuận tiện.
-• Giao thông: Đường rộng, ô tô đỗ cổng, di chuyển dễ dàng sang phố cổ hoặc các khu vực lân cận.
-• Tiện ích: Sát vách trường quốc tế Pháp, gần công viên Ngọc Thụy, chợ dân sinh và các trường học các cấp. Không khí trong lành, dân trí cao.
-Thiết kế hiện đại – Tối ưu công năng (5 tầng):
-• Tầng 1: Phòng khách sang trọng, bếp ấm cúng và WC.
-• Tầng 2, 3, 4: Thiết kế thông sàn rộng rãi (tổng 3 phòng ngủ lớn) + WC riêng biệt từng tầng.
-• Tầng 5: Phòng thờ trang nghiêm và sân phơi thoáng đãng.
-Pháp lý:
-• Sổ đỏ chính chủ, sẵn sàng giao dịch.
-• Giá chào: 7.2 tỷ (có thương lượng).
-Liên hệ xem nhà ngay: 📞 *** (Hỗ trợ 24/7</t>
-        </is>
-      </c>
-      <c r="R167" t="n">
         <v>131808179</v>
       </c>
     </row>
@@ -13571,28 +9515,6 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O168" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>RẺ NHẤT TRUNG TÂM LONG BIÊN – 5 TẦNG – VÀI BƯỚC RA Ô TÔ – 6.1 TỶ 🔥</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>💥RẺ NHẤT TRUNG TÂM LONG BIÊN – 5 TẦNG – VÀI BƯỚC RA Ô TÔ – 6.1 TỶ 🔥
-🚗 Ngõ gần ô tô, đi lại tiện
-🏫 Gần trường, chợ, tiện ích đầy đủ
-🏡 Nhà đẹp, ở ngay
-💰 Giá chỉ 6.1 tỷ – cực hiếm
-📞 Liên hệ em xem ngay và gặp chính chủ ạ
-#LongBien #NhaDep #GanOto #GiaTot #BatDongSan #NhaHaNoi #NhaTrungTam #DauTuBDS #NhaPho #MuaNha #BDSLongBien #ChotNhaNhanh</t>
-        </is>
-      </c>
-      <c r="R168" t="n">
         <v>131807948</v>
       </c>
     </row>
@@ -13647,29 +9569,6 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O169" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>GIẢM CHÀO 500TR 🔥VIỆT HƯNG – 50M² – 5 TẦNG – Ô TÔ ĐỖ CỬA</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>GIẢM CHÀO 500TR
-🔥VIỆT HƯNG – 50M² – 5 TẦNG – Ô TÔ ĐỖ CỬA 
-🏡 Nhà đẹp gần Ngô Gia Tự
-🚗 Ô tô đỗ cửa – kinh doanh tốt
-💰 Dòng tiền 30tr/tháng
-📍 Gần ngay trường học – tiện ích đầy đủ
-💸 Chỉ 10 tỷ
-#VietHung #LongBien #NhaDep #OtoDoCua #KinhDoanh #DongTienOnDinh</t>
-        </is>
-      </c>
-      <c r="R169" t="n">
         <v>131807862</v>
       </c>
     </row>
@@ -13724,27 +9623,6 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>21.02974</v>
-      </c>
-      <c r="O170" t="n">
-        <v>105.91316</v>
-      </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ ĐẸP - TRUNG TÂM PHỐ THẠCH BÀN , OTO XỊCH CỬA ,Ở SƯỚNG, GIÁ HỜI</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>Cc cần bán căn nhà đẹp, gần như mới nguyên, ngay tại phố lớn Thạch Bàn, vị trí khu vực trung tâm sầm uất, gần ngã tư Thạch Bàn - Cổ Linh, cách chợ Thạch Bàn chỉ vài bước chân
-+ Diện tích 42m x6 tầng, mặt tiền rộng 5m, thiết kế hiện đại, oto xịch ngay cổng, cực kỳ thuận tiện.
-+ Xung quanh là cụm trường học, quán xá sầm uất, vài phút đi bộ ra Aeon Mall Long Biên mua sắm vui chơi thỏa thích.
-+Nhà full nội thất xịn sò: giường tủ, bàn ghế đủ cả - mua về ở ngay .
-+ Giá bán nhanh cho khách thiện chí, chỉ 10,9 tỷ - có TL . Phù hợp ở gia đình hoặc vừa ở vừa  đầu tư, giữ tiền đều rất tốt
-Xem nhà miến phí liên hệ Dũng - Chuyên Bđs Long Biên, nhiều quỹ căn ngon bất ngờ .</t>
-        </is>
-      </c>
-      <c r="R170" t="n">
         <v>131801226</v>
       </c>
     </row>
@@ -13799,27 +9677,6 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O171" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>CỔ LINH- AEON LONG BIÊN, BÁN NHÀ MỚI XÂY, HÀNG HIẾM, GIÁ HỜI</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>CC cần bán nhà xây mới tại Cổ Linh- Đàm Quang Trung, ngay gần Aeon , vị trí đẹp, dân cư đông đúc, an ninh tốt. Hàng siêu hiếm trong tầm tiền quanh khu vưc.
-+ Căn góc, thoáng sáng ,diện tích 30m x5 tầng với 3 PN, thiết kế hiện đại, công năng tối ưu, nội thất cơ bản, xịn sò, chỉ việc xách vali về ở.
-+ Nhà gần chợ, trường học, gần cầu Vĩnh Tuy,  10m ra oto tránh , đi lại thuận tiện,  đi bộ vài phút ra AEON vui chơi mua sắm thỏa thích.
-+ Phù hợp cho gia đình trẻ hay gia đình nhỏ, vừa ở vừa đầu tư giữ tiền.
-+ Giá chỉ 7,25 tỷ- có TL, sổ đỏ cất két, giao dịch ngay.
-Xem nhà miễn phí alo Dũng - Chuyên Bđs Long Biên, nhiều quỹ căn ngon bất ngờ !</t>
-        </is>
-      </c>
-      <c r="R171" t="n">
         <v>131801879</v>
       </c>
     </row>
@@ -13874,27 +9731,6 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O172" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ MỚI TINH - SÁT QUANH AEON LB, OTO, THGMAY. GIÁ CHỈ 12,9TY</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>Cc cần bán că nhà mới tinh tại Cổ Linh - Đàm Quang Trung, vị trí cực hiếm, đối diện Aeon Mall Long Biên, tiện ích không thiếu thứ gì.
-+ Diện tích 42m x 6 tầng, thiết kế hiện đại, sang trọng, có Gara oto, thang máy nhập khẩu chạy vèo vèo.
-+ Xung quanh là chợ lớn, cụm trường học, chỉ vài phút đi bộ ra Aeon Mall mua sắm và vui chơi thỏa thích.
-+ Nhà được trang bị nội thất cơ bản, loại xịn sò - mua về ở ngay hoặc kết hợp làm văn phòng hay giữ tiền đều rất phù hợp.
-+ Giảm giá bán nhanh, chỉ còn 12,9 tỷ- có TL, cơ hội hiếm có trong khu vực.
-Xem nhà thực tế miến phí alo Dũng.- Chuyên bds Long Biên, nhiều quỹ căn ngon bất ngờ .</t>
-        </is>
-      </c>
-      <c r="R172" t="n">
         <v>131800843</v>
       </c>
     </row>
@@ -13949,32 +9785,6 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>21.033587</v>
-      </c>
-      <c r="O173" t="n">
-        <v>105.91761</v>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP 6 TẦNG - NỘI THÂT – 2 MẶT THOÁNG VĨNH VIỄN – GIÁ HIẾM SÀI ĐỒNG</t>
-        </is>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💎 Diện tích đẹp – mặt tiền rộng 4,2m
-💎 Thiết kế 6 tầng full công năng – chỉ việc xách vali về ở
-💎 2 mặt thoáng trước sau – nhà lúc nào cũng sáng, cực kỳ thoáng khí
-📍 Vị trí trung tâm Phúc Lợi:
-	•	Đi bộ vài bước là tới trường học
-	•	Vài phút xe máy ra ngay Aeon Mall, BigC – tiện ích ngập tràn
-	•	Khu dân trí cao, hàng xóm toàn cán bộ nghỉ hưu – yên tĩnh, an ninh cực tốt
-💰 Giá chỉ ~6.x tỷ – quá hiếm trong phân khúc
-⚡ Cơ hội tốt cho khách mua ở hoặc đầu tư giữ tiền
-📞 Nhanh tay là còn – chậm là mất!</t>
-        </is>
-      </c>
-      <c r="R173" t="n">
         <v>131805795</v>
       </c>
     </row>
@@ -14029,38 +9839,6 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>21.032267</v>
-      </c>
-      <c r="O174" t="n">
-        <v>105.90883</v>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>GĐ bán nhà Ng Văn Linh, 48m 5T thang máy, 50m oto tránh, chợ Đồng Dinh</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>Gia đình chuyển đổi nhu cầu sinh hoạt sang không gian lớn hơn để tiện cho công việc và sinh hoạt lâu dài, nên muốn nhượng lại căn nhà được tự tay xây dựng, chăm chút từng chi tiết với rất nhiều tâm huyết.
-Vị trí:
-Nhà nằm trong khu vực phát triển, ngõ thông thoáng, chỉ vài bước ra đường ô tô tránh. Kết nối nhanh tới các trục giao thông lớn, thuận tiện di chuyển đi các khu vực trung tâm và lân cận.
-Tiện ích xung quanh:
-Gần chợ, trung tâm thương mại, trường học các cấp và nhiều tiện ích sinh hoạt khác. Mọi nhu cầu từ mua sắm, học tập đến vui chơi giải trí đều có sẵn trong bán kính gần, cực kỳ thuận tiện cho cuộc sống gia đình.
-Kết cấu nhà:
-Nhà xây độc lập 5 tầng, có thang máy nhập khẩu, thiết kế hiện đại, sang trọng với kính KOG cao cấp.
-Tầng 1: Phòng khách rộng rãi + bếp + vệ sinh.
-Tầng 2, 3, 4: 3 phòng ngủ lớn, thiết kế thoáng, vệ sinh đầy đủ.
-Không gian các tầng được tối ưu ánh sáng tự nhiên, nội thất được đầu tư kỹ lưỡng, ở rất giữ gìn.
-Phù hợp cho gia đình nhiều thế hệ sinh sống lâu dài.
-Dân trí khu vực:
-Khu dân cư văn minh, hàng xóm thân thiện, dân trí cao, an ninh đảm bảo. Môi trường sống yên tĩnh, đáng sống.
-Pháp lý:
-Sổ đỏ chính chủ, vuông vắn đẹp, pháp lý rõ ràng, quy hoạch ổn định, giao dịch nhanh chóng.
-Nay gia đình rao bán với giá 9 tỷ nhưng có thương lượng với khách thiện chí, tránh tình trạng khảo giá các bên.
-Liên hệ: Quang (Miễn trung gian môi giới).</t>
-        </is>
-      </c>
-      <c r="R174" t="n">
         <v>131803605</v>
       </c>
     </row>
@@ -14115,39 +9893,6 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>21.027077</v>
-      </c>
-      <c r="O175" t="n">
-        <v>105.923355</v>
-      </c>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>Tôi bán nhà Nguyễn Văn Linh-Long Biên, 38m 6T thang máy, 20 oto tránh</t>
-        </is>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>Gia đình chuyển đổi kế hoạch sinh sống để thuận tiện công việc và gần người thân hơn, nên muốn nhượng lại căn nhà tự xây dựng, đầu tư rất kỹ từ thiết kế đến nội thất.
-Vị trí:
-Nhà nằm trong khu dân cư ổn định, ngõ vào dễ đi, cách trục ô tô chỉ vài bước chân. Kết nối nhanh ra các tuyến đường lớn, thuận tiện di chuyển vào trung tâm và các khu vực lân cận.
-Tiện ích xung quanh:
-Khu vực đầy đủ tiện ích: gần chợ, trường học các cấp, khu vui chơi, dịch vụ thiết yếu. Cuộc sống sinh hoạt thuận tiện, phù hợp cho gia đình ở lâu dài.
-Kết cấu nhà:
-Nhà xây 6 tầng có thang máy, thiết kế hiện đại, tối ưu không gian.
-Tầng 1: Phòng khách + vệ sinh + khu để xe.
-Tầng 2,3,4: Phòng ngủ rộng, vệ sinh khép kín, nội thất đồng bộ.
-Tầng 5: Khu bếp ấm cúng, thiết kế riêng biệt.
-Tầng 6: Phòng thờ + sân thượng thoáng mát.
-Nội thất được lựa chọn kỹ lưỡng, phong cách sang trọng, gia chủ để lại gần như toàn bộ.
-Dân trí khu vực:
-Hàng xóm thân thiện, dân trí cao, an ninh đảm bảo. Khu vực yên tĩnh, phù hợp để an cư lâu dài.
-Pháp lý:
-Sổ đỏ chính chủ, pháp lý rõ ràng, giao dịch nhanh gọn.
-Nay gia đình rao bán với giá 8 tỷ nhưng có thương lượng với khách thiện chí, tránh tình trạng khảo giá các bên.
-Liên hệ: Quang (Miễn trung gian môi giới).</t>
-        </is>
-      </c>
-      <c r="R175" t="n">
         <v>131803419</v>
       </c>
     </row>
@@ -14202,39 +9947,6 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>21.039669</v>
-      </c>
-      <c r="O176" t="n">
-        <v>105.90413</v>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>Tôi bán nhà Chu Huy Mân, ngay hồ Sài Đồng-Long Biên, 52m 5T, 20m otođỗ</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>Gia đình có kế hoạch chuyển đổi nơi sinh sống để thuận tiện công việc và gần người thân hơn, nên muốn nhượng lại căn nhà tự tay xây dựng, chăm chút từng chi tiết với nhiều tâm huyết.
-Vị trí:
-Nhà nằm trong khu trung tâm phát triển, đường trước nhà thoáng, di chuyển thuận tiện ra các trục chính. Khu vực dân cư hiện hữu, kết nối nhanh tới các cây cầu lớn và khu nội đô, rất tiện đi lại.
-Tiện ích xung quanh:
-Xung quanh đầy đủ tiện ích: gần chợ, trường học các cấp, khu vui chơi, dịch vụ sinh hoạt… đáp ứng đầy đủ nhu cầu của gia đình. Môi trường sống tiện nghi, phù hợp cả ở lâu dài hoặc đầu tư giữ tài sản.
-Kết cấu nhà:
-Nhà xây độc lập 6 tầng, có thang máy, thiết kế hiện đại, tối ưu công năng.
-Tầng 1: Khu để xe rộng rãi + vệ sinh.
-Tầng 2: Phòng khách sang trọng + bếp.
-Tầng 3,4,5: Phòng ngủ rộng, vệ sinh khép kín, nội thất cao cấp.
-Tầng 6: Phòng thờ + sân phơi thoáng.
-Nội thất được đầu tư đồng bộ, chất lượng cao, gia chủ để lại gần như toàn bộ – chỉ cần xách vali về ở.
-Dân trí khu vực:
-Khu dân cư văn minh, hàng xóm thân thiện, an ninh đảm bảo. Chủ yếu là các gia đình ổn định, ý thức tốt, môi trường sống yên tâm và lâu dài.
-Pháp lý:
-Sổ đỏ chính chủ, pháp lý rõ ràng, sẵn sàng giao dịch nhanh chóng.
-Nay gia đình rao bán với giá 9 tỷ nhưng có thương lượng với khách thiện chí, tránh tình trạng khảo giá các bên.
-Liên hệ: Quang (Miễn trung gian môi giới).</t>
-        </is>
-      </c>
-      <c r="R176" t="n">
         <v>131803274</v>
       </c>
     </row>
@@ -14289,32 +10001,6 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O177" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>🌟 NHÀ ĐẸP NGỌC THỤY – 50M² – NHỈNH 16 TỶ</t>
-        </is>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🌟 NHÀ ĐẸP NGỌC THỤY – 50M² – NHỈNH 16 TỶ 🌟
-🚗 Ngõ thông, xe 7 chỗ ra vào thoải mái, cực gần đường lớn  
-🌳 Gần công viên, chợ Ngọc Thụy, trường Việt Pháp, Khai Sơn Hill  
-🏡 Mặt tiền 4.6m, xây đơn lập bề thế, ở cực thích  
-✨ Thiết kế tiện nghi:
-- Tầng 1 gara ô tô  
-- Tầng 2,3,4 mỗi tầng 1 phòng ngủ rộng  
-- Tầng 5 khách bếp sang xịn  
-- Tầng 6 phòng thờ, sân phơi thoáng
-📩 Nhà đẹp vị trí sáng, khách quan tâm inbox em xem nhà ngay</t>
-        </is>
-      </c>
-      <c r="R177" t="n">
         <v>131779172</v>
       </c>
     </row>
@@ -14369,29 +10055,6 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O178" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>QUÁ RẺ ! 12 TỶ 💰NHÀ MỚI KENG -  66M2 x 6 TẦNG x MT 5M - THANG MÁ</t>
-        </is>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: QUÁ RẺ ! NHỈNH 12 TỶ 💰NHÀ MỚI KENG -  66M2 x 6 TẦNG x MT 5M - THANG MÁY - FULL ĐỒ NỘI THẤT 
-🔹️️ Vị trí : Ngọc Thuỵ - Bồ Đề - Long Biên - Gần  Khai Sơn Hill - Học viện Hậu Cần - Trường cấp 1,2 - Công viên - Hồ điều hòa thoáng mát... 
-📚 Sổ đỏ sẵn sàng – Giao dịch nhanh
-━━━━━━━━━━━
-☎️ LH em Đoan dẫn xem nhà - KHÔNG ĐĂNG ẢO : *** (gọi/zalo)
-📹Tiktok nhiều nhà đẹp: CỘ CỘ TÊN LÀ ĐOAN BĐS LONG BIÊN
-#nhadep #nhadeplongbien #ngocthuy #ngoclam #nguyenvancu #hongtien</t>
-        </is>
-      </c>
-      <c r="R178" t="n">
         <v>131786945</v>
       </c>
     </row>
@@ -14446,37 +10109,6 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>21.043814</v>
-      </c>
-      <c r="O179" t="n">
-        <v>105.872314</v>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>🏡 Nhà đẹp full nội thất, mặt ngõ Nguyễn Văn Cừ - giá chỉ hơn 9 tỷ</t>
-        </is>
-      </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 SẬP GIÁ - CHỦ CẦN THANH KHOẢN NHANH 🔥  
-🏡 Nhà đẹp full nội thất, mặt ngõ Nguyễn Văn Cừ - giá chỉ hơn 9 tỷ
-📌 Thông tin chi tiết:  
-📐 Diện tích: 33m2  🏢 Kết cấu: 6,5 tầng  🛗 Có thang máy  
-📍 Vị trí quá đẹp:  
-🚗 20m ra ô tô tránh, đỗ ngày đêm  
-🛒 Cạnh chợ dân sinh  
-👶 Gần trường mầm non  
-🏫 Gần cấp 1, cấp 2  
-🛣️ Di chuyển thuận tiện, sinh hoạt cực tiện
-💰 Giá chỉ hơn 9 tỷ  
-📈 Cơ hội tốt cho khách mua ở hoặc đầu tư giữ tiền
-━━━━━━━━━━━
-☎️ LH em Đoan dẫn xem nhà - KHÔNG ĐĂNG ẢO : *** (gọi/zalo)
-📹Tiktok nhiều nhà đẹp: CỘ CỘ TÊN LÀ ĐOAN BĐS LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="R179" t="n">
         <v>131779011</v>
       </c>
     </row>
@@ -14531,35 +10163,6 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>21.022837</v>
-      </c>
-      <c r="O180" t="n">
-        <v>105.88859</v>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>Bán nhà Tư Đình 71m2 x 7 tầng,thang máy,full NT</t>
-        </is>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>💥💥💥Bán Nhà Phố Tư Đình 71m2 x 7 tầng, thang máy ngõ thông 2 ô tô 🚘 để trong nhà,vị trí rất đẹp.
--Cạnh Chung Cư,Công viên hồ đắp nếp.
--Full nội thất chỉ việc về ở ngay
--Cách Cầu Trần Hưng Đạo chỉ 350m,giáp Lâm Du-Bồ Đề
--Chợ,Trường học bao quanh
-*Thiết kế:
--Tầng 1: Gara để được 2 xe 🚗 
--Tầng 2,3: 01 pn master
--Tầng 4: chia 2 Phòng ngủ
--Tầng 5 : phòng khách,bếp
--Tầng 6: phòng thờ,sân phơi
--Tầng 7 : sân thượng thiết kế bàn trà,bếp nướng BBQ…
-*Giá: 19.95 tỷ (có thương lượng)
-☎️: Mr Thái Bùi  (để xem nhà) - ảnh chuẩn, thông tin chuẩn 100%</t>
-        </is>
-      </c>
-      <c r="R180" t="n">
         <v>130550165</v>
       </c>
     </row>
@@ -14614,28 +10217,6 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>21.018677</v>
-      </c>
-      <c r="O181" t="n">
-        <v>105.88481</v>
-      </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ BÁT KHỐI THÔNG CỔ LINH LONG BIÊN 32M 5T FULL ĐỒ CHỈ 6.35 TỶ</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ CỔ LINH THÔNG BÁT KHỐI 32M 5TẦNG NGÕ 2,6M SÂN CỔNG ĐỂ XE GIÁ 6,35 TỶ CTL 
- Diện tích : 32m mặt tiền 3,45m vuông vắn . Ngõ 2,6m rộng thoáng , sân cổng để xe . 
- Nhà xây dựng 5tầng thiết kế hiện đại gồm 3 ngủ, 1 thờ , khách + bếp , sân phơi đầy đủ công năng 
- Vị trí trung tâm bán kính 200m đầy đủ tiện ích : chợ - trường học các cấp  , công viên cây xanh khu vui chơi 
-CAM KẾT SỔ ĐỎ PHÁP LÝ CHUẨN MUA BÁN NGAY 
- Giá mong muốn : 6,35 TỶ CTL , Hỗ trợ vay vốn ngân hàng 80%-20 năm 
- LH : Em Thơm  xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R181" t="n">
         <v>131512287</v>
       </c>
     </row>
@@ -14690,33 +10271,6 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>21.043318</v>
-      </c>
-      <c r="O182" t="n">
-        <v>105.86531</v>
-      </c>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>CON NHỎ CHUYỂN HÀ ĐÔNG BÁN NHÀ LONG BIÊN 32M 6T FULL ĐỒ CHỈ 6.85TY CTL</t>
-        </is>
-      </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ LONG BIÊN XÂY ĐỘC LẬP 1 CĂN 32M 6 TẦNG 2 THOÁNG TRƯỚC SAU- FULL NỘI THẤT CHỈ VÀO Ở , BÁN THIỆN CHÍ 6.85 TỶ CTL . NGÕ NÔNG-OTO ĐỖ CỔNG , SÂN CỔNG RIÊNG 1 MÌNH SỬ DỤNG .
-Diện Tích : 32m mặt tiền 4m vuông vắn , ngõ 2,5m oto đỗ cửa- không đối nhau, sân cổng riêng sd 1 mình. 
-Nhà 6 tầng thiết kế hiện đại , đẹp chắc chắn : 
-- Tầng 1 : khách , vs 
-- Tầng 2: bếp rộng rãi 
-- Tầng 3.4.5 : Phòng Ngủ + vs 
-- Tầng 6 : Phòng Thờ , sân phơi . 
-Nhà chủ để lại toàn bộ nội thất xịn khách chỉ vào  ở luôn : ti vi, tủ lanhh, máy giặt , bàn ghế , giường tủ , điều hòa ...  
-Vị trí : đông dân khu cán bộ dân trí cao , tiện ích 200m đầy đủ không thiếu gì : chợ , truong học các cấp , 3 phút qua Aeon mall , cầu Vĩnh Tuy . 
-CAM KẾT SỔ ĐỎ CHÍNH CHỦ , PHÁP LÝ CHUẨN MUA BÁN NGAY , KHÔNG TRANH CHẤP- QUY HOACJK - KHÔNG LỖI PHONG THỦY . 
-Gía mong muốn : 6.85 tỷ ctl bao thuế phí sang tên . Hỗ trợ vay vốn ngân hàng 80%-20 năm 
-LH : Em Thơm  xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R182" t="n">
         <v>131514763</v>
       </c>
     </row>
@@ -14771,32 +10325,6 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O183" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ 206 CỔ LINH 45M 6T THANG MÁY-GARA 7 CHỖ, FULL NỘI THẤT ~ 12 TỶ</t>
-        </is>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>🟠✅BÁN NHÀ NGÕ 206 CỔ LINH- ĐỐI DIỆN AEON MALL 45M 6 TẦNG THANG MÁY- GARA Ô TÔ 7 CHỖ VÀO- ĐƯỜNG TRẢI NHỰA FULL NỘI THẤT- GIÁ &gt; 12 TỶ TL MẠNH ĐẦU TƯ XUỐNG TIỀN BÁN . 
-🏠🚘Nhà mới xây 45m 6 Tầng có thang máy. Đường rộng 5m Ô tô 7 chỗ vào nhà thoải mái.
-Thiết kế :-  Tầng 1 : gara oto 7 chỗ 
-- Tầng 2: Khách , bếp 
-- Tầng 3,4,5 : phòng ngủ , vs vô cùng rộng 
-- Tầng 6 : phòng thờ, sân phơi 
-Nhà trang bị đồ chính hãng, điều hoà âm trần, xây dựng hiện đại , khách chỉ vào ở . 
-🔶Vị trí ngay khu đối diện Aeon Mall ngõ 206 Cổ Linh, cách cầu Vĩnh Tuy 2 phút, sang phố rất gần. bán kính 200m đầy đủ : chợ - trường học các cấp ... 
-📕Sổ đỏ chính chủ, ko tranh chấp ko quy hoạch, pháp lý chuẩn sẵn sàng mua bán ngay. 
-- Giá mong muốn : ~ 12 tỷ ctl, bao thuế phí sang tên . Hỗ trợ vay vốn ngân hàng 70%-30 năm 
-☎️LH Em Thơm  để đi xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R183" t="n">
         <v>131575097</v>
       </c>
     </row>
@@ -14851,28 +10379,6 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O184" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP TRUNG TÂM THẠCH BÀN 33M 5T 4NGỦ NGÕ RỘNG,70M RA CHỢ THẠCH BÀ</t>
-        </is>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>🍀🍀🍀 NHÀ ĐẸP TRUNG TÂM NHẤT THẠCH BÀN 33M 5 TẦNG 4NGỦ NGÕ RỘNG , Ô TÔ CACH 20M-70M RA CHỢ THẠCH BÀN 🔥💥 
-💥 Diện tích : 33M mặt tiền 4,5 M vuông vắn , 2 Thoáng- mở rất nhiều cửa sổ , ngõ rộng 2,8 M để xe -20M ra ôtô, 50m ra trục chính đường 8m kinh doanh , 100 m ra chợ Thạch bàn . 
-🏡 Nhà xây dựng 5 tầng tròn kiên cố chắc chắn gồm :  4 ngủ , 1 thờ , khách - bếp , sân phơi 
-🌹🌹 Vị trí trung tâm nhất Thạch bàn tiện ích bán kính 100m đầy đủ : chợ - trường học các cấp -3 phút ra TTTM AEON MALL , Cầu Vĩnh Tuy đi các ngả . 
-🍀 🌷 CAM KẾT SỔ ĐỎ CHÍNH CHỦ , KHÔNG TRANH CHẤP QUY HOẠCH , SẴN SÀNG MUA BÁN 
-🌾🌾 Giá 7,5 tỷ  ( có thương lượng ) TẶNG FULL NỘI THẤT . 
-☎️☎️  Liên hệ em Thơm  để có giá *** !</t>
-        </is>
-      </c>
-      <c r="R184" t="n">
         <v>131168613</v>
       </c>
     </row>
@@ -14927,32 +10433,6 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>21.02974</v>
-      </c>
-      <c r="O185" t="n">
-        <v>105.91316</v>
-      </c>
-      <c r="P185" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ MẶT NGÕ KINH DOANH THẠCH BÀN 40M 7TẦNG THANG MÁY- 13,5 TỶ</t>
-        </is>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>💥💥 BÁN NHÀ MẶT ĐƯỜNG KINH DOANH TỐT TẠI THẠCH BÀN 40M 7TẦNG THANG MÁY CHỈ 13,5 TỶ CTL THIỆN CHÍ 🔥🔥
-🍀🍀Diện tích :  40m vuông vắn , hướng tây tứ trạch, đường trước nhà 2 oto tránh thông đang kinh doanh tốt.  
-🏡🏡 Nhà xây dựng 7 tầng hiện đại, xây độc lập 1 căn chắc chắn , thang máy : 
-📍 Tầng 1: gara,  kinh doanh, hoặc cho thuê \
-📍 Tầng 2,3,4,5: thông full tầng , vs khép kín 
-📍 tầng 6 : Khách + bếp 
-📍 Tầng 7 : phòng thờ , sân phơi 
-✏️✏️  Ngay liền kề Aeon Long Biên - Chợ - Trường học - UBND xung quanh đầy đủ tiện ích.Tiện ích ngập tràn, chỉ cần xách vali về ở, Ngay cổng khu công nghiệp Hanel với 50 nghìn công nhân kinh doanh tốt các loại . 
-Sổ đỏ chỉnh chủ, ko tranh chấp, quy hoạch, sẵn sàng mua bán ngay . 
-🌹🌹 Giá mong muốn : 13,5 tỷ ctl, bao thuế phí sang tên - hỗ trợ vay vốn ngân hàng 70% 20 năm . 
-☎️☎️ Liên hệ/zalo: Em Thơm  xem nhà trực tiếp.</t>
-        </is>
-      </c>
-      <c r="R185" t="n">
         <v>131055286</v>
       </c>
     </row>
@@ -15007,27 +10487,6 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O186" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ THẠCH BÀN CỔ LINH 35M 5T FULL ĐỒ CHỈ 6.95TỶ -15M ÔTÔ ĐI THÔNG</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>🟠✅BÁN NHÀ THẠCH BÀN 35M 5 TẦNG - 20M RA ĐƯỜNG THÔNG Ô TÔ- FULL NỘI THẤT- GIÁ 6,95 TỶ
-🏠Nhà 35m xây 5 tầng hiện đại: Thiết kế đầy đủ 3 ngủ, 4 vệ sinh, phòng thờ sân phơi.
-🔶Gần khu đô thị Garden City, chỉ cách 20m ra đường thông Ô tô, Khu vực đang quy hoạch đường giao thông rất đẹp.
-📕Sổ đỏ chính chủ, ko quy hoạch, k tranh chấp , sẵn sàng muia bán ngay . 
-- Gía mong muốn : 6.95 tỷ ctl bao thuế sang tên , Hỗ trợ vay vốn ngân hàng 70%-30 năm 
-☎️☎️ LH : Em Thơm *** xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R186" t="n">
         <v>130289085</v>
       </c>
     </row>
@@ -15082,33 +10541,6 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>21.02555</v>
-      </c>
-      <c r="O187" t="n">
-        <v>105.89239</v>
-      </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ MẶT NGÕ THÔNG PHỐ TRẠM 50M 6T THANG MÁY-Ô TÔ THÔNG - 12,7 TỶ</t>
-        </is>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>Bán nhanh căn nhà phố Trạm - long biên 50m 6 Tầng lô góc, ô tô vào nhà đi thông- Giá 12,7 tỷ ctl thiện chí
-Diện tích 50m mt 4m nở hậu , lô góc 2 mặt thoáng . Ngõ trước nhà rộng ô tô vào đi thông- 30m ra mặt phố Trạm, 250m lên cầu Vĩnh tuy .
-Nhà Xây dựng 6 tầng thiết kế mới hiện đại - Thang Máy
-Tầng 1 : gara ô tô + vs
-Tầng 2: Khách + Bếp
-Tầng 3,4 : ngủ + vs
-Tầng 5 : 2 ngủ + vs
-Tầng 6 : phòng thờ + Sân phơi
-Nhà Lô góc mở rất nhiều cửa thoáng sáng tự nhiên , Gia chủ đang ở làm toàn bộ nội thất đẹp xịn xò tặng lại cho khách mới về ở luôn .
-CAM KẾT SỔ ĐỎ CHÍNH CHỦ- PHÁP LÝ ĐẦY ĐỦ SẴN SÀNG MUA BÁN NGAY .
-Giá mong muốn : 12,7 tỷ bao toàn bộ thuế phí sang tên , có thương lượng thiện chí .
-LH : Em Thơm  mien phi</t>
-        </is>
-      </c>
-      <c r="R187" t="n">
         <v>131055535</v>
       </c>
     </row>
@@ -15163,34 +10595,6 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O188" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P188" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ LONG BIÊN 71M 5T GARA, THANG MÁY , FULL ĐỒ CHỈ 14,2 TỶ K LỖI</t>
-        </is>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>🌇🌇🌇 Mở bán căn nhà 70m 5tầng thang máy .
-Tại Chu Huy Mân, Phúc Đồng , Long Biên Hà Nội GIÁ CHỈ 14,2 TỶ FULL NỘI THẤT . 
-✏️ Đất : 70M vuông vắn , ngõ ô tô vào nhà thoải mái 
-✅ Nhà 5 tầng hiện đại - mới Thiết kế: 
-📌 Tầng 1: Sân cổng oto+ P khách + Bếp + sân sau nhà
-📌 Tầng 2: 2 Ngủ full nội thất 
-📌 Tầng 3: 2 ngủ full nội thất
-📌 Tầng 4: 1 ngủ + 1 thờ
-📌 Tầng 5: hai sân trước sau.
-Full nội thất tivi, tủ lạnh, điều hoà, bàn ăn, Sofa...vv
-💰 Giá 14,2 tỷ ctl- Bao thuế phí sang tên , Hỗ trợ vay vốn ngân hàng 70% 
-🍀🍀 CAM KẾT SỔ ĐỎ CHÍNH CHỦ - PHÁP LÝ CHUẨN MUA BÁN NGAY 
-☎️☎️ LH : Em Thơm *** xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R188" t="n">
         <v>130277438</v>
       </c>
     </row>
@@ -15245,29 +10649,6 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O189" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>NHÀ DÂN XÂY 66M 3TẦNG THẠCH BÀN - 200M NGÃ TƯ CỔ LINH, LONG BIÊN ~ 8TY</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: BÁN ĐẤT 66M TẶNG NHÀ 3 TẦNG DÂN XÂY Ở LUÔN NGÕ  249 THẠCH BÀN - NGÃ TƯ CỔ LINH . CÁCH 1 NHÀ TA ĐƯỜNG Ô TÔ  GIÁ CHỈ 8,7 TỶ CTL THIỆN CHÍ 
-Diện tích : 66M, oto 7 chỗ đỗ trước nhà , 7-80m ra mặt phố Thạch Bàn , 200m ra Ngã tư Cổ Linh . 
-Nhà dân xây 3 tầng thiết kế 3 ngủ , phòng khách - bếp riêng biệt ở luôn . Nhà có sân cổng riêng để xe 1 mình thoải mái 
-Vị trí: Trung tâm nhất Thạch bàn , 200m ra ngã Tư Cổ Linh , TTTM AEON MALL - Cầu Vĩnh Tuy , 200-250m đầy đủ tiện ích : Chợ - trường học các cấp . 
-CAM KẾT SỔ ĐỎ CHÍNH CHỦ - PHÁP LÝ CHUẨN SẴN SÀNG MUA BÁN NGAY 
-Giá mong muốn : 8,7 Tỷ có thương lượng , bao thuế phí sang tên . Hỗ trợ vay vốn ngân hàng 80%-20 năm 
- LH : Em Thơm  xem miễn phí</t>
-        </is>
-      </c>
-      <c r="R189" t="n">
         <v>131476772</v>
       </c>
     </row>
@@ -15322,28 +10703,6 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>21.028515</v>
-      </c>
-      <c r="O190" t="n">
-        <v>105.91935</v>
-      </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ SÀI ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ LIỀN KỀ SÀI ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng xây kiên cố 
-+ Diện tích ; 130m2- MT 9m 
-+ Nhà lắp đặt đầy đủ nội thất 
-+ Đường trước nhà 5m -đường thông tứ ngả 
-+ Tiện ích ngập tràn ; nhà cạnh vườn hoa công viên - trường các cấp - hàng xóm Vihom - nhà lại gần TTTM -AEON -Long biên - sân gôn long biên - và khu vực dân trí cao - mất 6 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên thổ cư long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R190" t="n">
         <v>123952277</v>
       </c>
     </row>
@@ -15398,29 +10757,6 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>21.012678</v>
-      </c>
-      <c r="O191" t="n">
-        <v>105.904854</v>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỰ KHỐI LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỰ KHỐI LONG BIÊN HÀ NỘI.
-+ Nhà 8 chủ xây kiên cố 
-+ Diện tích ; 135m2- MT 7m
-+ Hiện tại nhà đang cho thuê văn phòng dòng tiền tháng đều
-+ Hướng đông bắc
-+ Đường trước nhà 6m- đường thông tứ ngả 
-+ Tiện ích ; nhà nằm trong trung tâm phường - rùi trường các cấp- chợ - TTTM AEON -Long biên và khu vực đông dân cư - chỉ mất 10 phút là qua cầu tranh trì sang trung tâm thành phố hà nội rùi.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R191" t="n">
         <v>129525495</v>
       </c>
     </row>
@@ -15475,30 +10811,6 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>21.019062</v>
-      </c>
-      <c r="O192" t="n">
-        <v>105.903404</v>
-      </c>
-      <c r="P192" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ LIỀN KỀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ LIỀN KỀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Biệt thự 5 tầng ( căn góc 3 )
-+ Diện tích ; 145m2- MT quyền lực 20m
-+ Nội thất đầy đủ
-+ Hướng đông bắc 
-+ Đường trước nhà 12m - vỉa hè đường thông tứ ngả 
-+ Hiện đang cho thuê dòng tiền tháng 
-+ Tiện ích ngập tràn ; nhà căn góc 3 mặt thoáng - nhà lại gần trường các cấp - TTTM -AEON -Long biên - và khu vực dân trí cao - chỉ mất có 10 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R192" t="n">
         <v>129187011</v>
       </c>
     </row>
@@ -15553,28 +10865,6 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>21.012678</v>
-      </c>
-      <c r="O193" t="n">
-        <v>105.904854</v>
-      </c>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ LIỀN KỀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ LIỀN KỀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà xây thô 4 tầng 
-+ Diện tích ; 92m2- Mt 7,6m
-+ Hướng tây bắc 
-+ Đường trước nhà 7m - vỉa hè đường chạy vòng quanh
-+ Tiện ích ngập tràn ; nhà nằm trong khu vực dân trí cao - nhà lại gần trường các cấp - chợ - TTTM -AEON -Long biên và khu vưc đông dân cư - chỉ mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R193" t="n">
         <v>129154366</v>
       </c>
     </row>
@@ -15629,29 +10919,6 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>21.05286</v>
-      </c>
-      <c r="O194" t="n">
-        <v>105.92033</v>
-      </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ PHÚC LỢI LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ PHÚC LỢI LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng chủ xây kiên cố - thang máy nhập khẩu 
-+ Diện tích ; 90m2- MT 5m
-+ Hướng tây bắc 
-+ Nhà lắp đặt phun nội thất 
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả 
-+ Tiện ích ngập tràn ; nhà gần trường các cấp - chợ - TTTM -AEON -Long biên - và khu vực đông dân cư - chỉ mất có 10 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R194" t="n">
         <v>128795972</v>
       </c>
     </row>
@@ -15706,28 +10973,6 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>21.049894</v>
-      </c>
-      <c r="O195" t="n">
-        <v>105.89186</v>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ PHÚC ĐỒNG LONGH BIÊN HÀN NỘI.</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ PHÚC ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà 7 tầng chủ xây kiên cố 
-+ Diện tích ; 85m2- MT 5m 
-+ Nhà lắp đặt phun nội thất đẹp 
-+ Hướng tây 
-+ Tiện ích ngập tràn ; nhà nằm trong khu phân lô quân đội - An ninh tốt - dân trí cao- nhà lại cạnh sân gôn long biên - rùi TTTM -AEON -Long biên -trường các cấp - và khu vực dân trí cao- chỉ mất có 6 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R195" t="n">
         <v>129509429</v>
       </c>
     </row>
@@ -15782,29 +11027,6 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>21.036516</v>
-      </c>
-      <c r="O196" t="n">
-        <v>105.91136</v>
-      </c>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ SÀI ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ SÀI ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà 2 tầng cũ chủ xây kiên cố
-+ Diện tích ; 85m2- MT 5m
-+ Hướng tây bắc 
-+ Đường trước nhà 12m - vỉa hè đường thông tứ ngả 
-+ Hiện nhà đang cho thuê dòng tiền tháng đều 
-+ Tiện ích ; nhà nằm trên mặt tuyến phố lớn của long biên - kinh doanh sầm uất ngày và đêm - nhà lại gần trường các cấp - chợ - TTTM -AEON -Long biên - và khu vực dân trí cao - chỉ mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R196" t="n">
         <v>126427196</v>
       </c>
     </row>
@@ -15859,29 +11081,6 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O197" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng chủ xây kiên cố 
-+ Diện tích ; 35m2- MT 3,7m
-+ Nhà lắp đặt đầy đủ nội thất 
-+ Hướng đông nam - quanh năm mát mẻ
-+ Đường trước nhà 6m - đường thông tứ ngả 
-+ Tiện ích ; khách mua về vừa ở vừa kinh doanh nhỏ lẻ thì quá tuyệt vời - nhà lại gần trường các cấp -chợ - TTTM -AEON -Long biên - chỉ mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên nhà đất long dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R197" t="n">
         <v>128796887</v>
       </c>
     </row>
@@ -15936,29 +11135,6 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>21.035637</v>
-      </c>
-      <c r="O198" t="n">
-        <v>105.91076</v>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ SÀI ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ SÀI ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng chủ xây kiên cố 
-+ Diện tích ; 140m2- MT 7,2m
-+ Hướng đông nam - quanh năm thoáng mát
-+ Hiện nhà đang cho thuê văn phòng cty - dòng tiền tháng 
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả
-+ Tiện ích ; nhà nằm trong khu vực An Ninh Tốt - Dân trí cao - nhà lại gần hồ vườn hoa công viên quanh năm mát mẻ - nhà lại gần trường các cấp - TTTM -AEOn -Long biên chỉ mất 10 phút lái xe sang tới trung tâm hồ hoàn kiếm hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R198" t="n">
         <v>127183786</v>
       </c>
     </row>
@@ -16013,28 +11189,6 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O199" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ LIỀN KỀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ LIỀN KỀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 4 tầng kiên cố 
-+ Diện tích ; 145m2- MT 8m 
-+ Hướng đông nam quanh năm mát mẻ
-+ Đường trước nhà 6m - ô tô vào nhà 
-+ Tiện ích ; nhà nằm trong khu dân trí cao An ninh Tốt - nhà gần trường các cấp - chợ - TTTM -AEON -Long biên - mất 7 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên thổ cư long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R199" t="n">
         <v>123846527</v>
       </c>
     </row>
@@ -16089,29 +11243,6 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O200" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng chủ xây kiên cố - thang máy nhập khẩu 
-+ Diện tích ; 56m2- MT 3,9m
-+ Hướng đông nam - quanh năm mát mẻ 
-+ Đường trước nhà 6m - ngõ thông ô tô vào nhà đường thông tứ ngả 
-+ Khách mua nhà về ở vừ ở vừa kinh doanh thì quá tuyệt vời - vì nhà ngay đầu chợ 
-+ Tiện ích ; nhà gần ngay chợ - trường các cấp - TTTM- AEON -Long biên - hồ công viên - và khu vực đông dân cư - mất 10 phút lái xe sang trung tâm thành phố.
-+ Liên hệ ;***- Em thắng chuyên thổ cư long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R200" t="n">
         <v>124087193</v>
       </c>
     </row>
@@ -16166,29 +11297,6 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>21.041908</v>
-      </c>
-      <c r="O201" t="n">
-        <v>105.873924</v>
-      </c>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BỒ ĐỀ LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BỒ ĐỀ LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng mới - thang máy nhập khẩu 
-+ Diện tích ; 58m2- MT 3,9m
-+ Nội thất cơ bản 
-+ Hướng tây
-+ Đường trước nhà 3m - ngõ thông tứ ngả - ô tô vào nhà 
-+ Tiện ích ; nhà gần cạnh trường các cấp chợ - Bệnh viện tâm Anh -cầu trần hưng đạo - và khu vực dân trí cao - chỉ mất 10 phút lái xe là sang tới trung tâm hồ hoàn kiếm hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R201" t="n">
         <v>127125695</v>
       </c>
     </row>
@@ -16243,25 +11351,6 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>21.037483</v>
-      </c>
-      <c r="O202" t="n">
-        <v>105.902596</v>
-      </c>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP, 50M2 5 TẦNG, DÂN XÂY, PHỐ PHÚC ĐỒNG, LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ 50M2, 5 TẦNG, 6 NGỦ, PHỐ CHU HUY MÂN, PHÚC ĐỒNG, LONG BIÊN, NGÕ RỘNG THOÁNG, OTO ĐỖ GẦN, CHỈ NHỈNH 9 TỶ XÍU
-VỊ TRÍ : CẠNH VINCOM, TTTM AEON, BỆNH VIỆN ĐỨC GIANG, TÂM ANH 
-KẾT NỐI : CẦU THANH TRÌ, VĨNH TUY, CHƯƠNG DƯƠNG SANG NÔI ĐÔ
-LH : EM NGỌC SĐT/ZALO ĐI XEM MIỄN PHÍ.</t>
-        </is>
-      </c>
-      <c r="R202" t="n">
         <v>131787143</v>
       </c>
     </row>
@@ -16316,40 +11405,6 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>21.044842</v>
-      </c>
-      <c r="O203" t="n">
-        <v>105.86866</v>
-      </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ NGỌC LÂM-60M*6 T-THANG MÁY-SÁT Ô -NỘI THẤT-Ở NGAY -HƠN 13 TỶ</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ NGỌC LÂM - 60M*6 T- MẶT TIỀN TÀI LỘC - THANG MÁY - 10m Ô TÔ TRÁNH - NỘI THẤT ĐẸP - Ở NGAY, nhỉnh 13 tỷ 
-Mô tả : 
-💎 Nhà dân xây cực chắc – đẹp mới tinh, thiết kế hiện đại, phòng nào cũng sáng thoáng
-🚗 Ô tô  tránh gần   – ngõ thông nông đi lại cực tiện
-🌳 Diện tích rộng 60m –cực hiếm tầm tiền nhỉnh 13 tỷ 
-- vài bước chân ra mặt phố ô tô tránh 
-📍 Vị trí trung tâm Long Biên:
- • Vài phút tới BIGC Long Biên.bệnh viện bắc hà .bb Tâm Anh.công viên .chợ ....
- • Gần chợ, trường học các cấp – tiện ích đủ đầy bán kính 1_2km 
- • khu vực phố cổ ngọc lâm, dân trí cao, ở cực sướng
-🏡 Công năng chuẩn ở:
- • Phòng bếp  được thiết kế  bố trí  thang máy cầu thang  điểm cuối vừa vặn tăng độ rộng của không Gian khu vực bếp cực rộng .tiện nghi đầy đủ tủ bếp kệ .....vv
-*Phòng khách tầng lửng không Gian riêng rộng rãi ,bố trí các cửa kính siêu rộng anh sáng vô đối 
-*phòng ngủ thoáng decor  đầy đủ tiện nghi gường tủ cao cấp có  khoảng của sổ  siêu to giúp ánh sáng tự nhiên và không khí tốt hơn thoải mái khi 
- * Sân thượng siêu chill
-💰 Nhỉnh  13tỷ – RẺ NHẤT KHU VỰC – KHÔNG CÓ CĂN THỨ 2
-📞 Gọi ngay kẻo mất: xem là thích – thích là chốt!
-☎️Em Phương  chuyên bđs Long Biên - Gia Lâm
-#BĐSLongBien #bannha #</t>
-        </is>
-      </c>
-      <c r="R203" t="n">
         <v>131753994</v>
       </c>
     </row>
@@ -16404,38 +11459,6 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>21.025381</v>
-      </c>
-      <c r="O204" t="n">
-        <v>105.895256</v>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>Bán nhà Phố Trạm Long Biên 54m kinh doanh đỉnh</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 BÁN NHÀ PHỐ TRẠM – LONG BIÊN – Ô TÔ TRÁNH – THANG MÁY – KINH DOANH ĐỈNH – 54m² x 7 TẦNG – NHỈNH 23 TỶ
-✨ Phố Trạm – tuyến phố đẹp bậc nhất Long Biên, kinh doanh sầm uất- 🚗 Kết nối nhanh sang trung tâm 
-✨Sát AEON MALL - vị trí đón đầu hạ tầng, đặc biệt cầu Trần Hưng Đạo sắp triển khai, tiềm năng tăng giá mạnh
-📐 Thiết kế hiện đại – công năng tối ưu:
-• Tầng 1: Gara ô tô + WC
-• Tầng 2: Phòng khách rộng + WC
-• Tầng 3–4–5: Phòng ngủ master, WC khép kín
-• Tầng 6: Bếp + phòng ăn + phòng thờ + WC
-• Tầng 7: Sân chơi + tiểu cảnh cực chill
-🛗 Nhà xây mới 7 tầng thang máy – chủ đầu tư uy tín – hoàn thiện cao cấp
-🏪 Phù hợp ở kết hợp kinh doanh, văn phòng, cho thuê dòng tiền tốt
-📜 Pháp lý:
-• Sổ đỏ chính chủ – sẵn sàng giao dịch
-⸻
-📞 *** – Hường BĐS Thổ Cư Hà Nội
-📲 Hỗ trợ tận tâm từ A-Z – xem nhà nhanh – làm việc trực tiếp chủ nhà</t>
-        </is>
-      </c>
-      <c r="R204" t="n">
         <v>131754507</v>
       </c>
     </row>
@@ -16490,25 +11513,6 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>21.039703</v>
-      </c>
-      <c r="O205" t="n">
-        <v>105.8727</v>
-      </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>ÁI MỘ - BỒ ĐỀ HƠN 7 TỶ</t>
-        </is>
-      </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>Căn nhà thuộc khu Vip Bồ Đề cạnh trường quốc tế, bệnh viện Tâm Anh. Thích hợp gia đình có ôtô có thể để thoải mái bên ngoài.
-Nhà thiết kế 5 tầng,  2 ngủ, bếp, phòng thờ, vườn cây trên sân thượng.
-Chủ rất thiện chí bán, pháp lý chuẩn, không quy hoạch, không tranh chấp.
-Liên hệ em để xem nhà miễn phí</t>
-        </is>
-      </c>
-      <c r="R205" t="n">
         <v>131614082</v>
       </c>
     </row>
@@ -16563,30 +11567,6 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O206" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>Bán Nhà Phố Cổ Linh 40m x 7 Tầng Thang Máy, Đường Vỉa Hè, Ô Tô Tránh,</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Bán Nhà Phố Cổ Linh 40m x 7 Tầng Thang Máy, Đường Vỉa Hè, Ô Tô Tránh, Đối Diện Trường Học, Kinh Doanh Ngày Đêm.
-- Diện tích 40m2, mặt tiền = hậu 4m, dài 10m.
-- Đường trước nhà ô tô tránh + vỉa hè rộng 13.5m.
-- Vị trí: Mặt ngõ 33 Cổ Linh, Khu vực trung tâm, Giao thông đồng bộ. Ngay ngã tư Cổ Linh – Thạch Bàn, tiện ích đầy đủ: Trường mầm non Hoa Mai, Trường Cấp 2 Thạch Bàn, Cách Aeon Mall Long Biên chỉ 500m
-- Thiết kế 7 Tầng, Thang máy 650kg nhập khẩu, phù hợp làm trụ sở công ty, văn phòng, kinh doanh spa, buôn bán + kết hợp nhà ở.
-- Nhà đang trong quá trình xây dựng, Hoàn thiện như 3D, Bàn giao T8/2026
-Sổ đỏ chính chủ, ko tranh chấp, quy hoạch. Hỗ trợ vay ngân hàng lãi suất tốt.
-Liên hệ: Mr Tùng *** để đi xem nhà trực tiếp và miễn phí</t>
-        </is>
-      </c>
-      <c r="R206" t="n">
         <v>131743289</v>
       </c>
     </row>
@@ -16641,27 +11621,6 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O207" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>📢📢📢Nhà 59m2 x 5 Tầng Ngay Mặt Phố Sân Cổng Riêng - 2 Thoáng - Hơn 10B</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: ✨️Diện tích 59m2 / 5 tầng
-- Mặt tiền 5.3m, nở hậu, hướng Tây Bắc
-- Ngõ trước nhà hơn 2m, cách 15m ra ô tô vào, ngay mặt phố Thạch Bàn kinh doanh sầm uất
-- Nhà thiết kế 4 tầng 1 tum, thang máy, 3 phòng ngủ
-📱Phở bò/ zep lào: Huy Định *** xem nhà 24/7</t>
-        </is>
-      </c>
-      <c r="R207" t="n">
         <v>131773441</v>
       </c>
     </row>
@@ -16716,36 +11675,6 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>21.057554</v>
-      </c>
-      <c r="O208" t="n">
-        <v>105.902435</v>
-      </c>
-      <c r="P208" t="inlineStr">
-        <is>
-          <t>✨ HÀNG HIẾM THƯỢNG THANH – Ô TÔ ĐỖ CỬA 🚗</t>
-        </is>
-      </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>✨ HÀNG HIẾM THƯỢNG THANH – Ô TÔ ĐỖ CỬA 🚗
-ĐƯỜNG QUY HOẠCH 9,5M – VỈA HÈ RỘNG – TIỀM NĂNG TĂNG GIÁ RÕ RÀNG
-💥 Giá đã được chủ nhà giảm nhiều lần – chỉ gia lộc nhẹ cho khách thiện chí!
-🏡 Vị trí trung tâm Thượng Thanh – khu dân cư văn minh, ở cực sướng, đi lại thuận tiện.
-📐 Diện tích rộng hiếm có trong tầm giá – mặt bằng thoáng, thiết kế tối ưu công năng.
-🚧 Quy hoạch mở đường 9,5m KHÔNG vào nhà (hiên chừa 1m) – kiểm tra thoải mái.
-👉 Sau quy hoạch: mặt tiền rộng đẹp, giao thông thuận lợi → giá trị tăng mạnh.
-✨ Nhà mới xây, kết cấu chắc chắn, full nội thất xịn – chỉ việc xách vali về ở!
-🏠 Thiết kế 4 tầng – 5 phòng ngủ, trước sau thoáng:
-• Tầng 1: Để xe + phòng khách + bếp + WC + giếng trời
-• Tầng 2 &amp; 3: Mỗi tầng 2 phòng ngủ + WC
-• Tầng 4: Phòng ngủ/phòng thờ + sân phơi
-• Tum: 2 bình inox Sơn Hà, chống nóng đầy đủ
-📜 Sổ đỏ chính chủ – pháp lý chuẩn – sẵn sàng giao dịch ngay.
-📞 Liên hệ ngay để xem nhà – cơ hội tốt không chờ lâu!</t>
-        </is>
-      </c>
-      <c r="R208" t="n">
         <v>131772183</v>
       </c>
     </row>
@@ -16800,45 +11729,6 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>21.055147</v>
-      </c>
-      <c r="O209" t="n">
-        <v>105.90521</v>
-      </c>
-      <c r="P209" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ VIỆT HƯNG-LÔ GÓC-65M*5-8 TỶx–Ô TÔ GẦN-NGÕ THÔNG -PHÁP LÝ CHUẨN</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ VIỆT HƯNG -LÔ GÓC- 65M*5 Hơn 8 TỶ x– Ô TÔ ĐỖ GẦN  -NGÕ THÔNG -PHÁP LÝ RÕ RÀNG 
-    Mô tả : diện tích 65m2 mặt tiền siêu rộng 
-💎 Nhà dân xây  độc lập cực chắc – đẹp mới tinh, thiết kế hiện đại, phòng nào cũng sáng thoáng
-* Ngõ cực nông cái bước chân ra mặt ngõ ô tô chạy 
-🚗 Ô tô  đỗ  đầu ngõ– ngõ nông thông , đi lại cực tiện
-🌳 Diện tích rộng 65m ,cực hiếm tầm tiền hơn 8 tỷ x
-✅ Nhà có thoáng các mặt tràn ngập nắng gió
-- Tầng 1. Khách + Bếp  thông rộng ( sofa)
-- Tầng 2 -3 mỗi tầng 2  phòng ngủ master rộng vệ sinh khép kín
--  Tầng 4. Phòng thờ + phòng giặt + sân
-✅ Thiết bị cao cấp Vigracera, đèn sưởi, bình nước nóng 30L có cabin tắm. 
-* Cửa nhôm Xingfa cao cấp, kính an toàn* Tủ bếp gỗ công nghiệp cao cấp
-* ful đồ nội thất cao cấp tầng 1
-* Đá thang bộ Granitie, tay vịn cầu thang gỗ Lim
-* Sơn Jotun Majictic cao cấp
-* Hệ thống điện luồn ống tiêu chuẩn, dây Trần Phú
-* Hệ thống thông gió đầy đủ
-* Cấp nước Tiền Phong. PPR, thoát nước Tiền Phong D90-D110mm C2
-* Hệ thống Ineternet Cat6, Camera Fun HD
-.+ Sổ đỏ chính chủ, pháp lý đảm bảo, chủ thiện chí bán.
-💰 HƠN  8tỷ x– RẺ NHẤT KHU VỰC – KHÔNG CÓ CĂN THỨ 2
-📞 Gọi ngay kẻo mất: xem là thích – thích là chốt!
-☎️Em Phương  *** chuyên bđs Long Biên - Gia Lâm
-#BĐSLongBien #bannha #</t>
-        </is>
-      </c>
-      <c r="R209" t="n">
         <v>131527709</v>
       </c>
     </row>
@@ -16893,30 +11783,6 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>21.04372</v>
-      </c>
-      <c r="O210" t="n">
-        <v>105.92593</v>
-      </c>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>MÓT BÁN - LONG BIÊN - Ô TÔ TRÁNH - 6TẦNG THANG MÁY GIẢM CHÀO 500TR.</t>
-        </is>
-      </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dự án: 
-Thông tin chi tiết: MÓT BÁN - LONG BIÊN - Ô TÔ TRÁNH - 6TẦNG THANG MÁY GIẢM CHÀO 500TR. 
-SỔ ĐỎ CHÍNH CHỦ - PHÁP LÝ CHUẨN ĐẸP NÉT
-CANG.
-THÔNG SỐ SIÊU ĐẸP CỰC HIẾM - NHÀ NỞ HẬU
-ĐÓN TÀI LỘC
-Đường trước nhà ô tô tránh nhau, ô tô vào tận nhà thoải mái, ngõ siêu thông thoáng. 
-Nhà thiết kế theo phong cách hiện đại, fom dáng đẹp phù hợp với mọi lứa tuổi. 6 tầng thang máy, căn góc cực hiếm tại khu vực
- Chủ để lại toàn bộ nội thất siêu sịn gồm: Điều hòa, bình nóng lạnh, giường, tủ, bếp ăn... Khách mua chỉ việc ở. *** </t>
-        </is>
-      </c>
-      <c r="R210" t="n">
         <v>131769736</v>
       </c>
     </row>
@@ -16971,27 +11837,6 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>21.038532</v>
-      </c>
-      <c r="O211" t="n">
-        <v>105.91242</v>
-      </c>
-      <c r="P211" t="inlineStr">
-        <is>
-          <t>Bán nhà Sài Đồng- 74mv - 7.x tỷ - Camry đỗ tận cửa</t>
-        </is>
-      </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>- nhà dân xây 5 tầng chắc chắn, không phải nhà thương mại
-- nhà đơn lập, không sân chung, cổng chung, tường chung, móng chung
-- 2 ngoặt từ ngõ vào nhà, đường trước nhà thông ra chợ, trường học.
-- xung quanh nhà biệt thự của quan chức, chủ doanh nghiệp.
-- sổ vuông vắn, chủ thiện mót bán.
-liên hệ *** để xem nhà và gặp chủ nhà</t>
-        </is>
-      </c>
-      <c r="R211" t="n">
         <v>131419617</v>
       </c>
     </row>
@@ -17046,22 +11891,6 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>21.062166</v>
-      </c>
-      <c r="O212" t="n">
-        <v>105.91639</v>
-      </c>
-      <c r="P212" t="inlineStr">
-        <is>
-          <t>Bán nhà phố Kẻ Tạnh</t>
-        </is>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>Nhà mặt ngõ 65 phố Kẻ Tạnh, an ninh tốt, giấy tờ chính chủ.</t>
-        </is>
-      </c>
-      <c r="R212" t="n">
         <v>131054022</v>
       </c>
     </row>
@@ -17116,26 +11945,6 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O213" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>Nhà Ngay TĐC Thạch Bàn – Ngõ Riêng 2 Nhà Ko Đối Cửa – Nhỉnh 6 tỷ</t>
-        </is>
-      </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>-	DIện tích 30m2/ 4.5 tầng
--	Mặt tiền 3.4m nở hậu, hướng Đông Nam
--	Ngõ 3m để xe thoải mái, cách 30m2 ra khu TĐC, giao thông cực thuận tiện
--	Thiết kế 4.5 tầng, 3 ngủ đầy đủ công năng
-Phở bò/zép lào: Huy Định *** xem nhà và tư vấn miễn phí 24/7</t>
-        </is>
-      </c>
-      <c r="R213" t="n">
         <v>128854863</v>
       </c>
     </row>
@@ -17190,27 +11999,6 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O214" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>bán nhà khu phân lô cổ Linh, ngõ thông ô tô, 5 tầng, 7,5 tỷ</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>cần bán nhà đường Cổ Linh, Long Biên, nhà đẹp ở ngay.
-Vị trí: nằm khu phân lô mới Cổ Linh, gần công ăn phường Long Biên.
-- Nhà thiết kế 5 tầng, phòng ngủ rộng, đầy đủ cho gia đình sinh hoạt. trước nhà rộng thoáng, rất gần công viên, Aoen Long Biên
-- Sổ đỏ chính chủ, 36 m2, sang tên nhanh gọn
-- Giá mong muốn hơn 7,5 tỷ ( có thoả thuận)
-Liên hệ em Hương: *** để gặp chính chủ, mở cửa xem nhà</t>
-        </is>
-      </c>
-      <c r="R214" t="n">
         <v>131448988</v>
       </c>
     </row>
@@ -17265,33 +12053,6 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>21.049482</v>
-      </c>
-      <c r="O215" t="n">
-        <v>105.893654</v>
-      </c>
-      <c r="P215" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ BỒ ĐỀ -Hơn 8 tỷ-45M*5T-SÁT HỒ- NỘI THẤT-Ô TÔ 30M-MẶT TIỀN HIẾM</t>
-        </is>
-      </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>BÁN BỒ ĐỀ  -Hơn 8 tỷ- 45M*5T - SÁT HỒ- NỘI THẤT -Ô TÔ 30M- MẶT TIỀN HIẾM 
-    📍 Mô tả: - Nhà đẹp dân xây, ba bước ra hồ Bồ Đề. 500m ra trường quốc tế wellspring, bệnh viện Tâm Anh....Tiện ích vô vàn. 
-Chủ xây tâm huyết, thiết kế tỉ mỉ.💯
-🏡 Nhà 5 tầng Thiết kế: gia chủ đã decor Nội thất đầy đủ tăng lại công năng đầy đủ cho hộ gia đình 3_4 người thoải mái 
-Các phòng thiết kế anh sáng tự nhiên - không gian dễ chịu . thoáng sáng 
-- sân thượng chill chill thưởng trà thư giãn 
-- Tầng 1: PK, bếp, WC.
-- Tầng 2,3,4: Mỗi tầng 1  ngủ, wc
-.- Tầng 5: Phòng thờ, sân phơi, sân chơi
- Pháp lý:
-Sổ đỏ vuông đẹp – cất két Sẵn sàng giao dịch ngay
-LIÊN HỆ : EM PHƯƠNG  NHÀ ĐẤT LONG BIÊN</t>
-        </is>
-      </c>
-      <c r="R215" t="n">
         <v>131716158</v>
       </c>
     </row>
@@ -17346,36 +12107,6 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>21.036098</v>
-      </c>
-      <c r="O216" t="n">
-        <v>105.87419</v>
-      </c>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>Bán nhà BỒ ĐỀ-2 LÀN PHỐ-50M*6T-THANG MÁY-GARA-SÁT Ô TÔ TRÁNH-hơn 14 TỶ</t>
-        </is>
-      </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>Bán nhà BỒ ĐỀ -2  LÀN PHỐ - 50M2*6 TẦNG - THANG MÁY - GARA-SÁT Ô TÔ TRÁNH -Hơn 14 TỶ 
-  🏡 Diện tích 50m 6 TẦNG ,thang máy nhập khẩu ,gara ô tô thông các nhả
-  📍  mô tả : vị trí nhà nằm sát mặt phố 2 Làn ô tô tránh hồng tiến 
-  - ngõ thông ô tô siêu thoáng , trải nhựa sạch sẽ 
-   - 2p đi chuyển tới , cầu Chương Dương ,xung quanh bao quanh hồ , bệnh viện tâm anh , trường học ...
-  -5p đi chuyển tới Aeon long biên , cung đương đi chuyển vô cùng thuận lợi ,
-    Thiết kế công năng :
-*🏡 Phòng khách + bếp  : không gian chung rộng rãi gia chủ đã bố trí đầy đủ tiện nghi tủ bếp chất liệu nội thất cao cấp  dễ sử dụng , khoảng không gian được thiết kế cửa kính siêu rộng ,ban công rộng rãi...
-*🏡Phòng ngủ khép kín :các tầng đã decor nhẹ thiết kế  tủ kịch trần ,kệ ti vi ....vv chất liệu gỗ ốp cao cấp .k gian có khoản bạn công rộng cửa kính siêu lớn .phòng nào cũng có ánh sáng tự nhiên không khí đối lưu mát thoáng 
-    Gia chủ mới có thể decor thêm theo sở thích 
-📕 Pháp lý sổ đỏ chính chủ sang tên ngay 
- HƠN  14tỷ  – RẺ NHẤT KHU VỰC – KHÔNG CÓ CĂN THỨ 2
-📞 Gọi ngay kẻo mất: xem là thích – thích là chốt!
-☎️Em Phương  chuyên bđs Long Biên - Gia Lâm
-#BĐSLongBien #bannha #</t>
-        </is>
-      </c>
-      <c r="R216" t="n">
         <v>131715585</v>
       </c>
     </row>
@@ -17430,25 +12161,6 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>21.04023</v>
-      </c>
-      <c r="O217" t="n">
-        <v>105.87803</v>
-      </c>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>Chính chủ Bán nhà 4 tầng lô góc số nhà 31 ngõ 90 phố Hoàng Như Tiếp</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>Chính chủ Bán nhà 4 tầng lô góc số nhà 31 ngõ 90 phố Hoàng Như Tiếp trung tâm quận long biên. Diện tích sổ đỏ 51m diện tích thực tế 54m MT 4.3 m, ngõ thẳng nhìn ra mặt đường.
-Năm trên con phố là trung tâm quận sắp tới xong dự án cầu Trần hưng đạo giá đất sẽ còn tăng, bác nào có điều kiện mua về ở thì tuyệt.
-Giá em bán 11 tỷ.
-Các bác có nhu cầu liên hệ Mr Thành *** chính chủ</t>
-        </is>
-      </c>
-      <c r="R217" t="n">
         <v>131729082</v>
       </c>
     </row>
@@ -17503,32 +12215,6 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>21.025381</v>
-      </c>
-      <c r="O218" t="n">
-        <v>105.895256</v>
-      </c>
-      <c r="P218" t="inlineStr">
-        <is>
-          <t>Mặt phố kinh doanh - Phố Trạm - Long Biên - 7 tầng full nội thất</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>🔥 NHÀ PHỐ TRẠM BÁT KHỐI – 7 TẦNG THANG MÁY – GARA Ô TÔ – FULL NỘI THẤT 🔥
-🏡 Bán nhà Bát Khối – Long Biên, ở ngay, đẳng cấp
-✔ Diện tích: 58m² – MT 4.2m
-✔ 7 tầng thang máy xịn – gara ô tô
-✔ 4 phòng ngủ rộng – công năng đầy đủ
-✔ Full nội thất cao cấp – xách vali về ở ngay
-🌿 Gần hồ sinh thái, công viên – không khí trong lành
-🚗 Đường nhựa có vỉa hè – ô tô vào nhà
-🏫 Gần Aeon mall, cầu Vĩnh Tuy Gần trường, chợ, tiện ích đầy đủ
-📕 Sổ đỏ chính chủ, sẵn sàng giao dịch
-📞 Alo Em Lan  xem nhà ngay hôm nay</t>
-        </is>
-      </c>
-      <c r="R218" t="n">
         <v>131620366</v>
       </c>
     </row>
@@ -17583,35 +12269,6 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O219" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P219" t="inlineStr">
-        <is>
-          <t>🌟 SIÊU PHẨM NGỌC THUỴ - LÔ GÓC - DÒNG TIỀN ỔN ĐỊNH - CHỈ 6.98 TỶ 🌟</t>
-        </is>
-      </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>🌟 SIÊU PHẨM NGỌC THUỴ - LÔ GÓC - DÒNG TIỀN ỔN ĐỊNH - CHỈ 6.98 TỶ 🌟
-🌹 BÁN ĐẤT TẶNG NHÀ - CƠ HỘI ĐẦU TƯ SINH LỜI NGAY 🌹
-✅ Vị trí đắc địa:
-• Khu vực trung tâm Ngọc Thụy, tiện ích ngập tràn.
-• Mặt ngõ nông, cực gần đường ô tô, di chuyển thuận tiện.
-• Hiện trạng nhà 2 tầng cũ đang cho thuê 9 triệu/tháng (có sẵn dòng tiền hàng tháng).
-✅ Thiết kế tối ưu:
-• Lô góc 2 mặt thoáng, ánh sáng tự nhiên ngập tràn các phòng.
-• Tầng 1: Phòng khách, bếp, WC.
-• Tầng 2: Phòng ngủ rộng rãi, WC.
-• Khách mua có thể ở ngay hoặc xây mới cực đẹp.
-✅ Pháp lý: 📕 Sổ đỏ chính chủ, sẵn sàng giao dịch.
-💰 Giá chào: 6.98 tỷ (Có thương lượng).
-📞 Liên hệ xem nhà ngay: *** (Hỗ trợ 24/7)</t>
-        </is>
-      </c>
-      <c r="R219" t="n">
         <v>131742687</v>
       </c>
     </row>
@@ -17666,27 +12323,6 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>21.05286</v>
-      </c>
-      <c r="O220" t="n">
-        <v>105.92033</v>
-      </c>
-      <c r="P220" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ DÂN XÂY 5 TẦNG, Ô TÔ, THANG MÁY, PHÚC LỢI, VINHOMES RIVERSIDE</t>
-        </is>
-      </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>Diện tích: 50m², xây 5 tầng hiện đại.
-Tiện ích: Có THANG MÁY nhập khẩu, ô tô ra vào cực kỳ tiện lợi.
-Nhà dân xây tâm huyết năm 2021, mới sử dụng 5 năm, nội thất cao cấp được chăm chút từng chi tiết.
-Tọa lạc tại khu phân lô bàn cờ phường Phúc Lợi, hạ tầng đồng bộ, nói không với tắc đường và ngập lụt.
-Hàng xóm Vinhomes Riverside, trường Quốc tế Vin Harmony. Đi bộ ra Trường THPT Phúc Lợi (trường công lập hiện đại nhất quận) và hệ thống trường học các cấp, chợ Phúc Lợi bán kính chỉ vài trăm mét. Gần công viên, hồ điều hòa.
-Sổ đỏ chính chủ, giữ gìn cẩn thận, pháp lý sạch, giấy phép xây dựng đầy đủ. Giá thương lượng.</t>
-        </is>
-      </c>
-      <c r="R220" t="n">
         <v>131595221</v>
       </c>
     </row>
@@ -17741,39 +12377,6 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>21.068117</v>
-      </c>
-      <c r="O221" t="n">
-        <v>105.90059</v>
-      </c>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ  VIỆT HƯNG – 80M*4 Hơn 10 TỶ x– Ô TÔ ĐỖ GẦN -NGÕ THÔNG-DÂN XÂY</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ  VIỆT HƯNG – 80M*4 Hơn 10 TỶ x– Ô TÔ ĐỖ GẦN  -NGÕ THÔNG- DÂN XÂY-MẶT TIỀN RỘNG 
-    Mô tả : 
-💎 Nhà dân xây cực chắc – đẹp mới tinh, thiết kế hiện đại, phòng nào cũng sáng thoáng
-* Ngõ cực nông cái bước chân ra mặt ngõ ô tô chạy 
-🚗 Ô tô  đỗ  đầu ngõ– ngõ thông, đi lại cực tiện
-🌳 Diện tích rộng 80m ,cực hiếm tầm tiền hơn 10 tỷ x
-📍 Vị trí trung tâm Long Biên:
- • Vài phút tới BIGC Long Biên 🛍️
- • Gần chợ, trường học các cấp – tiện ích đủ đầy
- • dân trí cao, ở cực sướng
-🏡 Công năng chuẩn ở:
- • Phòng khách rộng – 3phòng ngủ thoáng
- • Cửa kính lớn, ánh sáng ngập tràn
- • Sân thượng siêu chill
-💰 HƠN  10tỷ xx – RẺ NHẤT KHU VỰC – KHÔNG CÓ CĂN THỨ 2
-📞 Gọi ngay kẻo mất: xem là thích – thích là chốt!
-☎️Em Phương  chuyên bđs Long Biên - Gia Lâm
-#BĐSLongBien #bannha #</t>
-        </is>
-      </c>
-      <c r="R221" t="n">
         <v>131716436</v>
       </c>
     </row>
@@ -17828,33 +12431,6 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>21.059816</v>
-      </c>
-      <c r="O222" t="n">
-        <v>105.863655</v>
-      </c>
-      <c r="P222" t="inlineStr">
-        <is>
-          <t>NHÀ ĐẸP NGỌC THUỴ – 5 TẦNG DÂN XÂY – NỞ HẬU CỰC LỘC – FULL NỘI THẤT 🔥</t>
-        </is>
-      </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🏡 Căn nhà tâm huyết của chủ, xây dựng chắc chắn, thiết kế tối ưu công năng. Nhà ở rất có lộc, chủ cần chuyển nhà to hơn nên muốn bán
-✨ Diện tích đẹp – nở hậu cực lộc, phong thuỷ vượng khí
-🎁 Tặng FULL nội thất, khách mua chỉ việc xách vali về ở ngay
-🚗 Ngõ nông, thông thoáng, di chuyển cực tiện
-📍 Vị trí trung tâm Ngọc Thuỵ – đi đâu cũng nhanh
-🌉 Chỉ hơn 3km ra cầu Chương Dương, kết nối phố cổ dễ dàng, không lo tắc
-🌿 Khu dân trí cao, hàng xóm thân thiện, an ninh đảm bảo
-🛍️ Tiện ích xung quanh đầy đủ: trường học, chợ, công viên… chỉ vài phút
-📕 Sổ đỏ vuông đẹp, nở hậu, pháp lý chuẩn – sẵn sàng giao dịch
-💰 Giá chỉ hơn 7 tỷ – quá tốt cho một căn 5 tầng trung tâm!
-📞 Liên hệ ngay để không bỏ lỡ căn hiếm!</t>
-        </is>
-      </c>
-      <c r="R222" t="n">
         <v>131739596</v>
       </c>
     </row>
@@ -17909,28 +12485,6 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O223" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P223" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng chủ xây kiên cố 
-+ Diện tích ; 45m2- MT 4,08m
-+ Hướng tây 
-+ Đường trước nhà 3m - ngõ thông ô tô vào nhà - đường thông tứ ngả 
-+ Tiện ích ; nhà gần trường các cấp - chợ - TTTM AEON -Long biên - và khu vực đông dân cư - mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên thổ cư long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R223" t="n">
         <v>124625248</v>
       </c>
     </row>
@@ -17985,31 +12539,6 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>21.032185</v>
-      </c>
-      <c r="O224" t="n">
-        <v>105.90883</v>
-      </c>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>Bán Nhà Đằng Sau Aeon Long Biên, Đường Ô tô tránh kinh doanh, Khu dân</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Bán Nhà Đằng Sau Aeon Long Biên, Đường Ô tô tránh kinh doanh, Khu dân cư đông đúc.
-- Nhà Xây độc lập - 40m - 5tầng 1 lửng  1tum - thang máy nhập khẩu.
-- 2 oto ngủ trong nhà - đường trước nhà 2 oto tránh 
-- Tầng 1 kinh doanh, hoặc cho thuê - Ngay liền kề Aeon Long Biên - Chợ - Trường học - UBND xung quanh đầy đủ tiện ích
-- Ngay cổng khu công nghiệp Hanel với 50 nghìn công nhân.
-- Tiện ích ngập tràn, chỉ cần xách vali về ở 
-Giá Nhỉnh 12 tỷ (có thương lượng)
-Sổ đỏ chỉnh chủ, ko tranh chấp, quy hoạch
-Liên hệ: Mr Tùng xem nhà trực tiếp</t>
-        </is>
-      </c>
-      <c r="R224" t="n">
         <v>131675491</v>
       </c>
     </row>
@@ -18064,28 +12593,6 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>21.026669</v>
-      </c>
-      <c r="O225" t="n">
-        <v>105.89605</v>
-      </c>
-      <c r="P225" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ ĐÀM QUANG TRUNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ ĐÀM QUANG TRUNG LONG BIÊN HÀ NỘI.
-+ Nhà 8 tầng chủ xây kiên cố - thang máy nhập khẩu
-+ Diện tích ; 89m2- MT 4,5m
-+ Hướng đông nam quanh năm thoáng mát 
-+ Nhà lắp đặt phun nội thất nhập khẩu 
-+ Tiện ích ; nhà nằm trên mặt tuyến phố lớn - kinh doanh sầm uất ngày và đêm - nhà gần cạnh TTTM -AEON -Long biên - rùi trường các cấp - và khu vực dân trí cáo - chỉ mất 5 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R225" t="n">
         <v>126832011</v>
       </c>
     </row>
@@ -18140,30 +12647,6 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>21.049894</v>
-      </c>
-      <c r="O226" t="n">
-        <v>105.89186</v>
-      </c>
-      <c r="P226" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ PHÚC ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ PHÚC ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng - thang máy nhập khẩu 
-+ Diện tích ; 36m2- MT 4,2m
-+ Nhà lắp đặt phun nội thất đẹp 
-+ Hiện nhà đang trong quá trình hoàn thiện nội thất để bàn giao cho khách mua nhà
-+ Hướng đông bắc
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả 
-+ Tiện ích ; nhà nằm trong khu phân lô quân đội bộ quốc phòng 918 - An Ninh Tốt - Dân trí cao toàn cán bộ hàng không - rùi nhà lại gần TTTM -AEON -Long biên - sân gôn Long biên - rùi trường các câp - và khu vực dân trí cao- mất tâmg 8 phút lái xe là qua cầu vĩnh tuy sang trung tâm thành phố hà nội rùi.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R226" t="n">
         <v>130671377</v>
       </c>
     </row>
@@ -18218,31 +12701,6 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>21.039669</v>
-      </c>
-      <c r="O227" t="n">
-        <v>105.90413</v>
-      </c>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ PHÚC ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ PHÚC ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà 8 tầng thang máy nhập khẩu
-+ Diện tích ; 120m2- MT 9,5m
-+ Nội thất đầy đủ 
-+ Nhà đã lắp đặt đầy đủ hệ thống phòng cháy chữa cháy 
-+ Khách mua về vừa ở vừa làm văn phòng công ty thì quá tuyệt vời 
-+ Hướng đông bắc
-+ Đường trước nhà 7m - vỉa hè  cách 50m ra mặt phố chu huy mân- đường thông tứ ngả 
-+ Tiện ích ngập tràn ; nhà gần cạnh phố lớn - Vinhom - rùi vườn hoa ccoong viên - trường các cấp - sân gôn Long biên - và khu vực dân trí cao- chỉ mất tầm 10 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R227" t="n">
         <v>130671767</v>
       </c>
     </row>
@@ -18297,30 +12755,6 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O228" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P228" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN  CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 7 tầng mới - thang máy nhập khẩu
-+ Diện tích ; 50m2- MT 4,6m
-+ Nhà lắp đặt phun nội thất đẹp 
-+ Hiện nhà đang trong quá trình hoàn thiện nốt nội thất 
-+ Hướng đông nam quanh năm thoáng mát
-+ Đường trước nhà 7m - vỉa hè và đã có quy hoạch mở rộng đường trước nhà 17m vỉa hè không ảnh hưởng đến nhà mình sau đường quá rộng đẹp.
-+ Tiện ích ngập tràn ; nhà gần cạnh hồ công viên thạch bàn quanh năm thoáng mát - nhà lại gần trường các cấp - chợ - TTTM AEON -Long biên - và khu vực đông dân cư - chỉ mất đúng 10 phút lái xe là sang tới trung tâm thành phố hà nội rùi.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R228" t="n">
         <v>130670388</v>
       </c>
     </row>
@@ -18375,28 +12809,6 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O229" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỔ LINH THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỔ LINH THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 7 tầng chủ xây kiên cố.
-+ Diện tích; 100m2 - MT 6m.
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả - View vườn hoa công viên.
-+ Hướng Đông.
-+ Tiện ích; nhà view vườn hoa công viên cạnh hồ ben rộng 7ha - rùi TTTM - AEON - Long Biên - rùi trường các cấp - và khu vực dân trí cao - chỉ mất 10 phút lái xe sang trung tâm thành phố Hà Nội.
-+ Liên hệ; *** - Em Thắng chuyên nhà đất Long Biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R229" t="n">
         <v>130654676</v>
       </c>
     </row>
@@ -18451,29 +12863,6 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>21.038532</v>
-      </c>
-      <c r="O230" t="n">
-        <v>105.91242</v>
-      </c>
-      <c r="P230" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ SÀI ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ SÀI ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng - thang máy nhập khẩu 
-+ Nội thất đầy đủ
-+ Diện tích ; 54m2- MT 4m
-+ Hướng đông bắc
-+ Đường trước nhà 5m - đường thông - ô tô vào nhà đường thông tứ ngả
-+ Tiện ích ; nhà cạnh phố sài đông  kinh doanh sầm uất ngày và đêm - nhà lại gần trường các cấp - rùi TTTM -AEON -Long biên - và khu vực dân trí cao- chỉ mất khoảng 10 phút lái xe là qua cầu vĩnh tuy sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R230" t="n">
         <v>130075588</v>
       </c>
     </row>
@@ -18528,29 +12917,6 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O231" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P231" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng mới - thang máy nhập khẩu 
-+ Diện tích ; 71m2- MT 4,3m
-+ Nhà đã lắp đặt phun nội thất đẹp 
-+ Hướng tây bắc
-+ Đường trước nhà 3m - ô tô vào nhà 
-+ Tiện ích ngập tràn ; nhà nằm giữa trung tâm hành chính phường long biên - rùi trường các cấp - và khu vực dân trí cao- nahf chỉ cách TTTM -AEON -Long biên có 500m - mất 8 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R231" t="n">
         <v>130584453</v>
       </c>
     </row>
@@ -18605,29 +12971,6 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>21.058416</v>
-      </c>
-      <c r="O232" t="n">
-        <v>105.89463</v>
-      </c>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ HOA LÂM VIỆT HƯNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ HOA LÂM VIỆT HƯNG LONG BIÊN HÀ NỘI.
-+ Nhà 8 tầng mới - thang máy nhập khẩu
-+ Diện tích ; 56m2- MT 4,3m
-+Nhà lắp đặt phun nội thất đẹp 
-+ Hướng đông bắc
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả
-+ Tiện ích ; nhà nằm trên tuyến phố kinh doanh sầm uất ngày và đêm - nhà lại nằm giữa trung tâm hành chính phường - rùi trường các cấp- và khu vực dân trí cao- nahf chỉ mất 10 phút lái xe là sang tới trung tâm hồ hoàn kiếm hà nội.
-+ Liên hệ ;***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R232" t="n">
         <v>130584034</v>
       </c>
     </row>
@@ -18682,30 +13025,6 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>21.026669</v>
-      </c>
-      <c r="O233" t="n">
-        <v>105.89605</v>
-      </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ ĐÀM QUANH TRUNG CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ ĐÀM QUANG TRUNG CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 7 tầng chủ xây kiên cố 
-+ Diện tích ; 89m2- MT 4,5m
-+ Hướng đông nam - quanh năm mát mẻ 
-+ Đường trước nhà 12m - đường thông tứ ngả 
-+ nhà lắp đặt phun nội thất xịn sò 
-+ Hiện nhà đang trong giai đoạn hoàn thiện nốt nội thất để bàn giao cho chủ mới  chỉ vc sách vali về ở thui
-+ Tiện ích ngập tràn ; nhà nằm trên mặt phố lớn long biên - kinh doanh sầm uất ngày và đêm - nhà lại đối diện TTTM -AEON -Long biên - rùi trường các cấp - chợ - và khu vực đông dân cư- mất 5 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên thổ cư long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R233" t="n">
         <v>124341093</v>
       </c>
     </row>
@@ -18760,29 +13079,6 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O234" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng mới - thang máy 
-+ Diện tích ; 36m2- MT 3,3m
-+ Hướng tây nam 
-+ Nội  thất cơ bản như hình
-+ Đường trước nhà 2,4m- cách 20m ra đường ô tô tránh nhau
-+ Tiện ích ; nhà gần ngay cạnh phố cổ linh sầm uất - nhà lại gần trường các cấp - rùi TTTM AEON -Long biên - và khu vực đông dân cư - chỉ mất tầm 7 phút lái xe là qua cầu vĩnh tuy sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R234" t="n">
         <v>130582815</v>
       </c>
     </row>
@@ -18837,28 +13133,6 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>21.038532</v>
-      </c>
-      <c r="O235" t="n">
-        <v>105.91242</v>
-      </c>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ SÀI ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ SÀI ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà 4 tầng cũ chủ xây kiên cố
-+ Diện tích ; 75m2- MT 4,4m
-+ Hiện nhà đang cho thuê dòng tiền tháng 
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả 
-+ Tiện ích ; nhà nằm trên tuyến phố ẩm thực kinh doanh sầm uất ngày và đêm - nhà lại gần trường các cấp - hồ điều hòa - TTTM -AEON -Long biên -và khu vực dân trí cao - mất 10 phút lái xe sang trung tâm thành phố hà nội .
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R235" t="n">
         <v>126438916</v>
       </c>
     </row>
@@ -18913,29 +13187,6 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>21.018879</v>
-      </c>
-      <c r="O236" t="n">
-        <v>105.91188</v>
-      </c>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ THẠCH BÀN CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ THẠCH BÀN CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 4 tầng xây kiên cố 
-+ Diện tích ; 144m2- MT8m
-+ Nhà lắp đăth phun nội thất xịn sò 
-+ Hướng tây bắc 
-+ Đường trước nhà 7m - đường thông tứ ngả 
-+ Tiện ích ; nhà nằm giữa khu trung tâm hành chính phường thạch bàn - rùi gần trường các cấp - chợ - TTTM -AEON -Long biên - và khu vực dân trí cao - mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên thổ cư long biên - dẫn đi xem nhà miễn phí 24/7,</t>
-        </is>
-      </c>
-      <c r="R236" t="n">
         <v>123958083</v>
       </c>
     </row>
@@ -18990,28 +13241,6 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>21.043814</v>
-      </c>
-      <c r="O237" t="n">
-        <v>105.872314</v>
-      </c>
-      <c r="P237" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ NGUYỄN VĂN CỪ LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q237" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ MẶT PHỐ NGUYỄN VĂN CỪ LONG BIÊN HÀ NỘI.
-+ Nhà 4 tầng cũ chủ xây kiên cố 
-+ Diện tích ; 70m2- MT 4,3m
-+ Hướng tây bắc 
-+ Đường trước nhà 12m- vỉa hè đường thông tứ ngả 
-+ Tiện ích ngập tràn ; nhà nằm trên tuyến phố lớn của long biên - kinh doanh sầm uất ngày và đêm - nhà lại gần trường các cấp - chợ - TTTM -và khu vực dân trí cao - mất 5 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R237" t="n">
         <v>125010972</v>
       </c>
     </row>
@@ -19066,29 +13295,6 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>21.035637</v>
-      </c>
-      <c r="O238" t="n">
-        <v>105.91076</v>
-      </c>
-      <c r="P238" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆTTHỰ LIỀN KỀ THỰ SÀI ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q238" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆTTHỰ LIỀN KỀ THỰ SÀI ĐỒNG LONG BIÊN HÀ NỘI.
-+ Nhà biệt thự 4 tầng 1 tum xây kiên cố 
-+ Diện tích ; 140m2- MT 7,2m
-+ Nhà lắp đặt phun nội thất 
-+ Hướng đông bắc 
-+ Đường trước nhà 7m- vỉa hè đường thông tứ ngả 
-+ Tiện ích ; nhà nằm trong khu vực An Ninh Tốt - Dân trí cao - nhà lại cạnh công viên hồ điều hoà - rùi trường các cấp - TTTM -AEOn -Long biên chỉ mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R238" t="n">
         <v>127183225</v>
       </c>
     </row>
@@ -19143,27 +13349,6 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>21.009169</v>
-      </c>
-      <c r="O239" t="n">
-        <v>105.915115</v>
-      </c>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỰ KHỐI LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỰ KHỐI LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng chủ xây kiên cố 
-+ Diện tích ; 33m2- MT 5m ( căn góc )
-+ Đường trước nhà 2,7m
-+ Tiện ích ; nhà gần trườn cấp 1-2 - chợ - rùi TTTM -AEON -Long biên và khu vực đông dân cư - mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R239" t="n">
         <v>126696642</v>
       </c>
     </row>
@@ -19218,29 +13403,6 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>21.025959</v>
-      </c>
-      <c r="O240" t="n">
-        <v>105.909584</v>
-      </c>
-      <c r="P240" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng mới - thang máy nhập khẩu 
-+ Diện tích ; 45m2- MT 4,1m
-+ Hướng tây 
-+ Nhà lắp đặt phun nội thất 
-+ Đường trước nhà 3m - ngõ thông ô tô vào nhà đường thông tứ ngả 
-+ Tiện ích ; nhà gần trường các cấp - chợ - TTTM -AEON -Long biên - và khu vực đông dân cư -chỉ mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R240" t="n">
         <v>125421092</v>
       </c>
     </row>
@@ -19295,28 +13457,6 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>21.019062</v>
-      </c>
-      <c r="O241" t="n">
-        <v>105.903404</v>
-      </c>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ LIỀN KỀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ BIỆT THỰ LIỀN KỀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 5 tầng xây thô chưa hoàn thiện 
-+ Diện tích ; 90m2- MT 7,6m
-+ Hướng tây bắc 
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả 
-+ Tiện ích ; nhà nằm trung khu dân trí cao - An Ninh Tốt - nhà lại gần trường các cấp - chợ - TTTM -AEON -Long biên - mất 10 phút lái xe sang trung tâm thành phố hà nội.
-+ Liên hệ ;***- Em thắng chuyên thổ cư long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R241" t="n">
         <v>124487089</v>
       </c>
     </row>
@@ -19371,29 +13511,6 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O242" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P242" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q242" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng chủ xây kiên cố - thang máy nhập khẩu ( căn góc )
-+ Diện tích ; 30m2- MT 4,2m
-+ Hướng tây 
-+ Nhà đã lắp đặt phun nội thất đẹp 
-+ Đường trước nhà 3m - ngõ thông xe nhỏ vào nhà đường thông tứ ngả - cách 200m ra mặt phố cổ linh 
-+ Tiện ích ngập tràn ; nhà gần ngay trường các cấp - rùi trung tâm TTTM-AEON -Long biên -và khu vực đông dân cư - chỉ mất có 10 phút lái xe là sang tới trung tâm thành phố .
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R242" t="n">
         <v>128768032</v>
       </c>
     </row>
@@ -19448,29 +13565,6 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>21.028275</v>
-      </c>
-      <c r="O243" t="n">
-        <v>105.917725</v>
-      </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ THẠCH BÀN LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng - thang máy nhập khẩu 
-+ Diện tích ; 56m2- MT 4,1m
-+ Hướng đông bắc 
-+Nội thất đầy đủ
-+ Đường trước nhà 6m - vỉa hè đường thông tứ ngả 
-+ Tiện ích ngập tràn ; nhà gần trường các cấp - TTTM -AEON -Long biên - avf khu vực dân trí cao - chỉ mất 10 phút lái xe sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R243" t="n">
         <v>128754111</v>
       </c>
     </row>
@@ -19525,29 +13619,6 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O244" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P244" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỔ LINH LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q244" t="inlineStr">
-        <is>
-          <t>CẦN BÁN NHÀ CỔ LINH LONG BIÊN HÀ NỘI.
-+ Nhà 6 tầng chủ xây kiên cố
-+ Diện tích ; 32m2- MT 4,5m
-+ Hướng tây bắc 
-+ Đường trước nhà 2,8m - cách đường ô tô 10m - xe nhỏ vào nhà 
-+ Nội  thất chủ đã lắp đặt đầy đủ vì chuyển công tác lên phải bán đi
-+ Tiện ích ngập tràn ; nhà đối diện TTTM -AEON -Long biên - rùi trường các cấp - chợ - và khu vực đông dân cư- chỉ mất có 5 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R244" t="n">
         <v>129005085</v>
       </c>
     </row>
@@ -19602,29 +13673,6 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>21.039352</v>
-      </c>
-      <c r="O245" t="n">
-        <v>105.90519</v>
-      </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ SÀI ĐỒNG LONG BIÊN HÀ NỘI.</t>
-        </is>
-      </c>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>CẦN BÁN BIỆT THỰ SÀI ĐỒNG LONG BIÊN HÀ NỘI.
-+ Biệt thự 4 tầng - thang máy nhập khẩu 
-+ Diện tích ; 180m2- MT 12m
-+ Hướng đông bắc 
-+ Đường trước nhà 7m - vỉa hè đường thông tứ ngả 
-+ Nhà lắp đặt phun nội thất xịn sò
-+ Tiện ích ngập tràn ; nhà cạnh vườn hoa công viên - rùi trường các cấp- hàng xóm Vinhoms - và khu vực dân trí cao - chủ mất có 10 phút lái xe là sang tới trung tâm thành phố hà nội.
-+ Liên hệ ; ***- Em thắng chuyên nhà đất long biên - dẫn đi xem nhà miễn phí 24/7.</t>
-        </is>
-      </c>
-      <c r="R245" t="n">
         <v>129012511</v>
       </c>
     </row>
@@ -19679,28 +13727,6 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>21.044842</v>
-      </c>
-      <c r="O246" t="n">
-        <v>105.86866</v>
-      </c>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>SIÊU PHẨM ĐẸP KHÔNG TÌ VẾT NGỌC LÂM-LÔ GÓC-Ô TÔ VÀO NHÀ-7 TẦNG/ TM</t>
-        </is>
-      </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>+ Full nội thất nhập khẩu
-+ DT 36m/ MT 3.6/ trước nhà 3.2m
-+ Vị trí ngõ thông thoáng
-+ Khu dân cư sầm uất, tiện ích đầy đủ
-+ Nhà thiết kế hiện đại,  thoáng sáng các phòng
-☎️ ***
-( Hà Land - thích nhà đẹp Long Biên)</t>
-        </is>
-      </c>
-      <c r="R246" t="n">
         <v>131714403</v>
       </c>
     </row>
@@ -19755,33 +13781,6 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O247" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P247" t="inlineStr">
-        <is>
-          <t>🔥 KINH DOANH ĐỈNH - SÁT CHỢ NGỌC THỤY - NHỈNH 12 TỶ 🔥</t>
-        </is>
-      </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🔥 KINH DOANH ĐỈNH - SÁT CHỢ NGỌC THỤY - NHỈNH 12 TỶ 🔥
-📍 Vị trí: Ngay sát Chợ Ngọc Thụy, Long Biên. Khu vực buôn bán sầm uất nhất phố, dòng người qua lại tấp nập ngày đêm.
-🌟 ƯU ĐIỂM VÀNG:
-• ✅ Vị trí đắc địa: Chỉ vài bước ra chợ, kinh doanh bất chấp mọi loại hình: Spa, Salon, hiệu thuốc, siêu thị mini...
-• ✅ Đường ô tô tránh: Ngõ thông, to như phố, giao thương cực thuận tiện.
-• ✅ Thang máy hiện đại: Nhà cao tầng, thiết kế thông sàn, tối ưu diện tích sử dụng.
-• ✅ Kết nối: Liền kề KĐT Khai Sơn City, 5 phút sang Phố Cổ.
-📐 THÔNG SỐ: Diện tích đẹp, nhà xây chắc chắn, sổ đỏ sẵn sàng giao dịch.
-💰 GIÁ CỰC TỐT: Chỉ nhỉnh 12 tỷ (Tiềm năng tăng giá cực cao).
-📞 LH EM ĐẠT XEM NHÀ NGAY:
-🎯 Hotline: *** (Hỗ trợ tận tâm - Xem nhà 24/7)</t>
-        </is>
-      </c>
-      <c r="R247" t="n">
         <v>131710953</v>
       </c>
     </row>
@@ -19836,36 +13835,6 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>21.00597</v>
-      </c>
-      <c r="O248" t="n">
-        <v>105.89656</v>
-      </c>
-      <c r="P248" t="inlineStr">
-        <is>
-          <t>HIẾM, NHÀ ĐẸP 5 TẦNG, CÓ VƯỜN, NGAY TRUNG TÂM CỰ KHỐI</t>
-        </is>
-      </c>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>Tổng diện tích sử dụng ~250m2
-30m2 SĐCC + 220m2 đất vườn
-Nhà xây 5 tầng chắc chắn, đang có dòng tiền 💰
-📍 Vị trí:
-Sau 1 nhà ra phố Xuân Đỗ
-Ô tô đỗ sát nhà 🚗
-Gần công viên hồ Cự Khối – cực thoáng, mát
-Xung quanh đầy đủ tiện ích: trường học, chợ, siêu thị… bán kính 1km
-🏡 Thiết kế:
-T1: Khách – bếp – VS – vườn rộng phía sau
-T2-3-4: Mỗi tầng 1 phòng + VS (đang cho thuê)
-T5: Phòng thờ + sân phơi
-👉 Phù hợp:
-Ở kết hợp đầu tư cho thuê
-Gia đình thích không gian rộng, có sân vườn hiếm trong khu</t>
-        </is>
-      </c>
-      <c r="R248" t="n">
         <v>131704440</v>
       </c>
     </row>
@@ -19920,24 +13889,6 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>21.05286</v>
-      </c>
-      <c r="O249" t="n">
-        <v>105.92033</v>
-      </c>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>chính chủ bán nhà chợ phúc lợi</t>
-        </is>
-      </c>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Mình chính chủ cần bán nhà ngay chợ phúc lợi, oto để viar hè hoặc cho vào nhà
-Nhà 5 tầng thang máy, 7 phòng ngủ, liên hệ chính chủ để giao dịch. Nhà cạnh đường lớn siêu thị chợ, cạnh khu himlam xây 12 toà Nõh và thương mại.</t>
-        </is>
-      </c>
-      <c r="R249" t="n">
         <v>131703932</v>
       </c>
     </row>
@@ -19992,28 +13943,6 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>21.02167</v>
-      </c>
-      <c r="O250" t="n">
-        <v>105.91418</v>
-      </c>
-      <c r="P250" t="inlineStr">
-        <is>
-          <t>Liền kề sát góc, 136m2, Thạch Bàn Elegant Park Villa, MT 8m, 41 tỷ</t>
-        </is>
-      </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>Liền kề áp góc (căn TT2.16), xây thô hoàn thiện mặt ngoài, tổng DTXD 400m2, khu cao cấp bảo vệ 24/24 Elegant Park Villa tại Đường Thạch Bàn, Phường Thạch Bàn, Long Biên, Hà Nội, là một lựa chọn lý tưởng cho những ai tìm kiếm không gian sống sang trọng và tiện nghi. Với thiết kế 4 tầng, 6 phòng ngủ, 5 phòng tắm, và mặt tiền rộng 8m, đường vào 12m và ngay sát cổng ra ngõ số 5 Thạch Bàn, thuận tiện cho xe ô tô, đây là một ngôi nhà hoàn hảo cho gia đình lớn hoặc những ai yêu thích sự rộng rãi. Khu cao cấp, bảo vệ 24/24, do chủ đầu tư MIK phát triển, tập trung toàn nhà lãnh đạo. Mặt tiền rộng rãi, có sẵn gara ô tô trong nhà, ô chờ thang máy, xung quanh nhiều hồ, gần công viên Thạch Bàn, Hapro Mart, Aeon Mall Long Biên trong vòng 2km.
-Giới thiệu dự án:
-https://youtu.be/LZT4qKHSZ-Y?si=1TXL0tzyr1kbDYtf
-https://youtu.be/sFAAG10480Q?si=3vEr52mVX7z_xrPl
-Sổ đỏ chính chủ, giá 41 tỷ VND thu nét. 
-Liên hệ chính chủ: Mr. Le ***
-Dự án xây công viên ngay tại hồ Ben, cạnh khu Elegant Park Villa: ***</t>
-        </is>
-      </c>
-      <c r="R250" t="n">
         <v>131703576</v>
       </c>
     </row>
@@ -20068,30 +13997,6 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>21.043814</v>
-      </c>
-      <c r="O251" t="n">
-        <v>105.872314</v>
-      </c>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>🚀 NGUYỄN VĂN CỪ - 7 TẦNG THANG MÁY - SÁT VÁCH BỆNH VIỆN TÂM ANH 🚀</t>
-        </is>
-      </c>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 🚀 NGUYỄN VĂN CỪ - 7 TẦNG THANG MÁY - SÁT VÁCH BỆNH VIỆN TÂM ANH 🚀
-Cơ hội sở hữu nhà đẹp trung tâm, vừa ở vừa làm Văn phòng/Spa cực đỉnh:
-✅ Vị trí: Ngõ ô tô vào nhà, thông thoáng. Gần Big C, Aeon Mall, trường quốc tế Wellspring.
-✅ Đẳng cấp: 7 tầng thang máy xịn. Điểm nhấn là Phòng ngủ Master + Phòng xông hơi khép kín giúp gia chủ thư giãn tại gia.
-✅ Hạ tầng: Nội thất Inax, Daikin cao cấp. Đã có công tơ điện nước riêng từng căn.
-✅ Kết nối: Vài phút sang nội thành qua cầu Chương Dương, cầu Long Biên.
-💵 Giá chào: 21 tỷ (Có thương lượng). Sổ đỏ chính chủ, pháp lý sạch.
-☎️ Alo em Đạt xem nhà ngay: [Số điện thoại]</t>
-        </is>
-      </c>
-      <c r="R251" t="n">
         <v>131482721</v>
       </c>
     </row>
@@ -20146,31 +14051,6 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O252" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P252" t="inlineStr">
-        <is>
-          <t>💥 SIÊU PHẨM NGỌC THỤY - DIỆN TÍCH KHỦNG - SÁT Ô TÔ - GIÁ ĐẦU TƯ 💥</t>
-        </is>
-      </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: 💥 SIÊU PHẨM NGỌC THỤY - DIỆN TÍCH KHỦNG - SÁT Ô TÔ - GIÁ ĐẦU TƯ 💥
-✅ Thông số: * Diện tích: 65m2 (Sổ 50.6m2), mặt tiền 4.2m cực đẹp.
-• Thiết kế: 4 tầng hiện đại, 4 phòng ngủ thoáng sáng, có sân trước sân sau.
-✅ Vị trí &amp; Tiện ích:
-• Cách đường ô tô tránh đúng 20m, cách phố Ngọc Thụy 200m.
-• Ngay sát Hồ điều hòa khu VIP, chợ, trường mầm non, cấp 1-2.
-• Khu dân trí cao, an ninh tốt, không gian sống xanh sạch.
-⚖️ Pháp lý: Sổ đỏ chính chủ, vuông vắn, sẵn sàng giao dịch.
-💰 Giá bán: 9.x tỷ (Có thương lượng).</t>
-        </is>
-      </c>
-      <c r="R252" t="n">
         <v>131701338</v>
       </c>
     </row>
@@ -20225,26 +14105,6 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O253" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P253" t="inlineStr">
-        <is>
-          <t>Mặt Tư Đình 61m2 x 6 Tầng, Thang Máy, Ô Tô Tránh - Nhỉnh 15B</t>
-        </is>
-      </c>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>-	Diện tích 61m2, xây dựng 40m2/ 6 tầng
--	Mặt tiền 4m nở hậu, hướng Tây Nam
--	Đường trước nhà kinh doanh, ô tô tránh, ra vào thoải mái, ngõ thông chợ - đường Cổ Linh
--	Nhà thiết kế 6 tầng, nội thất sang trọng thang máy nhập khẩu
--	Giá Nhỉnh 15 tỷ nhẹ</t>
-        </is>
-      </c>
-      <c r="R253" t="n">
         <v>127886469</v>
       </c>
     </row>
@@ -20299,42 +14159,6 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>21.031935</v>
-      </c>
-      <c r="O254" t="n">
-        <v>105.87937</v>
-      </c>
-      <c r="P254" t="inlineStr">
-        <is>
-          <t>Bán nhà phố Cổ Linh -Long Biên ,40m2x5 T,Ô tô Tránh .12,5 tỷ</t>
-        </is>
-      </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>Bán nhà phố Cổ Linh -Long Biên ,40m2x5 T,Ô tô Tránh .12,5 tỷ
-🔥 NHÀ PHỐ CỔ LINH – LONG BIÊN – Ô TÔ TRÁNH – 40M² x 5T – GIÁ 12,5 TỶ
-💥 SIÊU PHẨM PHÂN LÔ – Ô TÔ TRÁNH – Ở SƯỚNG KẾT HỢP KINH DOANH
-Hàng hiếm khu vực Cổ Linh – giá trị tăng trưởng cực mạnh!
-📐 Diện tích: 40m²
-🏢 Kết cấu: 5 tầng
-🚗 Đường: Ô tô tránh – đỗ cửa
-📜 Pháp lý: Sổ đỏ vuông đẹp
-🏡 Công năng cực hợp lý:
-Tầng 1: Gara ô tô / kinh doanh
-Tầng 2: Phòng khách + bếp
-Tầng 3,4: Mỗi tầng 2 phòng ngủ + WC xịn
-Tầng 5: Phòng thờ + sân phơi
-✨ Nhà mới đẹp – nội thất xịn – vào ở ngay
-📍 Vị trí vàng:
-Gần cầu Vĩnh Tuy
-Đối diện AEON Mall Long Biên
-Khu dân cư đông đúc – kinh doanh sầm uất
-An sinh tốt – yên tĩnh – đáng sống
-💰 Giá bán: 12,5 tỷ (có thương lượng)
-📞 Liên hệ: Chu Mạnh Đồng .</t>
-        </is>
-      </c>
-      <c r="R254" t="n">
         <v>131681935</v>
       </c>
     </row>
@@ -20389,45 +14213,6 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>21.037178</v>
-      </c>
-      <c r="O255" t="n">
-        <v>105.87307</v>
-      </c>
-      <c r="P255" t="inlineStr">
-        <is>
-          <t>NHÀ NGỌC THỤY – Ô TÔ TRÁNH – THANG MÁY – KINH DOANH  –  12.75 TỶ</t>
-        </is>
-      </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>🏡 NHÀ NGỌC THỤY – LONG BIÊN
-🚗 Ô TÔ TRÁNH – THANG MÁY – KINH DOANH
-💰 Giá chỉ 12.75 tỷ
-✨ Điểm nổi bật:
-Ngõ thông, ô tô tránh nhau – cực hiếm phân khúc
-Khu dân cư đông đúc, kinh doanh tốt
-Gần công viên Ngọc Thụy, tiện ích đầy đủ
-Di chuyển nhanh qua cầu Long Biên, Chương Dương vào trung tâm
-📐 Thông số:
-Diện tích: 50m²
-30m² đất ở lâu dài
-20m² đất trồng cây lâu năm
-Mặt tiền: 4m
-Hướng: Tây Nam
-🏗 Kết cấu:
-Nhà 4 tầng, thiết kế thông sàn
-Thang máy + thang bộ + lối thoát hiểm
-Xây chắc chắn, full nội thất → vào ở ngay
-💼 Công năng:
-Ở kết hợp kinh doanh cực tốt
-Phù hợp: văn phòng, spa, salon, shop
-Đang cho thuê 22 triệu/tháng → dòng tiền sẵn
-⚖ Pháp lý: Sổ đỏ riêng
-📞 Liên hệ: ***</t>
-        </is>
-      </c>
-      <c r="R255" t="n">
         <v>131679926</v>
       </c>
     </row>
@@ -20482,33 +14267,6 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>21.0472</v>
-      </c>
-      <c r="O256" t="n">
-        <v>105.91091</v>
-      </c>
-      <c r="P256" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ 7 TẦNG 1 TUM số 10, ngõ 99/59, PHỐ CHU HUY MÂN, LONG BIÊN, HN.</t>
-        </is>
-      </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Dự án: 
-Thông tin chi tiết: BÁN NHÀ 7 TẦNG 1 TUM số 10, ngõ 99/59, PHỐ CHU HUY MÂN, LONG BIÊN, HN.
-📐 Dt 40m², mt 4m, 7 tầng 1 tum, thang máy xịn
-T1 : để ô tô
-T2,3,4,5: 4 phòng ngủ, 5 wc, có phòng tắm master
-T6: bếp+ khách
-T7:  phòng thờ, sân phơi
-🚗 Ngõ thông tứ phía, trường quốc tế cấp 1,2 cạnh nhà, cạnh chợ Phúc Đồng, hàng xóm khu Vinhome riverside, dân cư đông đúc, tiện ích xung quanh đầy đủ. Nhà xây kiên cố, thiết kế hiện đại, phù hợp ở hoặc cho thuê. Full nội thất, chỉ cần xách vali đến ở.
-💰 Giá bán: 15,5 tỷ, hoa hồng 2%
-LH: ***
-Đào Kim Ngân</t>
-        </is>
-      </c>
-      <c r="R256" t="n">
         <v>131638126</v>
       </c>
     </row>
@@ -20563,27 +14321,6 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>21.055147</v>
-      </c>
-      <c r="O257" t="n">
-        <v>105.90521</v>
-      </c>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>SIÊU PHẨM VIỆT HƯNG - Ô TÔ 7 CHỖ ĐỖ CỬA - DÒNG TIỀN 6 TỶ</t>
-        </is>
-      </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Anh chị dòng tiền 6tỷ mua ngay căn này ở sướng, nhà Việt Hưng-Long Biên 35M 5tầng -full nội thất -Ô tô  7 chỗ đón ngay cửa 
-_ Tiện ích ngập tràn, ngõ thông , đi bộ vài bước ra mặt phố sầm uất 
-_ Giá trị: Phù hợp cho gia đình trẻ muốn ở sướng hoặc đầu tư giữ tiền cực tốt.
-_ Pháp lý chuẩn
-☎️ Gọi e Lan *** để xem nhà</t>
-        </is>
-      </c>
-      <c r="R257" t="n">
         <v>131663764</v>
       </c>
     </row>
@@ -20638,28 +14375,6 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>21.04372</v>
-      </c>
-      <c r="O258" t="n">
-        <v>105.92593</v>
-      </c>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>Nhà Đẹp Nguyễn Lam . Long Biên. Hà Nội</t>
-        </is>
-      </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: Cơ Hội Vàng……
-Nhà Đẹp Nguyễn Lam. Phúc Đồng. Long Biên . 6 tầng thang máy di chuyển nhẹ nhàng 
-Dt 42m2* 6 tầng. Full công năng sử dụng. Tặng nội thất lung Linh 
-Khu tiện ích VIP. Đối diện là giới tinh hoa Vinhome 
-Zá bán 12.x tỷ
-Lh TT *** 24/7</t>
-        </is>
-      </c>
-      <c r="R258" t="n">
         <v>131651958</v>
       </c>
     </row>
@@ -20714,30 +14429,6 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>21.030355</v>
-      </c>
-      <c r="O259" t="n">
-        <v>105.88742</v>
-      </c>
-      <c r="P259" t="inlineStr">
-        <is>
-          <t>BÁN NHÀ TƯ ĐÌNH,LONG BIÊN DÂN XÂY 50M 5TẦNG-4 PHÒNG NGỦ-Ô TÔ ĐỖ CỬA</t>
-        </is>
-      </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>Dự án: 
-Thông tin chi tiết: _ 📍 Vị trí vàng: * Khu vực Tư Đình, trung tâm kết nối: 500m tới Cầu Chương Dương, BV Tâm Anh, Trường quốc tế Wellspring.
-• Tương lai rạng ngời với dự án Cầu Trần Hưng Đạo, di chuyển sang phố cổ chỉ trong vài phút.
-🏠 Thông số &amp; Thiết kế: * Diện tích: 50m  x 5 tầng (Dân tự xây tâm huyết, cực kỳ chắc chắn).
-• Kiến trúc: Phong cách Tân cổ điển sang trọng, công năng tối ưu với 4 phòng ngủ (có Master) + 5 WC khép kín.
-• Tiện nghi: Full nội thất cao cấp (giường tủ âm tường, điều hòa, sofa...). Chủ tặng lại toàn bộ cho khách thiện chí.
-✨ Ưu điểm vượt trội:
-• Đường thông, ô tô đỗ cửa, không gian ở cực thoáng và sướng.
-• Sổ đỏ vuông nét như phân lô, giao dịch ngay.</t>
-        </is>
-      </c>
-      <c r="R259" t="n">
         <v>131655454</v>
       </c>
     </row>
